--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$U$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$K$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$25</definedName>
   </definedNames>
@@ -4240,7 +4240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4569,22 +4569,22 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-VOL-III</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>Volume III referenced (VOL-I 3.1), not supplied; pack confirmed complete (2 Oct). Only Drawing 03-C-114 shows the effluent main's delivery point (VOL-II 5.1). No omission claim after the PDD (VOL-I 3.4)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
@@ -4592,22 +4592,22 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr"/>
@@ -4615,12 +4615,12 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>I-SLICE-ADD-01</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ADD-01: 3 of 36 provisions are outside this register slice (listed in A2); their effect on rows not in the slice is not modelled</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>C20 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr"/>
@@ -4638,12 +4638,12 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-SLICE-ADD-01</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01: 3 of 36 provisions are outside this register slice (listed in A2); their effect on rows not in the slice is not modelled</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C20 (automatic)</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr"/>
@@ -4661,12 +4661,12 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -4684,12 +4684,12 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>I-SLICE-ADD-02</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ADD-02: 7 of 40 provisions are outside this register slice (listed in A2); their effect on rows not in the slice is not modelled</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>C20 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr"/>
@@ -4707,12 +4707,12 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-STALE</t>
+          <t>I-SLICE-ADD-02</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>STALE at ADD-02 (a dependency changed after the interpretation was made; dates recomputed, reading needs a person): VOL-I-8.3-01</t>
+          <t>ADD-02: 7 of 40 provisions are outside this register slice (listed in A2); their effect on rows not in the slice is not modelled</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -4722,24 +4722,20 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>C11 (automatic)</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.3-01</t>
-        </is>
-      </c>
+          <t>C20 (automatic)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-STALE</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>STALE at ADD-02 (a dependency changed after the interpretation was made; dates recomputed, reading needs a person): VOL-I-8.3-01</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -4749,79 +4745,79 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr"/>
+          <t>C11 (automatic)</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.3-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PENDING-READINGS</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Rows relying on image readings still pending the owner's review: VOL-I-9.4-01, VOL-II-T2-4-TN, VOL-IV-F4C-04, VOL-IV-F4C-N1</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>readings (automatic)</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-9.4-01; VOL-II-T2-4-TN; VOL-IV-F4C-04; VOL-IV-F4C-N1</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-PENDING-READINGS</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>Rows relying on image readings still pending the owner's review: VOL-I-9.4-01, VOL-II-T2-4-TN, VOL-IV-F4C-04, VOL-IV-F4C-N1</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>readings (automatic)</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>VOL-I-9.4-01; VOL-II-T2-4-TN; VOL-IV-F4C-04; VOL-IV-F4C-N1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -4831,39 +4827,66 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>I-A5-attendance-notice</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>I-A5-lcc-certificate</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Commercial</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E24"/>
+  <autoFilter ref="A1:E25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr"/>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -12,13 +12,15 @@
     <sheet name="Issues" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Stages" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Date coverage" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$X$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -516,14 +518,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A1 Obligations and compliance register — SLICE (Stage 2 first connected version)</t>
+          <t>A1 Obligations and compliance register — WORKING DRAFT</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>DRAFT. 202 representative rows, not the full register. Interpretations and amendment ops are PROPOSED by the assistant and not reviewed by a person; image readings are PENDING the owner's review. Validated state: ADD-02.</t>
+          <t>WORKING DRAFT, full register: 202 rows (review status: proposed 202; amendment ops: proposed 37). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: VOL-II-p3-r1, VOL-IV-p6-r1. Validated state: ADD-02.</t>
         </is>
       </c>
     </row>
@@ -757,7 +759,7 @@
       </c>
       <c r="V5" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/2.1: proposed</t>
         </is>
       </c>
       <c r="W5" s="4" t="inlineStr">
@@ -1689,7 +1691,7 @@
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/4.1: proposed; ADD-02/9.1: proposed</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
@@ -2157,7 +2159,7 @@
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
@@ -2743,7 +2745,7 @@
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
@@ -2857,7 +2859,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/4.1: proposed</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -3073,7 +3075,7 @@
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/T1-1-rev/note(2): proposed</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
@@ -3403,7 +3405,7 @@
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -3513,7 +3515,7 @@
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -3623,7 +3625,7 @@
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/5.1: proposed</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -4193,7 +4195,7 @@
       </c>
       <c r="V35" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="W35" s="4" t="inlineStr">
@@ -4307,7 +4309,7 @@
       </c>
       <c r="V36" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="W36" s="4" t="inlineStr">
@@ -4421,7 +4423,7 @@
       </c>
       <c r="V37" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/7.1: proposed</t>
         </is>
       </c>
       <c r="W37" s="4" t="inlineStr">
@@ -7311,7 +7313,7 @@
       </c>
       <c r="V62" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/2.1: proposed</t>
         </is>
       </c>
       <c r="W62" s="4" t="inlineStr">
@@ -8801,7 +8803,7 @@
       </c>
       <c r="V75" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W75" s="4" t="inlineStr">
@@ -8911,7 +8913,7 @@
       </c>
       <c r="V76" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W76" s="4" t="inlineStr">
@@ -9021,7 +9023,7 @@
       </c>
       <c r="V77" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W77" s="4" t="inlineStr">
@@ -9131,7 +9133,7 @@
       </c>
       <c r="V78" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/3.1: proposed</t>
         </is>
       </c>
       <c r="W78" s="4" t="inlineStr">
@@ -13855,7 +13857,7 @@
       </c>
       <c r="V120" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/4.1: proposed</t>
         </is>
       </c>
       <c r="W120" s="4" t="inlineStr">
@@ -14417,7 +14419,7 @@
       </c>
       <c r="V125" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/5.1: proposed</t>
         </is>
       </c>
       <c r="W125" s="4" t="inlineStr">
@@ -14527,7 +14529,7 @@
       </c>
       <c r="V126" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/5.1: proposed</t>
         </is>
       </c>
       <c r="W126" s="4" t="inlineStr">
@@ -17895,7 +17897,7 @@
       </c>
       <c r="V156" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W156" s="4" t="inlineStr">
@@ -18009,7 +18011,7 @@
       </c>
       <c r="V157" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W157" s="4" t="inlineStr">
@@ -18127,7 +18129,7 @@
       </c>
       <c r="V158" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W158" s="4" t="inlineStr">
@@ -18241,7 +18243,7 @@
       </c>
       <c r="V159" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W159" s="4" t="inlineStr">
@@ -18355,7 +18357,7 @@
       </c>
       <c r="V160" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W160" s="4" t="inlineStr">
@@ -18469,7 +18471,7 @@
       </c>
       <c r="V161" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-01/AppA/para1: proposed</t>
         </is>
       </c>
       <c r="W161" s="4" t="inlineStr">
@@ -22799,7 +22801,7 @@
       </c>
       <c r="V200" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>ADD-02/8.1: proposed</t>
         </is>
       </c>
       <c r="W200" s="4" t="inlineStr">
@@ -28507,7 +28509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -28516,11 +28518,10 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28566,15 +28567,10 @@
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Outside slice</t>
+          <t>Unresolved</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
-        <is>
-          <t>Unresolved</t>
-        </is>
-      </c>
-      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Validated</t>
         </is>
@@ -28606,10 +28602,7 @@
       <c r="I2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" s="4" t="b">
+      <c r="J2" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28642,7 +28635,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed 15</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
@@ -28651,10 +28644,7 @@
       <c r="I3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" s="4" t="b">
+      <c r="J3" s="4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -28687,7 +28677,7 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>proposed 22</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -28696,15 +28686,12 @@
       <c r="I4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" s="4" t="b">
+      <c r="J4" s="4" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:J4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -30092,4 +30079,1295 @@
   <autoFilter ref="A1:D62"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Phrase</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>By</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Sentence</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:cover/para3</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, the start of the VOL-I 4.2 blackout)</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:4.3</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>two (2) Working Days</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-4.3-01 SPOC-CHANGE-NOTICE</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Each Bidder shall nominate a single point of contact and shall notify the Authority of any change within two (2) Working Days.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:5.2</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-5.2-01 CLARIFICATION-CUTOFF</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Requests for clarification shall be submitted no later than ten (10) Working Days before the Proposal Due Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:5.4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>30 September 2026</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-5.4-01 PRE-BID</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>A Pre-Bid Conference will be held on Wednesday 30 September 2026 at 10:00 Riyadh time at the Authority's offices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.1</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>00 hours</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01 PDD</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Proposals shall be received by the Authority not later than 14:00 hours Riyadh time on Thursday 26 November 2026 at the address given in Appendix 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.1</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>26 November 2026</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>defines PDD</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Proposals shall be received by the Authority not later than 14:00 hours Riyadh time on Thursday 26 November 2026 at the address given in Appendix 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:6.3</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>eighty (180) days</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.3-01 BID-BOND-VALIDITY</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Envelope A shall be accompanied by a Bid Bond which shall remain valid for one hundred and eighty (180) days from the Proposal Due Date and shall be extended on demand where the Authority extends the period of Proposal v</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:7.1</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>fifty (150) days</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-7.1-01 PROPOSAL-VALIDITY</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Each Proposal shall remain open for acceptance for one hundred and fifty (150) days from the Proposal Due Date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.5#fn12</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) years</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.5-01 REFERENCE-LOOKBACK</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>For the avoidance of doubt, a Bidder that does not evidence at least two (2) reference sewage treatment plants, each of nominal capacity not less than 80,000 m³/day and each having achieved commercial operation within th</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.8</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.8-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>The proposed O&amp;M Operator shall evidence not less than five (5) years of continuous operation of at least one (1) wastewater treatment facility of nominal capacity not less than 50,000 m³/day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.10</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.10-01 DEBARMENT-LOOKBACK</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.1</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>twenty-five (25) years</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.1-01 CONCESSION-END-PCOD</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>The concession period shall be twenty-five (25) years commencing on the Project Commercial Operation Date, following which the Project shall transfer to the Authority in accordance with Volume V.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.2</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>twenty (120) days</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.2-01 PB-COMMERCIAL-CLOSE</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days, and Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>seventy (270) days</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-12.2-02 PB-FINANCIAL-CLOSE</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days, and Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>authority: standstill of ten Working Days before the Authority executes the Project Agreement; no bidder action</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>A standstill period of ten (10) Working Days shall apply between the Preferred Bidder Notification and execution of the Project Agreement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:12.4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>twenty (20) Working Days</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>informational: an optional right of unsuccessful Bidders to request a debrief; not an obligation</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Unsuccessful Bidders may request a debrief within twenty (20) Working Days of notification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:cover/para3</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, fixed)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>fifty (50) years</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.2-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>The design life of all civil structures shall be not less than fifty (50) years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.2</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>twenty (20) years</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.2-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>The design life of mechanical and electrical equipment shall be not less than twenty (20) years or the manufacturer's rated life, whichever is the shorter, with lifecycle replacement provided for in the Project Company's</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:3.2</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>seven (7) years</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-3.2-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Where a membrane process is proposed, the Project Company shall demonstrate membrane replacement provisions in the lifecycle plan and shall warrant a membrane life of not less than seven (7) years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:4.4</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>ninety-six (96) hours</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-4.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Standby power shall be sized to carry the full inlet works, the disinfection stage and the effluent pumping station for not less than ninety-six (96) hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:5.5</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>475 years</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-5.5-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>All permanent civil structures shall be designed for a seismic event with a return period of 475 years and for a flood with a return period of 100 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:5.5</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>100 years</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-5.5-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>All permanent civil structures shall be designed for a seismic event with a return period of 475 years and for a flood with a return period of 100 years.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:6.4</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>seven (7) years</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-6.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>All process data shall be retained for not less than seven (7) years and shall be made available to the Authority on demand in a non-proprietary format.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.2</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>thirty (30) days</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.2-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>PCOD shall not be certified until the Facility has completed a continuous reliability run of thirty (30) days at not less than 90% of nominal capacity, during which every parameter in Table 2-4 has been met.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.4</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>sixty (60) days</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.4-01 VOL-II-AS-BUILT-DUE</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall provide as-built documentation, operation and maintenance manuals, and an asset register in the Authority's standard format not later than sixty (60) days after PCOD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.1</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>two (2) years</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.1-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall hold a spare parts inventory sufficient for two (2) years of normal operation for all items with a lead time exceeding twelve (12) weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.1</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>twelve (12) weeks</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.1-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall hold a spare parts inventory sufficient for two (2) years of normal operation for all items with a lead time exceeding twelve (12) weeks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:8.5</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>two (2) years</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-8.5-01 VOL-II-HANDBACK-SURVEY-WINDOW</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>A handback condition survey shall be carried out in the final two (2) years of the concession, and any remedial works identified shall be completed before transfer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:cover/para3</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and issue date (14 September 2026, a fixed date); no bidder obligation</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:cover/para3</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>informational: tender reference and date of issue (14 September 2026, fixed)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>14 September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:3.1</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>twenty-five (25) years</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-3.1-01 VOL-V-TERM-END</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>This Agreement shall come into force on the Effective Date and shall continue for a period of twenty-five (25) years from the Effective Date, unless terminated earlier in accordance with its terms.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:12.1</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>thirty-six (36) months</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-12.1-01 VOL-V-SCHEDULED-PCOD</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall achieve PCOD within thirty-six (36) months of the Notice to Proceed (the Scheduled PCOD).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.3</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>sixty-five (365) days</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-18.3-01 VOL-V-PCOD-LONG-STOP</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>If PCOD has not been achieved within three hundred and sixty-five (365) days after the Scheduled PCOD, the Authority may terminate under Clause 39.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.3</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>twelve (12) months</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.3-01 VOL-V-RAMP-UP-END</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>During the first twelve (12) months after PCOD (the Ramp-Up Period) the Availability Payment shall be paid at ninety per cent (90%) of the full rate, and no availability deduction shall apply to a parameter listed in Tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.4</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>ten (10) Working Days</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.4-01 VOL-V-INVOICE-DUE</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Invoices shall be submitted within ten (10) Working Days of each month end and shall be paid within thirty (30) days of receipt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.4</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>thirty (30) days</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.4-01 VOL-V-INVOICE-DUE</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Invoices shall be submitted within ten (10) Working Days of each month end and shall be paid within thirty (30) days of receipt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.3</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>twenty-four (24) hours</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.3-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>A cure period of twenty-four (24) hours applies to an Unavailability Event under Clause 31.1(a) and of seventy-two (72) hours to an event under Clause 31.1(c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.3</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>seventy-two (72) hours</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.3-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>A cure period of twenty-four (24) hours applies to an Unavailability Event under Clause 31.1(a) and of seventy-two (72) hours to an event under Clause 31.1(c).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.4</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>ninety (90) day</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Persistent breach, being three (3) or more Unavailability Events in any rolling ninety (90) day period, entitles the Authority to require a remediation plan and, on a second occurrence, to terminate under Clause 39.3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:34.3</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>five (5) Working Days</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-34.3-01 VOL-V-RELIEF-EVENT-NOTICE</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall notify a Relief Event within five (5) Working Days of becoming aware of it, failing which no relief shall be granted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.4</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>sixty (60) days</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">informational: the Project Company's right to terminate for an Authority Event of Default (unpaid undisputed sum over SAR 20,000,000 for 60 days after notice); </t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company may terminate for an Authority Event of Default, being a failure to pay an undisputed sum exceeding SAR 20,000,000 that continues for sixty (60) days after notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:42.1</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>five (5) years</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-42.1-02 quotes it as part of the requirement</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>The Project Company shall transfer the Facility to the Authority on expiry in the condition required by Volume II Clause 8.5, free of encumbrance and with a remaining design life of not less than five (5) years for all m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01:3.1</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>five (5) Working Days</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>rule</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01 ATTENDANCE-NOTICE</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01:AppA/proposal-due-date</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>12 November 2026</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>printed</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>prints the PDD as 2026-11-12; the effective date is 2026-11-26 (raised as an issue, C31; not corrected)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>12 November 2026, 14:00 Riyadh time</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02:F4-G/T1/4</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>twenty-four (24) hours</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>post_award</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02-F4G-01: undertaking 4: notify security incidents within 24 hours of detection, after award; an event-driven period, not a bid-stage date</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$X$206</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$E$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$62</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
@@ -27470,7 +27470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -28315,12 +28315,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-STALE</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -28330,24 +28330,20 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>C11 (automatic)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -28357,7 +28353,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -28365,93 +28361,89 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PENDING-READINGS</t>
+          <t>I-AUTO-STALE</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
+          <t>3 row(s) STALE at ADD-02: a dependency changed after the interpretation was made (dates recomputed; the reading needs a person). Rows: VOL-I-8.3-01, VOL-I-3.4-01, VOL-I-6.7-01</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>readings (automatic)</t>
+          <t>C11 (automatic)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
+          <t>VOL-I-8.3-01; VOL-I-3.4-01; VOL-I-6.7-01</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-PENDING-READINGS</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>20 row(s) rely on image readings (Table 2-4, Form 4-C) still pending the owner's review. Rows: VOL-I-9.4-01, VOL-II-2.5-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-NOTE1, VOL-II-T2-4-OilGrease, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-TSS, VOL-II-T2-4-Turbidity, VOL-II-T2-4-pH, VOL-IV-F4C-01, VOL-IV-F4C-02, VOL-IV-F4C-03, VOL-IV-F4C-04, VOL-IV-F4C-05, VOL-IV-F4C-N1, VOL-V-29.3-01</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
+          <t>readings (automatic)</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+          <t>VOL-I-9.4-01; VOL-II-2.5-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-04; VOL-IV-F4C-05; VOL-IV-F4C-N1; VOL-V-29.3-01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (latest start 2026-10-06 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -28473,32 +28465,86 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
+          <t>I-A5-attendance-notice</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>A5 attendance-notice: DEADLINE PASSED (ATTENDANCE-NOTICE = 2026-10-14 is before the status date 2026-10-22; record whether it was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-lcc-certificate</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>A5 lcc-certificate: INFEASIBLE by 7 WD (latest start 2026-10-13 is before the status date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.6-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; attendance-notice DEADLINE PASSED; lcc-certificate INFEASIBLE by 7 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>ADD-01-3.1-01; VOL-I-5.4-01; VOL-I-8.6-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E39"/>
+  <autoFilter ref="A1:E41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$100</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$44</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33676,7 +33676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D65"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -34600,7 +34600,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before 14:00 on the PDD; not stated</t>
+          <t>PROVISIONAL ASSUMPTION: courier to the Appendix 3 address before the Proposal Due Date time stated in VOL-I 6.1 as amended (the time is derived, not assumed); not stated</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -35074,17 +35074,17 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>planning.delivery_cutoff_time</t>
+          <t>calendar.holidays</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>configurable planning choice</t>
+          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -35093,30 +35093,8 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>calendar.holidays</t>
-        </is>
-      </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>the pack declares none (VOL-I 2.4 excludes declared public holidays)</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>Bid manager</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D65"/>
+  <autoFilter ref="A1:D64"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -13,14 +13,16 @@
     <sheet name="Stages" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Date coverage" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Relationships" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AB$209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AC$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$100</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$64</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Relationships'!$A$1:$O$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB209"/>
+  <dimension ref="A1:AC209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -509,6 +511,7 @@
     <col width="14" customWidth="1" min="26" max="26"/>
     <col width="50" customWidth="1" min="27" max="27"/>
     <col width="20" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,6 +669,11 @@
           <t>Issues</t>
         </is>
       </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Relationships (curated links, their status; reached at the validated stage; documents not supplied)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -804,6 +812,7 @@
         </is>
       </c>
       <c r="AB5" s="4" t="inlineStr"/>
+      <c r="AC5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -942,6 +951,7 @@
         </is>
       </c>
       <c r="AB6" s="4" t="inlineStr"/>
+      <c r="AC6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1080,6 +1090,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1214,6 +1225,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1348,6 +1360,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1486,6 +1499,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1624,6 +1638,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1764,6 +1779,7 @@
         </is>
       </c>
       <c r="AB12" s="4" t="inlineStr"/>
+      <c r="AC12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1904,6 +1920,7 @@
           <t>I-LCC-ISSUER</t>
         </is>
       </c>
+      <c r="AC13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -2046,6 +2063,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -2176,6 +2194,7 @@
         </is>
       </c>
       <c r="AB15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2314,6 +2333,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AC16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -2448,6 +2468,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AC17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -2588,6 +2609,11 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -2726,6 +2752,7 @@
           <t>I-READING-F4C; I-F4C-EXCLUSION</t>
         </is>
       </c>
+      <c r="AC19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -2862,6 +2889,11 @@
       <c r="AB20" s="4" t="inlineStr">
         <is>
           <t>I-READING-F4C</t>
+        </is>
+      </c>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FORM-4C [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -2996,6 +3028,7 @@
           <t>I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AC21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -3122,6 +3155,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -3248,6 +3282,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -3374,6 +3409,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -3500,6 +3536,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -3630,6 +3667,7 @@
         </is>
       </c>
       <c r="AB26" s="4" t="inlineStr"/>
+      <c r="AC26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -3760,6 +3798,7 @@
         </is>
       </c>
       <c r="AB27" s="4" t="inlineStr"/>
+      <c r="AC27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3890,6 +3929,7 @@
         </is>
       </c>
       <c r="AB28" s="4" t="inlineStr"/>
+      <c r="AC28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -4020,6 +4060,7 @@
         </is>
       </c>
       <c r="AB29" s="4" t="inlineStr"/>
+      <c r="AC29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -4154,6 +4195,7 @@
         </is>
       </c>
       <c r="AB30" s="4" t="inlineStr"/>
+      <c r="AC30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -4284,6 +4326,7 @@
         </is>
       </c>
       <c r="AB31" s="4" t="inlineStr"/>
+      <c r="AC31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -4414,6 +4457,7 @@
         </is>
       </c>
       <c r="AB32" s="4" t="inlineStr"/>
+      <c r="AC32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -4546,6 +4590,11 @@
       <c r="AB33" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -4684,6 +4733,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4814,6 +4864,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AC35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -4942,6 +4993,7 @@
           <t>I-NO-CONSEQUENCE; I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -5070,6 +5122,7 @@
           <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
+      <c r="AC37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5196,6 +5249,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -5322,6 +5376,7 @@
           <t>I-F4G-NO</t>
         </is>
       </c>
+      <c r="AC39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -5448,6 +5503,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -5586,6 +5642,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -5724,6 +5781,7 @@
           <t>I-VOL-I-ENV-B; I-VOL-I-ENV-A-PRICES; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -5866,6 +5924,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AC43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -5996,6 +6055,7 @@
         </is>
       </c>
       <c r="AB44" s="4" t="inlineStr"/>
+      <c r="AC44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -6134,6 +6194,7 @@
         </is>
       </c>
       <c r="AB45" s="4" t="inlineStr"/>
+      <c r="AC45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -6268,6 +6329,7 @@
         </is>
       </c>
       <c r="AB46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -6398,6 +6460,7 @@
         </is>
       </c>
       <c r="AB47" s="4" t="inlineStr"/>
+      <c r="AC47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -6532,6 +6595,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AC48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -6666,6 +6730,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -6804,6 +6869,7 @@
           <t>I-VOL-I-ENV-A-PRICES</t>
         </is>
       </c>
+      <c r="AC50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -6938,6 +7004,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-COPIES</t>
         </is>
       </c>
+      <c r="AC51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -7078,6 +7145,7 @@
           <t>I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AC52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -7216,6 +7284,7 @@
         </is>
       </c>
       <c r="AB53" s="4" t="inlineStr"/>
+      <c r="AC53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -7346,6 +7415,7 @@
         </is>
       </c>
       <c r="AB54" s="4" t="inlineStr"/>
+      <c r="AC54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -7484,6 +7554,7 @@
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -7620,6 +7691,11 @@
       <c r="AB56" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -7756,6 +7832,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -7890,6 +7971,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-FIN-STANDING [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -8026,6 +8112,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -8160,6 +8247,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -8298,6 +8386,11 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-INVESTMENT-LICENCE [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -8434,6 +8527,11 @@
       <c r="AB62" s="4" t="inlineStr">
         <is>
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
         </is>
       </c>
     </row>
@@ -8588,6 +8686,7 @@
           <t>I-NO-CONSEQUENCE; I-F4G-LETTERING</t>
         </is>
       </c>
+      <c r="AC63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -8722,6 +8821,7 @@
           <t>I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -8860,6 +8960,7 @@
           <t>I-VOL-I-APPENDICES</t>
         </is>
       </c>
+      <c r="AC65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -9000,6 +9101,7 @@
           <t>I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
@@ -9140,6 +9242,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
@@ -9276,6 +9379,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
@@ -9410,6 +9514,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AC69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -9544,6 +9649,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC70" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-QUOTED-PRICE [confirmed feeds_calculation] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -9678,6 +9788,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCIAL-MODEL [proposed depends_on] from calc:availability-payment; -&gt; REL-MODEL-FORM-4F [confirmed feeds_calculation] to VOL-IV-F4F-02</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -9812,6 +9927,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AC72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
@@ -9946,6 +10062,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -10080,6 +10197,7 @@
         </is>
       </c>
       <c r="AB74" s="4" t="inlineStr"/>
+      <c r="AC74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -10214,6 +10332,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -10348,6 +10467,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FINANCING-ASSUMPTIONS [possible depends_on] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="inlineStr">
@@ -10482,6 +10606,7 @@
         </is>
       </c>
       <c r="AB77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="4" t="inlineStr">
@@ -10612,6 +10737,7 @@
         </is>
       </c>
       <c r="AB78" s="4" t="inlineStr"/>
+      <c r="AC78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="4" t="inlineStr">
@@ -10742,6 +10868,7 @@
         </is>
       </c>
       <c r="AB79" s="4" t="inlineStr"/>
+      <c r="AC79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="inlineStr">
@@ -10872,6 +10999,7 @@
         </is>
       </c>
       <c r="AB80" s="4" t="inlineStr"/>
+      <c r="AC80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="4" t="inlineStr">
@@ -11002,6 +11130,7 @@
         </is>
       </c>
       <c r="AB81" s="4" t="inlineStr"/>
+      <c r="AC81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -11140,6 +11269,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
@@ -11274,6 +11404,7 @@
         </is>
       </c>
       <c r="AB83" s="4" t="inlineStr"/>
+      <c r="AC83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="4" t="inlineStr">
@@ -11416,6 +11547,7 @@
           <t>I-VOL-I-BOND-LONGSTOP</t>
         </is>
       </c>
+      <c r="AC84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="4" t="inlineStr">
@@ -11546,6 +11678,7 @@
         </is>
       </c>
       <c r="AB85" s="4" t="inlineStr"/>
+      <c r="AC85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="4" t="inlineStr">
@@ -11680,6 +11813,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="4" t="inlineStr">
@@ -11814,6 +11948,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -11944,6 +12079,7 @@
         </is>
       </c>
       <c r="AB88" s="4" t="inlineStr"/>
+      <c r="AC88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="4" t="inlineStr">
@@ -12078,6 +12214,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AC89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="4" t="inlineStr">
@@ -12208,6 +12345,7 @@
         </is>
       </c>
       <c r="AB90" s="4" t="inlineStr"/>
+      <c r="AC90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="4" t="inlineStr">
@@ -12350,6 +12488,7 @@
         </is>
       </c>
       <c r="AB91" s="4" t="inlineStr"/>
+      <c r="AC91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="inlineStr">
@@ -12480,6 +12619,7 @@
         </is>
       </c>
       <c r="AB92" s="4" t="inlineStr"/>
+      <c r="AC92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
@@ -12610,6 +12750,7 @@
         </is>
       </c>
       <c r="AB93" s="4" t="inlineStr"/>
+      <c r="AC93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -12740,6 +12881,7 @@
         </is>
       </c>
       <c r="AB94" s="4" t="inlineStr"/>
+      <c r="AC94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
@@ -12876,6 +13018,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AC95" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="inlineStr">
@@ -13014,6 +13161,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AC96" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="inlineStr">
@@ -13148,6 +13300,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC97" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="inlineStr">
@@ -13282,6 +13439,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC98" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -13416,6 +13578,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC99" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -13550,6 +13717,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC100" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="inlineStr">
@@ -13684,6 +13856,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC101" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="inlineStr">
@@ -13818,6 +13995,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC102" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="inlineStr">
@@ -13952,6 +14134,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AC103" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -14086,6 +14273,11 @@
           <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AC104" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
@@ -14220,6 +14412,11 @@
           <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
+      <c r="AC105" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="inlineStr">
@@ -14352,6 +14549,11 @@
       <c r="AB106" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT; I-READING-T24</t>
+        </is>
+      </c>
+      <c r="AC106" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: the Environmental Permit issued for the site (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): cannot be established: that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
     </row>
@@ -14502,6 +14704,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AC107" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-PROCESS-DESIGN [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-PROCESS-DESIGN</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -14632,6 +14839,7 @@
         </is>
       </c>
       <c r="AB108" s="4" t="inlineStr"/>
+      <c r="AC108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="4" t="inlineStr">
@@ -14762,6 +14970,7 @@
         </is>
       </c>
       <c r="AB109" s="4" t="inlineStr"/>
+      <c r="AC109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -14896,6 +15105,7 @@
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
+      <c r="AC110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="4" t="inlineStr">
@@ -15026,6 +15236,7 @@
         </is>
       </c>
       <c r="AB111" s="4" t="inlineStr"/>
+      <c r="AC111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="4" t="inlineStr">
@@ -15156,6 +15367,7 @@
         </is>
       </c>
       <c r="AB112" s="4" t="inlineStr"/>
+      <c r="AC112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="4" t="inlineStr">
@@ -15290,6 +15502,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="4" t="inlineStr">
@@ -15424,6 +15637,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="4" t="inlineStr">
@@ -15558,6 +15772,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="4" t="inlineStr">
@@ -15688,6 +15903,7 @@
         </is>
       </c>
       <c r="AB116" s="4" t="inlineStr"/>
+      <c r="AC116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="4" t="inlineStr">
@@ -15822,6 +16038,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="4" t="inlineStr">
@@ -15952,6 +16169,7 @@
         </is>
       </c>
       <c r="AB118" s="4" t="inlineStr"/>
+      <c r="AC118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="4" t="inlineStr">
@@ -16082,6 +16300,7 @@
         </is>
       </c>
       <c r="AB119" s="4" t="inlineStr"/>
+      <c r="AC119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="4" t="inlineStr">
@@ -16216,6 +16435,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="4" t="inlineStr">
@@ -16346,6 +16566,7 @@
         </is>
       </c>
       <c r="AB121" s="4" t="inlineStr"/>
+      <c r="AC121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
@@ -16480,6 +16701,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AC122" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="inlineStr">
@@ -16610,6 +16836,7 @@
         </is>
       </c>
       <c r="AB123" s="4" t="inlineStr"/>
+      <c r="AC123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="4" t="inlineStr">
@@ -16740,6 +16967,7 @@
         </is>
       </c>
       <c r="AB124" s="4" t="inlineStr"/>
+      <c r="AC124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="4" t="inlineStr">
@@ -16874,6 +17102,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AC125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
@@ -17010,6 +17239,7 @@
           <t>I-FLOWS</t>
         </is>
       </c>
+      <c r="AC126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="4" t="inlineStr">
@@ -17144,6 +17374,7 @@
           <t>I-VOL-III</t>
         </is>
       </c>
+      <c r="AC127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="4" t="inlineStr">
@@ -17274,6 +17505,7 @@
         </is>
       </c>
       <c r="AB128" s="4" t="inlineStr"/>
+      <c r="AC128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="4" t="inlineStr">
@@ -17404,6 +17636,7 @@
         </is>
       </c>
       <c r="AB129" s="4" t="inlineStr"/>
+      <c r="AC129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="inlineStr">
@@ -17538,6 +17771,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AC130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="4" t="inlineStr">
@@ -17668,6 +17902,7 @@
         </is>
       </c>
       <c r="AB131" s="4" t="inlineStr"/>
+      <c r="AC131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="4" t="inlineStr">
@@ -17798,6 +18033,7 @@
         </is>
       </c>
       <c r="AB132" s="4" t="inlineStr"/>
+      <c r="AC132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="4" t="inlineStr">
@@ -17928,6 +18164,7 @@
         </is>
       </c>
       <c r="AB133" s="4" t="inlineStr"/>
+      <c r="AC133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="4" t="inlineStr">
@@ -18058,6 +18295,7 @@
         </is>
       </c>
       <c r="AB134" s="4" t="inlineStr"/>
+      <c r="AC134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="4" t="inlineStr">
@@ -18188,6 +18426,7 @@
         </is>
       </c>
       <c r="AB135" s="4" t="inlineStr"/>
+      <c r="AC135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -18318,6 +18557,7 @@
         </is>
       </c>
       <c r="AB136" s="4" t="inlineStr"/>
+      <c r="AC136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="4" t="inlineStr">
@@ -18448,6 +18688,7 @@
         </is>
       </c>
       <c r="AB137" s="4" t="inlineStr"/>
+      <c r="AC137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="4" t="inlineStr">
@@ -18582,6 +18823,7 @@
         </is>
       </c>
       <c r="AB138" s="4" t="inlineStr"/>
+      <c r="AC138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="4" t="inlineStr">
@@ -18712,6 +18954,7 @@
         </is>
       </c>
       <c r="AB139" s="4" t="inlineStr"/>
+      <c r="AC139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="4" t="inlineStr">
@@ -18842,6 +19085,7 @@
         </is>
       </c>
       <c r="AB140" s="4" t="inlineStr"/>
+      <c r="AC140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="4" t="inlineStr">
@@ -18972,6 +19216,7 @@
         </is>
       </c>
       <c r="AB141" s="4" t="inlineStr"/>
+      <c r="AC141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="4" t="inlineStr">
@@ -19110,6 +19355,11 @@
           <t>I-READING-T24; I-PERMIT</t>
         </is>
       </c>
+      <c r="AC142" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RELIABILITY-RUN [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RELIABILITY-RUN</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="inlineStr">
@@ -19248,6 +19498,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AC143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="4" t="inlineStr">
@@ -19378,6 +19629,7 @@
         </is>
       </c>
       <c r="AB144" s="4" t="inlineStr"/>
+      <c r="AC144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
@@ -19512,6 +19764,7 @@
         </is>
       </c>
       <c r="AB145" s="4" t="inlineStr"/>
+      <c r="AC145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="4" t="inlineStr">
@@ -19642,6 +19895,7 @@
         </is>
       </c>
       <c r="AB146" s="4" t="inlineStr"/>
+      <c r="AC146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="4" t="inlineStr">
@@ -19772,6 +20026,7 @@
         </is>
       </c>
       <c r="AB147" s="4" t="inlineStr"/>
+      <c r="AC147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -19902,6 +20157,7 @@
         </is>
       </c>
       <c r="AB148" s="4" t="inlineStr"/>
+      <c r="AC148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="4" t="inlineStr">
@@ -20032,6 +20288,7 @@
         </is>
       </c>
       <c r="AB149" s="4" t="inlineStr"/>
+      <c r="AC149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="4" t="inlineStr">
@@ -20170,6 +20427,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="4" t="inlineStr">
@@ -20308,6 +20566,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="inlineStr">
@@ -20442,6 +20701,7 @@
           <t>I-VOL-II-MISSING</t>
         </is>
       </c>
+      <c r="AC152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="4" t="inlineStr">
@@ -20572,6 +20832,7 @@
         </is>
       </c>
       <c r="AB153" s="4" t="inlineStr"/>
+      <c r="AC153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -20706,6 +20967,7 @@
         </is>
       </c>
       <c r="AB154" s="4" t="inlineStr"/>
+      <c r="AC154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="4" t="inlineStr">
@@ -20840,6 +21102,7 @@
         </is>
       </c>
       <c r="AB155" s="4" t="inlineStr"/>
+      <c r="AC155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="inlineStr">
@@ -20970,6 +21233,7 @@
         </is>
       </c>
       <c r="AB156" s="4" t="inlineStr"/>
+      <c r="AC156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="4" t="inlineStr">
@@ -21100,6 +21364,7 @@
         </is>
       </c>
       <c r="AB157" s="4" t="inlineStr"/>
+      <c r="AC157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="4" t="inlineStr">
@@ -21238,6 +21503,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AC158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="4" t="inlineStr">
@@ -21406,6 +21672,7 @@
           <t>I-F4A-FIELDS</t>
         </is>
       </c>
+      <c r="AC159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="4" t="inlineStr">
@@ -21540,6 +21807,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="4" t="inlineStr">
@@ -21678,6 +21946,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="4" t="inlineStr">
@@ -21812,6 +22081,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="4" t="inlineStr">
@@ -21946,6 +22216,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="4" t="inlineStr">
@@ -22080,6 +22351,7 @@
           <t>I-F4A-FIELDS; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="4" t="inlineStr">
@@ -22244,6 +22516,7 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-A-PRICES; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="4" t="inlineStr">
@@ -22378,6 +22651,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="4" t="inlineStr">
@@ -22512,6 +22786,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC167" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-MULTIPLE-PARTICIPATION [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="inlineStr">
@@ -22646,6 +22925,11 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE; I-BIDDER-FACTS</t>
         </is>
       </c>
+      <c r="AC168" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MEMBER-DEBARMENT [confirmed member_scope] from VOL-I:8.1, words:member of the Bidder, words:consortium member, words:member of the consortium</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="inlineStr">
@@ -22780,6 +23064,7 @@
           <t>I-READING-F4C; I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="4" t="inlineStr">
@@ -22936,6 +23221,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="4" t="inlineStr">
@@ -23066,6 +23352,7 @@
         </is>
       </c>
       <c r="AB171" s="4" t="inlineStr"/>
+      <c r="AC171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="inlineStr">
@@ -23196,6 +23483,7 @@
         </is>
       </c>
       <c r="AB172" s="4" t="inlineStr"/>
+      <c r="AC172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="4" t="inlineStr">
@@ -23326,6 +23614,7 @@
         </is>
       </c>
       <c r="AB173" s="4" t="inlineStr"/>
+      <c r="AC173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="inlineStr">
@@ -23456,6 +23745,7 @@
         </is>
       </c>
       <c r="AB174" s="4" t="inlineStr"/>
+      <c r="AC174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="inlineStr">
@@ -23586,6 +23876,7 @@
         </is>
       </c>
       <c r="AB175" s="4" t="inlineStr"/>
+      <c r="AC175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="inlineStr">
@@ -23716,6 +24007,7 @@
         </is>
       </c>
       <c r="AB176" s="4" t="inlineStr"/>
+      <c r="AC176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="4" t="inlineStr">
@@ -23846,6 +24138,7 @@
         </is>
       </c>
       <c r="AB177" s="4" t="inlineStr"/>
+      <c r="AC177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="4" t="inlineStr">
@@ -23998,6 +24291,7 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -24162,6 +24456,11 @@
           <t>I-NO-CONSEQUENCE; I-VOL-I-ENV-B</t>
         </is>
       </c>
+      <c r="AC179" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-PAY-FORM-4F [confirmed feeds_calculation] from calc:availability-payment</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="inlineStr">
@@ -24296,6 +24595,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
+      <c r="AC180" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-MODEL-FORM-4F [confirmed feeds_calculation] from VOL-I-10.3-01</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="inlineStr">
@@ -24434,6 +24738,7 @@
           <t>I-VOL-V-MISSING; I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="4" t="inlineStr">
@@ -24572,6 +24877,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="4" t="inlineStr">
@@ -24706,6 +25012,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="4" t="inlineStr">
@@ -24844,6 +25151,7 @@
         </is>
       </c>
       <c r="AB184" s="4" t="inlineStr"/>
+      <c r="AC184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="4" t="inlineStr">
@@ -24982,6 +25290,7 @@
         </is>
       </c>
       <c r="AB185" s="4" t="inlineStr"/>
+      <c r="AC185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="4" t="inlineStr">
@@ -25112,6 +25421,7 @@
         </is>
       </c>
       <c r="AB186" s="4" t="inlineStr"/>
+      <c r="AC186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="4" t="inlineStr">
@@ -25242,6 +25552,7 @@
         </is>
       </c>
       <c r="AB187" s="4" t="inlineStr"/>
+      <c r="AC187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="4" t="inlineStr">
@@ -25372,6 +25683,7 @@
         </is>
       </c>
       <c r="AB188" s="4" t="inlineStr"/>
+      <c r="AC188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="4" t="inlineStr">
@@ -25502,6 +25814,7 @@
         </is>
       </c>
       <c r="AB189" s="4" t="inlineStr"/>
+      <c r="AC189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="4" t="inlineStr">
@@ -25632,6 +25945,7 @@
         </is>
       </c>
       <c r="AB190" s="4" t="inlineStr"/>
+      <c r="AC190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="4" t="inlineStr">
@@ -25762,6 +26076,7 @@
         </is>
       </c>
       <c r="AB191" s="4" t="inlineStr"/>
+      <c r="AC191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="inlineStr">
@@ -25892,6 +26207,7 @@
         </is>
       </c>
       <c r="AB192" s="4" t="inlineStr"/>
+      <c r="AC192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="4" t="inlineStr">
@@ -26022,6 +26338,7 @@
         </is>
       </c>
       <c r="AB193" s="4" t="inlineStr"/>
+      <c r="AC193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="inlineStr">
@@ -26170,6 +26487,11 @@
           <t>I-READING-T24</t>
         </is>
       </c>
+      <c r="AC194" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-RAMP-UP-DEDUCTIONS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RAMP-UP-DEDUCTIONS</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="inlineStr">
@@ -26304,6 +26626,7 @@
         </is>
       </c>
       <c r="AB195" s="4" t="inlineStr"/>
+      <c r="AC195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="inlineStr">
@@ -26442,6 +26765,11 @@
           <t>I-VOL-V-MISSING; I-FLOWS</t>
         </is>
       </c>
+      <c r="AC196" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="4" t="inlineStr">
@@ -26580,6 +26908,11 @@
           <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING</t>
         </is>
       </c>
+      <c r="AC197" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-T24-UNAVAILABILITY [confirmed limit_applies] from VOL-II:T2-4; NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-UNAVAILABILITY</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="inlineStr">
@@ -26716,6 +27049,11 @@
       <c r="AB198" s="4" t="inlineStr">
         <is>
           <t>I-VOL-III; I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AC198" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 7 (deductions) (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): cannot be established: the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
         </is>
       </c>
     </row>
@@ -26848,6 +27186,7 @@
         </is>
       </c>
       <c r="AB199" s="4" t="inlineStr"/>
+      <c r="AC199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="4" t="inlineStr">
@@ -26978,6 +27317,7 @@
         </is>
       </c>
       <c r="AB200" s="4" t="inlineStr"/>
+      <c r="AC200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="4" t="inlineStr">
@@ -27116,6 +27456,11 @@
           <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
+      <c r="AC201" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): cannot be established: whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="inlineStr">
@@ -27254,6 +27599,7 @@
         </is>
       </c>
       <c r="AB202" s="4" t="inlineStr"/>
+      <c r="AC202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="4" t="inlineStr">
@@ -27384,6 +27730,7 @@
         </is>
       </c>
       <c r="AB203" s="4" t="inlineStr"/>
+      <c r="AC203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="4" t="inlineStr">
@@ -27520,6 +27867,11 @@
       <c r="AB204" s="4" t="inlineStr">
         <is>
           <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="AC204" s="4" t="inlineStr">
+        <is>
+          <t>NOT SUPPLIED: Volume V Schedule 11 (Project Company Events of Default) (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): cannot be established: which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
         </is>
       </c>
     </row>
@@ -27656,6 +28008,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="4" t="inlineStr">
@@ -27786,6 +28139,7 @@
         </is>
       </c>
       <c r="AB206" s="4" t="inlineStr"/>
+      <c r="AC206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="4" t="inlineStr">
@@ -27924,6 +28278,7 @@
           <t>I-CONCESSION</t>
         </is>
       </c>
+      <c r="AC207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="4" t="inlineStr">
@@ -28054,6 +28409,7 @@
         </is>
       </c>
       <c r="AB208" s="4" t="inlineStr"/>
+      <c r="AC208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="4" t="inlineStr">
@@ -28184,9 +28540,10 @@
         </is>
       </c>
       <c r="AB209" s="4" t="inlineStr"/>
+      <c r="AC209" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB209"/>
+  <autoFilter ref="A4:AC209"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -32188,7 +32545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -32986,94 +33343,106 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+        </is>
+      </c>
       <c r="F27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr"/>
@@ -33082,12 +33451,12 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -33106,12 +33475,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -33130,12 +33499,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -33154,12 +33523,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -33178,12 +33547,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -33193,7 +33562,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr"/>
@@ -33202,12 +33571,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -33217,7 +33586,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -33226,12 +33595,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -33241,7 +33610,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr"/>
@@ -33250,101 +33619,89 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [understated] 'responds to clarification requests 1 to 6', but ADD-01/Q4 adds an obligation (ADD-01:Q4): 'The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.'; [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
       <c r="F37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
       <c r="F38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr"/>
       <c r="F39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -33354,7 +33711,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr"/>
@@ -33362,12 +33719,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -33382,7 +33739,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -33390,17 +33747,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -33410,7 +33767,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -33418,12 +33775,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -33446,33 +33803,117 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>I-A5-copies</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-seal-and-mark</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-deliver</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; lcc-certificate INFEASIBLE by 12 WD; assemble-envelope-a INFEASIBLE by 12 WD; copies INFEASIBLE by 12 WD; seal-and-mark INFEASIBLE by 12 WD; deliver INFEASIBLE by 12 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D47" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
+      <c r="E47" s="4" t="inlineStr">
         <is>
           <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F44"/>
+  <autoFilter ref="A1:F47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36388,4 +36829,1487 @@
   <autoFilter ref="A1:E47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Id</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Kind</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Document</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Blocks</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Issues</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Reached</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FIN-STANDING</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr"/>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-FORM-4C</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-MULTIPLE-PARTICIPATION</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr"/>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-DEBARMENT</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr"/>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>REL-MEMBER-INVESTMENT-LICENCE</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>member_scope</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-8.9-01</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>I-BIDDER-FACTS</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-PROCESS-DESIGN</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-3.1-01</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RELIABILITY-RUN</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-7.2-01</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-UNAVAILABILITY</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-02</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-RAMP-UP-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-29.3-01</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>limit_applies</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:T2-4</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-MECHANISM</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-QUOTED-PRICE</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.2-01</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr"/>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-01</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr"/>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCIAL-MODEL</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>REL-MODEL-FORM-4F</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>feeds_calculation</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4F-02</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>possible</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>possible impact</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-10.6-01</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-39.1-01</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V:39.3</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 7 (deductions)</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>the Environmental Permit issued for the site</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>I-PERMIT</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O23"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AF$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$48</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Evidence'!$A$1:$F$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Relationships'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Relationships'!$A$2:$O$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,7 +103,9 @@
   <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -534,10 +536,10 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="210" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 37). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. Evidence codes are defined in the Evidence sheet.</t>
+          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 37). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none; approved by the owner: VOL-II-p3-r1 (transcription), VOL-IV-p6-r1 (transcription and displayed translations); their interpretations stay proposed. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. In 'Text as issued', a segment marked '[&lt;document&gt; &lt;clause&gt; p&lt;n&gt;; issued by ADD-0x]' is that addendum's own text, not text of the volumes as issued. Evidence codes are defined in the Evidence sheet. Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
         </is>
       </c>
     </row>
@@ -736,12 +738,12 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>not later than 14:00 hours Riyadh time on Thursday 26 November 2026</t>
+          <t>Thursday 26 November 2026</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 6.1 p3 as amended by ADD-01 2.1 p1</t>
+          <t>ADD-01 2.1 p1 (amending VOL-I 6.1)</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -801,12 +803,12 @@
       </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 6.1 p3 as amended by ADD-01 2.1 p1</t>
+          <t>ADD-01 2.1 p1 (amending VOL-I 6.1)</t>
         </is>
       </c>
       <c r="U5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 6.1 p3 as amended by ADD-01 2.1 p1</t>
+          <t>ADD-01 2.1 p1 (amending VOL-I 6.1)</t>
         </is>
       </c>
       <c r="V5" s="4" t="inlineStr">
@@ -1933,7 +1935,7 @@
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>[VOL-I 8.6 p4] The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) for the construction phase.
-[ADD-01 4.2 p1; issued by ADD-01] (not in the volumes as issued)</t>
+[ADD-01 4.2 p1; issued by ADD-01] Consequentially, any reference to a Local Content Certificate elsewhere in the RFP Documents shall be disregarded.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -2234,7 +2236,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.</t>
+          <t>[ADD-01 3.1 p1; issued by ADD-01] The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -2758,7 +2760,7 @@
       <c r="X18" s="4" t="inlineStr"/>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>high: text-layer clause; the form itself is an image (transcription confirmed by the owner, 3 Oct 2026)</t>
+          <t>high: text-layer clause; the form itself is an image (transcription and displayed translations confirmed by the owner, 3 Oct 2026)</t>
         </is>
       </c>
       <c r="Z18" s="4" t="inlineStr">
@@ -2912,7 +2914,7 @@
       <c r="X19" s="4" t="inlineStr"/>
       <c r="Y19" s="4" t="inlineStr">
         <is>
-          <t>medium: from an image reading (transcription confirmed by the owner, 3 Oct 2026); Arabic-only consequence whose category is unresolved</t>
+          <t>medium: from an image reading (transcription and displayed translations confirmed by the owner, 3 Oct 2026); Arabic-only consequence whose category is unresolved</t>
         </is>
       </c>
       <c r="Z19" s="4" t="inlineStr">
@@ -3062,7 +3064,7 @@
       <c r="X20" s="4" t="inlineStr"/>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>medium: from an image reading (transcription confirmed by the owner, 3 Oct 2026)</t>
+          <t>medium: from an image reading (transcription and displayed translations confirmed by the owner, 3 Oct 2026)</t>
         </is>
       </c>
       <c r="Z20" s="4" t="inlineStr">
@@ -3124,8 +3126,8 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>[ADD-02 7.2 p3; issued by ADD-02] (not in the volumes as issued)
-[ADD-02 p3 (inserted after VOL-I 9.1(e), p4)] (not in the volumes as issued)</t>
+          <t>[ADD-02 7.2 p3; issued by ADD-02] Form 4-G shall be completed and submitted with Envelope A. Failure to submit Form 4-G shall render the Proposal non-responsive.
+[ADD-02 p3 (inserted after VOL-I 9.1(e), p4)] FORM 4-G — CYBERSECURITY COMPLIANCE UNDERTAKING</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -3187,7 +3189,7 @@
       <c r="Q21" s="4" t="inlineStr"/>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>status NOT ISSUED -&gt; NEW. reading re-made at ADD-02. by ADD-02/7.1 [ADD-02; proposed] &lt;- ADD-02:7.1 (ADD-02 p3)</t>
+          <t>status NOT ISSUED -&gt; NEW. reading re-made at ADD-02: ADD-02 7.1 adds Form 4-G 'to Volume IV and to the list at Volume I Clause 9.1'; it prints no entry for the Index of Forms (VOL-IV p2, which lists Forms 4-A to 4-F), so no index row is inserted, and where the form sits in Volume IV is not stated. by ADD-02/7.1 [ADD-02; proposed] &lt;- ADD-02:7.1 (ADD-02 p3)</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr"/>
@@ -3213,7 +3215,11 @@
           <t>high: verbatim; the re-lettering of the Envelope A list after item (e) is not stated</t>
         </is>
       </c>
-      <c r="Z21" s="4" t="inlineStr"/>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02 7.1 adds Form 4-G 'to Volume IV and to the list at Volume I Clause 9.1'; it prints no entry for the Index of Forms (VOL-IV p2, which lists Forms 4-A to 4-F), so no index row is inserted, and where the form sits in Volume IV is not stated.</t>
+        </is>
+      </c>
       <c r="AA21" s="4" t="inlineStr">
         <is>
           <t>n/a (text layer)</t>
@@ -3264,7 +3270,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Item: 3 | Undertaking: A named accountable security officer will be appointed for the concession period. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/3 p3; issued by ADD-02] Item: 3 | Undertaking: A named accountable security officer will be appointed for the concession period. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -3402,7 +3408,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Item: 4 | Undertaking: Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/4 p3; issued by ADD-02] Item: 4 | Undertaking: Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -3540,7 +3546,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Item: 5 | Undertaking: An independent penetration test of the operational technology environment will be carried out annually and the report provided to the Authority. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/5 p3; issued by ADD-02] Item: 5 | Undertaking: An independent penetration test of the operational technology environment will be carried out annually and the report provided to the Authority. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -3678,7 +3684,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Item: 6 | Undertaking: Remote access to the control system will require multi-factor authentication and will be logged. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/6 p3; issued by ADD-02] Item: 6 | Undertaking: Remote access to the control system will require multi-factor authentication and will be logged. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -3826,12 +3832,12 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>for not less than ninety-six (96) hours</t>
+          <t>ninety-six (96) hours</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>VOL-II 4.4 p4 as amended by ADD-02 4.1 p1</t>
+          <t>ADD-02 4.1 p1 (amending VOL-II 4.4)</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -3892,7 +3898,7 @@
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>VOL-II 4.4 p4 as amended by ADD-02 4.1 p1</t>
+          <t>ADD-02 4.1 p1 (amending VOL-II 4.4)</t>
         </is>
       </c>
       <c r="V26" s="4" t="inlineStr">
@@ -4956,10 +4962,10 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>[ADD-01 cover/para3 p1; issued by ADD-01] (not in the volumes as issued)
-[ADD-01 AppA/addenda-acknowledged-numbers p3; issued by ADD-01] (not in the volumes as issued)
-[ADD-01 AppA/para1 p3; issued by ADD-01] (not in the volumes as issued)
-[ADD-02 cover/para3 p1; issued by ADD-02] (not in the volumes as issued)</t>
+          <t>[ADD-01 cover/para3 p1; issued by ADD-01] This Addendum amends the Proposal Due Date, deletes one qualification requirement, amends Volume II Clause 5.3, publishes the minutes of the Pre-Bid Conference, and responds to clarification requests 1 to 6. This Addendum forms part of the RFP Documents and takes precedence in accordance with Volume I Clause 3.2. Bidders shall acknowledge receipt in Form 4-A. All other terms of the RFP Documents remain unchanged.
+[ADD-01 AppA/addenda-acknowledged-numbers p3; issued by ADD-01] Addenda acknowledged (numbers):
+[ADD-01 AppA/para1 p3; issued by ADD-01] Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.
+[ADD-02 cover/para3 p1; issued by ADD-02] This Addendum amends the page limit, reissues the technical evaluation table, amends Volume II Clauses 4.4 and Table 2-4, adds Form 4-G, amends Volume V Clause 36.2, reinstates Volume I Clause 8.6, and responds to clarification requests 7 to 14. This Addendum forms part of the RFP Documents and takes precedence in accordance with Volume I Clause 3.2. Bidders shall acknowledge receipt in Form 4-A. All other terms of the RFP Documents remain unchanged.</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -5108,7 +5114,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>No: 4 | Bidder question: Can the Authority confirm the ground conditions at the wadi crossing? | Authority response: The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.</t>
+          <t>[ADD-01 Q4 p2; issued by ADD-01] No: 4 | Bidder question: Can the Authority confirm the ground conditions at the wadi crossing? | Authority response: The geotechnical report in the data room is provided for information. Bidders shall satisfy themselves as to ground conditions.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -5254,8 +5260,8 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>[ADD-02 5.2 p1; issued by ADD-02] (not in the volumes as issued)
-[ADD-02 5.1 p1; issued by ADD-02] (not in the volumes as issued)</t>
+          <t>[ADD-02 5.2 p1; issued by ADD-02] Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.
+[ADD-02 5.1 p1; issued by ADD-02] In Volume II Table 2-4, the limit for Total Nitrogen (TN) is amended from the value shown to 3 mg/l, assessed on the same basis. All other parameters in Table 2-4 are unchanged.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -5281,7 +5287,7 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>pass_fail</t>
+          <t>scored</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
@@ -5336,7 +5342,7 @@
       <c r="X36" s="4" t="inlineStr"/>
       <c r="Y36" s="4" t="inlineStr">
         <is>
-          <t>medium: verbatim; the basis of assessment rests on the image reading (transcription confirmed by the owner, 3 Oct 2026) and the Permit is not supplied. Assessed pass_fail because the amended limit is a mandatory Volume II requirement the design must reflect; the quality of the process design is scored separately under Table 1-1 criterion A (VOL-I-T1-1-A)</t>
+          <t>medium: verbatim; the basis of assessment rests on the image reading (transcription confirmed by the owner, 3 Oct 2026) and the Permit is not supplied. An obligation with no consequence stated (I-NO-CONSEQUENCE): the pack states no rejection or non-responsiveness for a design that does not reflect the limit, and does not say whether the VOL-I 11.1(i) mandatory compliance check covers it; the process design it governs is marked under Table 1-1 criterion A 'Process design, treatment performance and compliance with Volume II' (25 marks, reissued by ADD-02 3.1; row VOL-I-T1-1-A), so it is classed scored, as VOL-II-3.1-01 is</t>
         </is>
       </c>
       <c r="Z36" s="4" t="inlineStr">
@@ -5366,7 +5372,7 @@
       </c>
       <c r="AE36" s="4" t="inlineStr">
         <is>
-          <t>I-NO-CONSEQUENCE; I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24</t>
         </is>
       </c>
       <c r="AF36" s="4" t="inlineStr"/>
@@ -5394,8 +5400,8 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>[ADD-02 T1-1-rev/note(3) p1; issued by ADD-02] (not in the volumes as issued)
-[ADD-02 T1-1-rev p1; issued by ADD-02] (not in the volumes as issued)</t>
+          <t>[ADD-02 T1-1-rev/note(3) p1; issued by ADD-02] (3)  Marks are awarded on the Authority's standard five-point scale and multiplied by the weight shown.
+[ADD-02 T1-1-rev p1; issued by ADD-02] Table 1-1 (revised) — Technical evaluation criteria — Ref | Criterion | Marks</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -5534,7 +5540,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Item: 1 | Undertaking: The operational technology environment will be segregated from any business network in accordance with Volume II Clause 6.2. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/1 p3; issued by ADD-02] Item: 1 | Undertaking: The operational technology environment will be segregated from any business network in accordance with Volume II Clause 6.2. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -5672,7 +5678,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Item: 2 | Undertaking: An information security management system covering the operational technology environment will be implemented before commissioning. | Confirmed: Yes / No</t>
+          <t>[ADD-02 F4-G/T1/2 p3; issued by ADD-02] Item: 2 | Undertaking: An information security management system covering the operational technology environment will be implemented before commissioning. | Confirmed: Yes / No</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -5810,7 +5816,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Signed for and on behalf of the Bidder: _______________________ Name: _______________________ Date: ____________</t>
+          <t>[ADD-02 F4-G/para1 p3; issued by ADD-02] Signed for and on behalf of the Bidder: _______________________ Name: _______________________ Date: ____________</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -9114,7 +9120,7 @@
 [VOL-I 9.1(c) p4] (c) Form 4-C — Conflict of Interest and Debarment Declaration;
 [VOL-I 9.1(d) p4] (d) Form 4-D — Parent Company Guarantee (executed);
 [VOL-I 9.1(e) p4] (e) Form 4-E — Schedule of Deviations;
-[ADD-02 p3 (inserted after VOL-I 9.1(e), p4); issued by ADD-02] (not in the volumes as issued)
+[ADD-02 p3 (inserted after VOL-I 9.1(e), p4); issued by ADD-02] FORM 4-G — CYBERSECURITY COMPLIANCE UNDERTAKING
 [VOL-I 9.1(f) p4] (f) the Technical Proposal narrative;
 [VOL-I 9.1(g) p4] (g) the Bid Bond;
 [VOL-I 9.1(h) p4] (h) notarised Powers of Attorney for each signatory;
@@ -9189,7 +9195,7 @@
       <c r="Q63" s="4" t="inlineStr"/>
       <c r="R63" s="4" t="inlineStr">
         <is>
-          <t>status ACTIVE -&gt; AMENDED (ADD-02/7.1). reading re-made at ADD-02: ADD-02 §7.1 inserts Form 4-G after item (e) (row ADD-02-7.2-01); the re-lettering of the later items is not stated. by ADD-02/7.1 [ADD-02; proposed] &lt;- ADD-02:7.1 (ADD-02 p3)</t>
+          <t>status ACTIVE -&gt; AMENDED (ADD-02/7.1). reading re-made at ADD-02: ADD-02 §7.1 inserts Form 4-G after item (e) (row ADD-02-7.2-01); the re-lettering of the later items is not stated. Item (i), 'the certificates and evidence required under Section 8', again includes the Local Content Certificate: ADD-01 4.1 deleted VOL-I 8.6 (the certificate left this list at ADD-01) and ADD-02 9.1 reinstates it at 35% (row VOL-I-8.6-01). by ADD-02/7.1 [ADD-02; proposed] &lt;- ADD-02:7.1 (ADD-02 p3)</t>
         </is>
       </c>
       <c r="S63" s="4" t="inlineStr">
@@ -9221,7 +9227,7 @@
       </c>
       <c r="Z63" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 §7.1 inserts Form 4-G after item (e) (row ADD-02-7.2-01); the re-lettering of the later items is not stated.</t>
+          <t>ADD-02 §7.1 inserts Form 4-G after item (e) (row ADD-02-7.2-01); the re-lettering of the later items is not stated. Item (i), 'the certificates and evidence required under Section 8', again includes the Local Content Certificate: ADD-01 4.1 deleted VOL-I 8.6 (the certificate left this list at ADD-01) and ADD-02 9.1 reinstates it at 35% (row VOL-I-8.6-01).</t>
         </is>
       </c>
       <c r="AA63" s="4" t="inlineStr">
@@ -9426,12 +9432,12 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>The Technical Proposal narrative shall not exceed one hundred and fifty (150) pages of A4, excluding the Form Sheets and the appendices expressly permitted by Volume II.</t>
+          <t>one hundred and fifty (150) pages</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 9.2 p5 as amended by ADD-02 2.1 p1</t>
+          <t>ADD-02 2.1 p1 (amending VOL-I 9.2)</t>
         </is>
       </c>
       <c r="I65" s="4" t="inlineStr">
@@ -9481,7 +9487,7 @@
       </c>
       <c r="R65" s="4" t="inlineStr">
         <is>
-          <t>status ACTIVE -&gt; AMENDED (ADD-02/2.1). reading re-made at ADD-02: ADD-02 §2.1 raises the limit from 120 to 150 pages. ADD-01 Q2's '120-page limit' wording is now stale; its substance (forms excluded) still holds. by ADD-02/2.1 [ADD-02; proposed] &lt;- ADD-02:2.1 (ADD-02 p1)</t>
+          <t>status ACTIVE -&gt; AMENDED (ADD-02/2.1). reading re-made at ADD-02: ADD-02 §2.1 raises the limit from 120 to 150 pages; the clause as amended still prints 'excluding the Form Sheets and the appendices expressly permitted by Volume II'. ADD-01 Q2 answered about the '120-page limit': whether that answer still holds after ADD-02 2.1 is listed for review in A2 (a decision for a person; none recorded). by ADD-02/2.1 [ADD-02; proposed] &lt;- ADD-02:2.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="S65" s="4" t="inlineStr">
@@ -9496,7 +9502,7 @@
       </c>
       <c r="U65" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 9.2 p5 as amended by ADD-02 2.1 p1</t>
+          <t>ADD-02 2.1 p1 (amending VOL-I 9.2)</t>
         </is>
       </c>
       <c r="V65" s="4" t="inlineStr">
@@ -9517,7 +9523,7 @@
       </c>
       <c r="Z65" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 §2.1 raises the limit from 120 to 150 pages. ADD-01 Q2's '120-page limit' wording is now stale; its substance (forms excluded) still holds.</t>
+          <t>ADD-02 §2.1 raises the limit from 120 to 150 pages; the clause as amended still prints 'excluding the Form Sheets and the appendices expressly permitted by Volume II'. ADD-01 Q2 answered about the '120-page limit': whether that answer still holds after ADD-02 2.1 is listed for review in A2 (a decision for a person; none recorded).</t>
         </is>
       </c>
       <c r="AA65" s="4" t="inlineStr">
@@ -10409,7 +10415,7 @@
       </c>
       <c r="AF71" s="4" t="inlineStr">
         <is>
-          <t>&lt;- REL-PAY-FINANCIAL-MODEL [proposed depends_on] from calc:availability-payment; -&gt; REL-MODEL-FORM-4F [confirmed feeds_calculation] to VOL-IV-F4F-02</t>
+          <t>&lt;- REL-PAY-FINANCIAL-MODEL [proposed depends_on] from calc:availability-payment; -&gt; REL-MODEL-FORM-4F [confirmed feeds_calculation] to VOL-IV-F4F-02; &lt;- REL-CHANGE-IN-LAW-FINANCIAL-MODEL [possible depends_on] from VOL-V:36.2; REACHED at ADD-02 (possible impact): from VOL-V:36.2 via REL-CHANGE-IN-LAW-FINANCIAL-MODEL</t>
         </is>
       </c>
     </row>
@@ -11921,7 +11927,7 @@
       <c r="Q82" s="4" t="inlineStr"/>
       <c r="R82" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-02: ADD-02 Q7 (p2): 'The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' VOL-I 3.2 (p2) ranks '(b) Volume I (Instructions to Bidders)' above '(c) Volume V (Draft Project Agreement)', so this clause prevails over VOL-V 3.1 for the RFP Documents: the concession runs 25 years from PCOD. VOL-V 3.1 is left unamended; what to record in Form 4-E and which term start the Financial Model assumes stay for Legal (I-CONCESSION, CQ-CONCESSION-TERM). Confidence medium, not lower than VOL-V-3.1-01: this is the clause that prevails (session 11 audit A1-3, PROPOSED). by ADD-02/Q7 [ADD-02; proposed; annotates VOL-I:12.1 (confirms)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
+          <t>reading re-made at ADD-02: ADD-02 Q7 (p2) was asked 'Which applies?' and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither. Two readings: this clause, 'twenty-five (25) years commencing on the Project Commercial Operation Date'; VOL-V 3.1 (p2), 'twenty-five (25) years from the Effective Date' (row VOL-V-3.1-01). VOL-I 3.2 (p2) orders the RFP Documents '(a) the Addenda, a later Addendum prevailing over an earlier one;' '(b) Volume I (Instructions to Bidders);' '(c) Volume V (Draft Project Agreement);' 'the first named prevailing'; VOL-I 3.3 (p2): 'A Bidder that resolves such a conflict unilaterally does so at its own risk'. Which clause governs the term, what to record in Form 4-E and which term start the Financial Model assumes are a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded. by ADD-02/Q7 [ADD-02; proposed; annotates VOL-I:12.1 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="S82" s="4" t="inlineStr">
@@ -11952,12 +11958,12 @@
       </c>
       <c r="Y82" s="4" t="inlineStr">
         <is>
-          <t>medium: verbatim; prevails over VOL-V 3.1 under VOL-I 3.2 as ADD-02 Q7 directs; VOL-V 3.1 left unamended, so what to record in Form 4-E and the Financial Model is open for Legal (I-CONCESSION)</t>
+          <t>medium: verbatim; conflicts with VOL-V 3.1 (from the Effective Date); ADD-02 Q7 refers to the order of precedence at VOL-I 3.2 without saying which clause applies; which clause governs is a decision for a person (Legal, I-CONCESSION); no decision recorded</t>
         </is>
       </c>
       <c r="Z82" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 Q7 (p2): 'The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' VOL-I 3.2 (p2) ranks '(b) Volume I (Instructions to Bidders)' above '(c) Volume V (Draft Project Agreement)', so this clause prevails over VOL-V 3.1 for the RFP Documents: the concession runs 25 years from PCOD. VOL-V 3.1 is left unamended; what to record in Form 4-E and which term start the Financial Model assumes stay for Legal (I-CONCESSION, CQ-CONCESSION-TERM). Confidence medium, not lower than VOL-V-3.1-01: this is the clause that prevails (session 11 audit A1-3, PROPOSED).</t>
+          <t>ADD-02 Q7 (p2) was asked 'Which applies?' and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither. Two readings: this clause, 'twenty-five (25) years commencing on the Project Commercial Operation Date'; VOL-V 3.1 (p2), 'twenty-five (25) years from the Effective Date' (row VOL-V-3.1-01). VOL-I 3.2 (p2) orders the RFP Documents '(a) the Addenda, a later Addendum prevailing over an earlier one;' '(b) Volume I (Instructions to Bidders);' '(c) Volume V (Draft Project Agreement);' 'the first named prevailing'; VOL-I 3.3 (p2): 'A Bidder that resolves such a conflict unilaterally does so at its own risk'. Which clause governs the term, what to record in Form 4-E and which term start the Financial Model assumes are a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded.</t>
         </is>
       </c>
       <c r="AA82" s="4" t="inlineStr">
@@ -11977,7 +11983,7 @@
       </c>
       <c r="AD82" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:12.1 (VOL-I p6; text layer); ADD-02/Q7 [ADD-02; proposed; annotates VOL-I:12.1 (confirms)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
+          <t>VOL-I:12.1 (VOL-I p6; text layer); ADD-02/Q7 [ADD-02; proposed; annotates VOL-I:12.1 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="AE82" s="4" t="inlineStr">
@@ -12217,7 +12223,7 @@
       <c r="Q84" s="4" t="inlineStr"/>
       <c r="R84" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-02: ADD-02 Q13: the Authority will not extend; the periods in VOL-I 12.2 are unchanged. by ADD-02/Q13 [ADD-02; proposed; annotates VOL-I:12.2 (confirms)] &lt;- ADD-02:Q13 (ADD-02 p2)</t>
+          <t>reading re-made at ADD-02: ADD-02 Q13 (p2), asked whether the Authority will extend the Financial Close long-stop date, answers: 'The periods in Volume I Clause 12.2 are unchanged.'. by ADD-02/Q13 [ADD-02; proposed; annotates VOL-I:12.2 (confirms)] &lt;- ADD-02:Q13 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="S84" s="4" t="inlineStr">
@@ -12257,7 +12263,7 @@
       </c>
       <c r="Z84" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 Q13: the Authority will not extend; the periods in VOL-I 12.2 are unchanged.</t>
+          <t>ADD-02 Q13 (p2), asked whether the Authority will extend the Financial Close long-stop date, answers: 'The periods in Volume I Clause 12.2 are unchanged.'</t>
         </is>
       </c>
       <c r="AA84" s="4" t="inlineStr">
@@ -17349,7 +17355,7 @@
       <c r="Q120" s="4" t="inlineStr"/>
       <c r="R120" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-02: ADD-02 Q11 (peak hourly flow of 7,500 m3/h against a daily average of 120,000 m3/day) answers: 'Bidders shall design to the figures stated in Volume II. Volume II Clause 4.2 applies.' The answer does not resolve the figures it was asked about; the figures themselves are not contradictory (120,000 m3/day is 5,000 m3/h on average; 7,500 m3/h peak is a 1.5 peaking factor, I-FLOWS); what stays undefined is the dry-weather flow (CQ-DWF-STORM-FLOW). by ADD-02/Q11 [ADD-02; proposed; annotates VOL-II:4.2 (confirms)] &lt;- ADD-02:Q11 (ADD-02 p2)</t>
+          <t>reading re-made at ADD-02: ADD-02 Q11 (p2), asked about a peak hourly flow of 7,500 m3/h against a daily average of 120,000 m3/day, answers: 'Bidders shall design to the figures stated in Volume II. Volume II Clause 4.2 applies.' It settles the question asked (design to the Volume II figures; this clause applies) and does not comment on their consistency, which this clause leaves to the Bidder, or define 'dry weather flow' (CQ-DWF-STORM-FLOW). Engineering reading, for the process engineer to confirm (not the Authority's words): 120,000 m3/day is 5,000 m3/h on average and 7,500 m3/h a peaking factor of 1.5, so the two figures are not contradictory (I-FLOWS). by ADD-02/Q11 [ADD-02; proposed; annotates VOL-II:4.2 (confirms)] &lt;- ADD-02:Q11 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="S120" s="4" t="inlineStr">
@@ -17381,7 +17387,7 @@
       </c>
       <c r="Z120" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 Q11 (peak hourly flow of 7,500 m3/h against a daily average of 120,000 m3/day) answers: 'Bidders shall design to the figures stated in Volume II. Volume II Clause 4.2 applies.' The answer does not resolve the figures it was asked about; the figures themselves are not contradictory (120,000 m3/day is 5,000 m3/h on average; 7,500 m3/h peak is a 1.5 peaking factor, I-FLOWS); what stays undefined is the dry-weather flow (CQ-DWF-STORM-FLOW).</t>
+          <t>ADD-02 Q11 (p2), asked about a peak hourly flow of 7,500 m3/h against a daily average of 120,000 m3/day, answers: 'Bidders shall design to the figures stated in Volume II. Volume II Clause 4.2 applies.' It settles the question asked (design to the Volume II figures; this clause applies) and does not comment on their consistency, which this clause leaves to the Bidder, or define 'dry weather flow' (CQ-DWF-STORM-FLOW). Engineering reading, for the process engineer to confirm (not the Authority's words): 120,000 m3/day is 5,000 m3/h on average and 7,500 m3/h a peaking factor of 1.5, so the two figures are not contradictory (I-FLOWS).</t>
         </is>
       </c>
       <c r="AA120" s="4" t="inlineStr">
@@ -22707,9 +22713,9 @@
 [VOL-IV F4-A/power-of-attorney-reference-and-date p3] Power of Attorney reference and date:
 [VOL-IV F4-A/date p3] Date:
 [VOL-IV F4-A/company-seal p3] Company seal:
-[ADD-01 AppA/para1 p3; issued by ADD-01] (not in the volumes as issued)
-[ADD-01 AppA/single-point-of-contact p3; issued by ADD-01] (not in the volumes as issued)
-[ADD-01 AppA/signature-name-capacity p3; issued by ADD-01] (not in the volumes as issued)</t>
+[ADD-01 AppA/para1 p3; issued by ADD-01] Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.
+[ADD-01 AppA/single-point-of-contact p3; issued by ADD-01] Single point of contact:
+[ADD-01 AppA/signature-name-capacity p3; issued by ADD-01] Signature / name / capacity:</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -23866,7 +23872,7 @@
       <c r="X166" s="4" t="inlineStr"/>
       <c r="Y166" s="4" t="inlineStr">
         <is>
-          <t>medium: from an image reading (transcription and displayed translation confirmed by the owner, 3 Oct 2026, VOL-IV-p6-r1; the consequence category mapping stays open: I-F4C-EXCLUSION)</t>
+          <t>medium: from an image reading (transcription and displayed translations confirmed by the owner, 3 Oct 2026, VOL-IV-p6-r1; the consequence category mapping stays open: I-F4C-EXCLUSION)</t>
         </is>
       </c>
       <c r="Z166" s="4" t="inlineStr">
@@ -24012,7 +24018,7 @@
       <c r="X167" s="4" t="inlineStr"/>
       <c r="Y167" s="4" t="inlineStr">
         <is>
-          <t>medium: from an image reading (transcription and displayed translation confirmed by the owner, 3 Oct 2026, VOL-IV-p6-r1; the consequence category mapping stays open: I-F4C-EXCLUSION)</t>
+          <t>medium: from an image reading (transcription and displayed translations confirmed by the owner, 3 Oct 2026, VOL-IV-p6-r1; the consequence category mapping stays open: I-F4C-EXCLUSION)</t>
         </is>
       </c>
       <c r="Z167" s="4" t="inlineStr">
@@ -24162,7 +24168,7 @@
       <c r="X168" s="4" t="inlineStr"/>
       <c r="Y168" s="4" t="inlineStr">
         <is>
-          <t>medium: from an image reading (transcription confirmed by the owner, 3 Oct 2026); wording differs from VOL-I 8.10</t>
+          <t>medium: from an image reading (transcription and displayed translations confirmed by the owner, 3 Oct 2026); wording differs from VOL-I 8.10</t>
         </is>
       </c>
       <c r="Z168" s="4" t="inlineStr">
@@ -24312,7 +24318,7 @@
       <c r="X169" s="4" t="inlineStr"/>
       <c r="Y169" s="4" t="inlineStr">
         <is>
-          <t>medium: transcription confirmed by the owner, 3 Oct 2026, including the clause numeral (4.2); the interpretation is proposed</t>
+          <t>medium: transcription and displayed translations confirmed by the owner, 3 Oct 2026, including the clause numeral (4.2); the interpretation is proposed</t>
         </is>
       </c>
       <c r="Z169" s="4" t="inlineStr">
@@ -24506,7 +24512,7 @@
       </c>
       <c r="AE170" s="4" t="inlineStr">
         <is>
-          <t>I-NO-CONSEQUENCE</t>
+          <t>I-NO-CONSEQUENCE; I-F4D-WORDING</t>
         </is>
       </c>
       <c r="AF170" s="4" t="inlineStr"/>
@@ -25615,7 +25621,11 @@
           <t>I-NO-CONSEQUENCE</t>
         </is>
       </c>
-      <c r="AF178" s="4" t="inlineStr"/>
+      <c r="AF178" s="4" t="inlineStr">
+        <is>
+          <t>&lt;- REL-VOL-V-FORM-4E [confirmed depends_on] from VOL-V:1.1, VOL-V:1.2, VOL-V:1.3, VOL-V:1.4, VOL-V:1.5, VOL-V:1.6, VOL-V:3.1, VOL-V:3.2, VOL-V:3.3, VOL-V:12.1, VOL-V:12.2, VOL-V:12.3, VOL-V:12.4, VOL-V:18.1, VOL-V:18.2, VOL-V:18.3, VOL-V:18.4, VOL-V:24.1, VOL-V:24.2, VOL-V:24.3, VOL-V:24.4, VOL-V:29.1, VOL-V:29.2, VOL-V:29.3, VOL-V:29.4, VOL-V:29.5, VOL-V:31.1, VOL-V:31.2, VOL-V:31.3, VOL-V:31.4, VOL-V:31.5, VOL-V:34.1, VOL-V:34.2, VOL-V:34.3, VOL-V:36.1, VOL-V:36.2, VOL-V:36.3, VOL-V:39.1, VOL-V:39.2, VOL-V:39.3, VOL-V:39.4, VOL-V:39.5, VOL-V:40.1, VOL-V:40.2, VOL-V:40.3, VOL-V:42.1, VOL-V:42.2, VOL-V:44.1, VOL-V:44.2, VOL-V:44.3; REACHED at ADD-02 (confirmed dependency): from VOL-V:3.1, VOL-V:36.2 via REL-VOL-V-FORM-4E</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="inlineStr">
@@ -25935,7 +25945,7 @@
       </c>
       <c r="AF180" s="4" t="inlineStr">
         <is>
-          <t>&lt;- REL-MODEL-FORM-4F [confirmed feeds_calculation] from VOL-I-10.3-01</t>
+          <t>&lt;- REL-MODEL-FORM-4F [confirmed feeds_calculation] from VOL-I-10.3-01; REACHED at ADD-02 (possible impact): from VOL-V:36.2 via REL-CHANGE-IN-LAW-FINANCIAL-MODEL &gt; REL-MODEL-FORM-4F</t>
         </is>
       </c>
     </row>
@@ -26169,7 +26179,7 @@
       <c r="Q182" s="4" t="inlineStr"/>
       <c r="R182" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-02: ADD-02 Q7 (p2): 'The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' Under VOL-I 3.2 Volume I prevails over Volume V, so for the RFP Documents this clause is subordinate to VOL-I 12.1 (from PCOD); it is left unamended, and 'A deviation not listed in Form 4-E will be taken as accepted.' (VOL-V Note to Bidders, p2): what to record in Form 4-E and the Financial Model stays for Legal (I-CONCESSION, CQ-CONCESSION-TERM). (Session 11 audit A1-3 wording, PROPOSED.). by ADD-02/Q7 [ADD-02; proposed; annotates VOL-V:3.1 (confirms)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
+          <t>reading re-made at ADD-02: ADD-02 Q7 (p2) was asked 'Which applies?' and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither. Two readings: this clause, 'twenty-five (25) years from the Effective Date'; VOL-I 12.1 (p6), 'twenty-five (25) years commencing on the Project Commercial Operation Date' (row VOL-I-12.1-01). VOL-I 3.2 (p2) orders the RFP Documents '(a) the Addenda, a later Addendum prevailing over an earlier one;' '(b) Volume I (Instructions to Bidders);' '(c) Volume V (Draft Project Agreement);' 'the first named prevailing'; VOL-I 3.3 (p2): 'A Bidder that resolves such a conflict unilaterally does so at its own risk'; and 'A deviation not listed in Form 4-E will be taken as accepted.' (VOL-V Note to Bidders, p2). Which clause governs the term, what to record in Form 4-E and which term start the Financial Model assumes are a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded. by ADD-02/Q7 [ADD-02; proposed; annotates VOL-V:3.1 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="S182" s="4" t="inlineStr">
@@ -26200,12 +26210,12 @@
       </c>
       <c r="Y182" s="4" t="inlineStr">
         <is>
-          <t>medium: verbatim; subordinate to VOL-I 12.1 under VOL-I 3.2 as ADD-02 Q7 directs, but left unamended (what to record in Form 4-E is open for Legal, I-CONCESSION); the Effective Date is not a pack event</t>
+          <t>medium: verbatim; conflicts with VOL-I 12.1 (from PCOD); ADD-02 Q7 refers to the order of precedence at VOL-I 3.2 without saying which clause applies; which clause governs is a decision for a person (Legal, I-CONCESSION); no decision recorded; the Effective Date is not a pack event</t>
         </is>
       </c>
       <c r="Z182" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 Q7 (p2): 'The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' Under VOL-I 3.2 Volume I prevails over Volume V, so for the RFP Documents this clause is subordinate to VOL-I 12.1 (from PCOD); it is left unamended, and 'A deviation not listed in Form 4-E will be taken as accepted.' (VOL-V Note to Bidders, p2): what to record in Form 4-E and the Financial Model stays for Legal (I-CONCESSION, CQ-CONCESSION-TERM). (Session 11 audit A1-3 wording, PROPOSED.)</t>
+          <t>ADD-02 Q7 (p2) was asked 'Which applies?' and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither. Two readings: this clause, 'twenty-five (25) years from the Effective Date'; VOL-I 12.1 (p6), 'twenty-five (25) years commencing on the Project Commercial Operation Date' (row VOL-I-12.1-01). VOL-I 3.2 (p2) orders the RFP Documents '(a) the Addenda, a later Addendum prevailing over an earlier one;' '(b) Volume I (Instructions to Bidders);' '(c) Volume V (Draft Project Agreement);' 'the first named prevailing'; VOL-I 3.3 (p2): 'A Bidder that resolves such a conflict unilaterally does so at its own risk'; and 'A deviation not listed in Form 4-E will be taken as accepted.' (VOL-V Note to Bidders, p2). Which clause governs the term, what to record in Form 4-E and which term start the Financial Model assumes are a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded.</t>
         </is>
       </c>
       <c r="AA182" s="4" t="inlineStr">
@@ -26225,7 +26235,7 @@
       </c>
       <c r="AD182" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:3.1 (VOL-V p2; text layer); ADD-02/Q7 [ADD-02; proposed; annotates VOL-V:3.1 (confirms)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
+          <t>VOL-V:3.1 (VOL-V p2; text layer); ADD-02/Q7 [ADD-02; proposed; annotates VOL-V:3.1 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="AE182" s="4" t="inlineStr">
@@ -26493,7 +26503,7 @@
       </c>
       <c r="Z184" s="4" t="inlineStr">
         <is>
-          <t>Delay liquidated damages are the Authority's sole financial remedy for late completion, without prejudice to termination (18.2). Cap: their aggregate 'shall not exceed ten per cent (10%) of the Estimated Project Cost' (VOL-V 18.4, p2; session 11 audit A1-6, PROPOSED). PCOD: certified by the Independent Engineer against VOL-II 7.2 (VOL-V 1.5). The date rule records 36 months as 3 years (date rules have no month unit).</t>
+          <t>Delay liquidated damages are the Authority's sole financial remedy for late completion, without prejudice to termination (18.2). Cap: their aggregate 'shall not exceed ten per cent (10%) of the Estimated Project Cost' (VOL-V 18.4, p2). PCOD: certified by the Independent Engineer against VOL-II 7.2 (VOL-V 1.5). The date rule records 36 months as 3 years (date rules have no month unit).</t>
         </is>
       </c>
       <c r="AA184" s="4" t="inlineStr">
@@ -29118,12 +29128,12 @@
       </c>
       <c r="G203" s="4" t="inlineStr">
         <is>
-          <t>only to the extent that such expenditure exceeds SAR 2,500,000 in aggregate over the term</t>
+          <t>SAR 2,500,000</t>
         </is>
       </c>
       <c r="H203" s="4" t="inlineStr">
         <is>
-          <t>VOL-V 36.2 p4 as amended by ADD-02 8.1 p3</t>
+          <t>ADD-02 8.1 p3 (amending VOL-V 36.2)</t>
         </is>
       </c>
       <c r="I203" s="4" t="inlineStr">
@@ -29184,7 +29194,7 @@
       </c>
       <c r="U203" s="4" t="inlineStr">
         <is>
-          <t>VOL-V 36.2 p4 as amended by ADD-02 8.1 p3</t>
+          <t>ADD-02 8.1 p3 (amending VOL-V 36.2)</t>
         </is>
       </c>
       <c r="V203" s="4" t="inlineStr">
@@ -29739,7 +29749,11 @@
         </is>
       </c>
       <c r="Q207" s="4" t="inlineStr"/>
-      <c r="R207" s="4" t="inlineStr"/>
+      <c r="R207" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: ADD-02 Q7 (p2) was asked 'Which applies?' (VOL-I 12.1: from PCOD; VOL-V 3.1: from the Effective Date) and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither, so when year 20 of the term starts is not settled: a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded. The date rule records the start of year 20 as 19 years after the term starts. by ADD-02/Q7 [ADD-02; proposed; cited by the reading made at ADD-02 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
+        </is>
+      </c>
       <c r="S207" s="4" t="inlineStr">
         <is>
           <t>VOL-V 42.2 p4</t>
@@ -29768,12 +29782,12 @@
       </c>
       <c r="Y207" s="4" t="inlineStr">
         <is>
-          <t>medium: verbatim; when year 20 starts depends on the term start: VOL-I 12.1 (from PCOD) prevails under VOL-I 3.2 as ADD-02 Q7 directs, but VOL-V 3.1 (from the Effective Date) is left unamended (I-CONCESSION)</t>
+          <t>medium: verbatim; when year 20 starts depends on the term start: VOL-I 12.1 (from PCOD) or VOL-V 3.1 (from the Effective Date); ADD-02 Q7 answers 'The order of precedence at Volume I Clause 3.2 applies.' without saying which applies; which clause governs is a decision for a person (Legal, I-CONCESSION); no decision recorded</t>
         </is>
       </c>
       <c r="Z207" s="4" t="inlineStr">
         <is>
-          <t>The term runs from the Effective Date under VOL-V 3.1 but from PCOD under VOL-I 12.1. The date rule records the start of year 20 as 19 years after the term starts.</t>
+          <t>ADD-02 Q7 (p2) was asked 'Which applies?' (VOL-I 12.1: from PCOD; VOL-V 3.1: from the Effective Date) and answers: 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' It does not say which clause applies, and it amends neither, so when year 20 of the term starts is not settled: a decision for a person (Legal; I-CONCESSION, CQ-CONCESSION-TERM); no decision recorded. The date rule records the start of year 20 as 19 years after the term starts.</t>
         </is>
       </c>
       <c r="AA207" s="4" t="inlineStr">
@@ -29793,7 +29807,7 @@
       </c>
       <c r="AD207" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:42.2 (VOL-V p4; text layer)</t>
+          <t>VOL-V:42.2 (VOL-V p4; text layer); ADD-02/Q7 [ADD-02; proposed; cited by the reading made at ADD-02 (interprets)] &lt;- ADD-02:Q7 (ADD-02 p2)</t>
         </is>
       </c>
       <c r="AE207" s="4" t="inlineStr">
@@ -30073,6 +30087,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:AF209"/>
+  <mergeCells count="1">
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33954,7 +33971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34020,7 +34037,7 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.3-01; VOL-I-6.4-01; VOL-I-6.4-02; VOL-I-7.1-01; VOL-I-8.3-01; ADD-01-AppA-01; ADD-02-5.2-01; ADD-02-F4G-04; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-8.4-01; VOL-I-8.4-02; VOL-I-8.7-01; VOL-I-8.8-01; VOL-I-8.9-01; VOL-I-8.10-01; VOL-I-9.1-01; VOL-I-9.1h-01; VOL-I-9.7-01; VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.3-01; VOL-I-10.3-02; VOL-I-10.4-01; VOL-I-10.5-02; VOL-I-10.6-01; VOL-I-App3-01; VOL-IV-F4A-03; VOL-IV-F4A-04; VOL-IV-F4A-05; VOL-IV-F4A-06; VOL-IV-F4A-07; VOL-IV-F4B-01; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-05; VOL-IV-F4D-01; VOL-IV-F4E-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
+          <t>VOL-I-6.3-01; VOL-I-6.4-01; VOL-I-6.4-02; VOL-I-7.1-01; VOL-I-8.3-01; ADD-01-AppA-01; ADD-02-F4G-04; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-8.4-01; VOL-I-8.4-02; VOL-I-8.7-01; VOL-I-8.8-01; VOL-I-8.9-01; VOL-I-8.10-01; VOL-I-9.1-01; VOL-I-9.1h-01; VOL-I-9.7-01; VOL-I-10.1-01; VOL-I-10.2-01; VOL-I-10.3-01; VOL-I-10.3-02; VOL-I-10.4-01; VOL-I-10.5-02; VOL-I-10.6-01; VOL-I-App3-01; VOL-IV-F4A-02; VOL-IV-F4B-01; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-05; VOL-IV-F4D-01; VOL-IV-F4E-01; VOL-IV-F4F-01; VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr"/>
@@ -34033,7 +34050,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Local Content Certificate: issuing 'competent authority' not named and no lead time stated; the minutes (non-binding) record bidders' difficulty obtaining it in time</t>
+          <t>HUMAN DECISION PENDING: Local Content Certificate: issuing 'competent authority' not named and no lead time stated; the minutes (non-binding) record bidders' difficulty obtaining it in time</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -34065,7 +34082,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Bidder facts (members, signatories, attendance, references) are configurable assumptions, not facts; confirm them</t>
+          <t>Bidder facts are configurable assumptions about an assumed bidder (config/assumptions.yaml), not facts: the consortium members and how many are foreign, the reference plants offered, the signatories per member, and attendance at the Pre-Bid Conference; confirm them</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -34093,7 +34110,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Reissued Form 4-A (ADD-01 App A) drops fields and the numbered confirmations of the original and states a purpose ('acknowledgement of Addenda at paragraph 1') it has no paragraph for; what to print and sign, and whether to seek clarification before the cut-off</t>
+          <t>HUMAN DECISION PENDING: Reissued Form 4-A (ADD-01 App A) drops fields and the numbered confirmations of the original and states a purpose ('acknowledgement of Addenda at paragraph 1') it has no paragraph for; what to print and sign, and whether to seek clarification before the cut-off</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -34157,7 +34174,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Form 4-C declaration 4 says any incorrect statement 'leads to the exclusion of the proposal' (يؤدي إلى استبعاد العرض). The English volumes never use 'exclusion'; it is kept as its own category and not treated as equivalent to rejection, disqualification or non-responsiveness. Which, if any, it corresponds to is a legal question (clarification register CQ-F4C-EXCLUSION)</t>
+          <t>HUMAN DECISION PENDING: Form 4-C declaration 4 says any incorrect statement 'leads to the exclusion of the proposal' (يؤدي إلى استبعاد العرض). The English volumes never use 'exclusion'; it is kept as its own category and not treated as equivalent to rejection, disqualification or non-responsiveness. Which, if any, it corresponds to is a legal question (clarification register CQ-F4C-EXCLUSION)</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -34249,7 +34266,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Form 4-G undertakings are answered Yes/No; the effect of 'No' is not stated, and undertakings 3-6 add post-award obligations not in VOL-II 6</t>
+          <t>HUMAN DECISION PENDING: Form 4-G undertakings are answered Yes/No; the effect of 'No' is not stated, and undertakings 3-6 add post-award obligations not in VOL-II 6</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -34272,17 +34289,17 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT</t>
+          <t>I-F4D-WORDING</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Table 2-4 is reproduced from an Environmental Permit that is not in the pack. The precedence language is in the VOL-II p3 reproduction preamble ('the Environmental Permit shall prevail'; VOL-II 2.4 incorporates the table by reference); the owner confirmed that location on 3 Oct 2026. Not confirmed, and not claimed: the Permit's contents and compliance with the Permit, including after the TN amendment (ADD-02 5.1, 3 mg/l)</t>
+          <t>HUMAN DECISION PENDING: Form 4-D wording latitude: VOL-I 8.7 (p4) requires the guarantee 'substantially in the form set out in Form 4-D'; Volume IV (p2) states 'A Bidder that alters the wording of a Form does so at its own risk.' Whether a change to the Form 4-D wording stays within 'substantially in the form' is a decision for Legal; no decision recorded (the scope and expiry point is drafted as CQ-F4D-GUARANTEE-SCOPE)</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -34292,29 +34309,25 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-T2-4-TN; ADD-02-5.2-01; VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1; VOL-II-3.1-01; VOL-II-7.2-01; VOL-V-31.1-02</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>CQ-ENV-PERMIT</t>
-        </is>
-      </c>
+          <t>VOL-IV-F4D-01</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>I-CONCESSION</t>
+          <t>I-PERMIT</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Concession term: VOL-I 12.1 (25 years from PCOD) vs VOL-V 3.1 (25 years from the Effective Date). ADD-02 Q7 p2: 'The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' Under VOL-I 3.2 Volume I ((b)) prevails over Volume V ((c)), so for the RFP Documents the term runs from PCOD (VOL-I 12.1); VOL-V 3.1 is left unamended. Open for Legal (draft question CQ-CONCESSION-TERM): what to record in Form 4-E (a deviation not listed is taken as accepted, VOL-V Note to Bidders), which term start the Financial Model assumes, and how 'the term' in VOL-V 3.2 and 42.2 reads. A legal and commercial question</t>
+          <t>HUMAN DECISION PENDING: Table 2-4 is reproduced from an Environmental Permit that is not in the pack. The precedence language is in the VOL-II p3 reproduction preamble ('the Environmental Permit shall prevail'; VOL-II 2.4 incorporates the table by reference); the owner confirmed that location on 3 Oct 2026. Not confirmed, and not claimed: the Permit's contents and compliance with the Permit, including after the TN amendment (ADD-02 5.1, 3 mg/l)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -34324,29 +34337,29 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-3.3-01; VOL-I-9.6-01; VOL-I-12.1-01; VOL-II-1.1-01; VOL-II-8.5-01; VOL-II-8.5-02; VOL-V-NOTE-01; VOL-V-3.1-01; VOL-V-3.2-01; VOL-V-42.1-01; VOL-V-42.2-01</t>
+          <t>VOL-II-T2-4-TN; ADD-02-5.2-01; VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1; VOL-II-3.1-01; VOL-II-7.2-01; VOL-V-31.1-02</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>CQ-CONCESSION-TERM</t>
+          <t>CQ-ENV-PERMIT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>I-FLOWS</t>
+          <t>I-CONCESSION</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Design flows: settled by ADD-02 Q11 for the question asked: design to the Volume II figures (VOL-II 4.2 applies); the 120,000 m3/day average and 7,500 m3/h peak hourly flow are not contradictory. Open: 'dry weather flow' in Table 2-6 row 2-6.4 is undefined, so the storm flow to be passed to full treatment is unclear (draft question CQ-DWF-STORM-FLOW). An engineering question</t>
+          <t>HUMAN DECISION PENDING: Concession term: VOL-I 12.1 (p6) 'twenty-five (25) years commencing on the Project Commercial Operation Date'; VOL-V 3.1 (p2) 'twenty-five (25) years from the Effective Date'. ADD-02 Q7 (p2), asked 'Which applies?': 'The Authority notes the question. The order of precedence at Volume I Clause 3.2 applies. The Authority does not consider further amendment necessary at this stage.' The answer does not say which clause applies, and neither clause is amended. VOL-I 3.2 (p2) orders (a) the Addenda, (b) Volume I, (c) Volume V, 'the first named prevailing'; VOL-I 3.3 (p2): 'A Bidder that resolves such a conflict unilaterally does so at its own risk'. Which clause governs the term is a decision for a person (Legal); no decision recorded. It sets the term start in the Financial Model, what to record in Form 4-E ('A deviation not listed in Form 4-E will be taken as accepted.', VOL-V Note to Bidders) and how 'the term' in VOL-V 3.2 and 42.2 reads (draft question CQ-CONCESSION-TERM). A legal and commercial question</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -34356,24 +34369,24 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-4.1-01; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-4; VOL-II-4.2-01; VOL-II-5.2-01; VOL-V-31.1-01</t>
+          <t>VOL-I-3.3-01; VOL-I-9.6-01; VOL-I-12.1-01; VOL-II-1.1-01; VOL-II-8.5-01; VOL-II-8.5-02; VOL-V-NOTE-01; VOL-V-3.1-01; VOL-V-3.2-01; VOL-V-42.1-01; VOL-V-42.2-01</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>CQ-DWF-STORM-FLOW</t>
+          <t>CQ-CONCESSION-TERM</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-III</t>
+          <t>I-FLOWS</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Volume III referenced (VOL-I 3.1), not supplied; pack confirmed complete (2 Oct). Only Drawing 03-C-114 shows the effluent main's delivery point (VOL-II 5.1). No omission claim after the PDD (VOL-I 3.4)</t>
+          <t>HUMAN DECISION PENDING: Design flows: ADD-02 Q11 (p2), asked about a peak hourly flow of 7,500 m3/h against a daily average of 120,000 m3/day, answers 'Bidders shall design to the figures stated in Volume II. Volume II Clause 4.2 applies.': design to the Volume II figures. It does not comment on their consistency (VOL-II 4.2 leaves that to the Bidder) and does not define 'dry weather flow'. Engineering reading, for the process engineer to confirm (not the Authority's words): 120,000 m3/day is 5,000 m3/h on average and 7,500 m3/h a peaking factor of 1.5, so the two figures are not contradictory. Open: 'dry weather flow' in Table 2-6 row 2-6.4 is undefined, so the storm flow to be passed to full treatment is unclear (draft question CQ-DWF-STORM-FLOW). An engineering question</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -34388,29 +34401,29 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-Q4-01; VOL-I-3.4-01; VOL-I-5.5-01; VOL-II-5.1-01; VOL-II-5.2-02; VOL-V-31.1-03</t>
+          <t>VOL-II-4.1-01; VOL-II-T2-6-1; VOL-II-T2-6-2; VOL-II-T2-6-4; VOL-II-4.2-01; VOL-II-5.2-01; VOL-V-31.1-01</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>CQ-VOL-III-DRAWINGS</t>
+          <t>CQ-DWF-STORM-FLOW</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-ENV-B</t>
+          <t>I-VOL-III</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 10.1: Envelope B holds 'only' Form 4-F and the Financial Model, yet 10.3 (model auditor's opinion) and 10.6 (financing assumptions schedule) need more documents; where they go is unstated</t>
+          <t>Volume III referenced (VOL-I 3.1), not supplied; pack confirmed complete (2 Oct). Only Drawing 03-C-114 shows the effluent main's delivery point (VOL-II 5.1). No omission claim after the PDD (VOL-I 3.4)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -34420,24 +34433,24 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-3.3-01; VOL-I-10.1-01; VOL-I-10.3-02; VOL-I-10.6-01; VOL-IV-F4F-01</t>
+          <t>ADD-01-Q4-01; VOL-I-3.4-01; VOL-I-5.5-01; VOL-II-5.1-01; VOL-II-5.2-02; VOL-V-31.1-03</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>CQ-ENV-B-CONTENTS</t>
+          <t>CQ-VOL-III-DRAWINGS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-ENV-A-PRICES</t>
+          <t>I-VOL-I-ENV-B</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 6.2 makes any price, rate or other commercial information in Envelope A non-responsive, but Form 4-B (Envelope A) asks for each reference's contract value in SAR</t>
+          <t>VOL-I 10.1: Envelope B holds 'only' Form 4-F and the Financial Model, yet 10.3 (model auditor's opinion) and 10.6 (financing assumptions schedule) need more documents; where they go is unstated</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -34452,24 +34465,24 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-3.3-01; VOL-I-6.2-02; VOL-I-9.5-01; VOL-IV-F4B-01</t>
+          <t>VOL-I-3.3-01; VOL-I-10.1-01; VOL-I-10.3-02; VOL-I-10.6-01; VOL-IV-F4F-01</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>CQ-F4B-CONTRACT-VALUE</t>
+          <t>CQ-ENV-B-CONTENTS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-COPIES</t>
+          <t>I-VOL-I-ENV-A-PRICES</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Copy quantities are per Proposal (VOL-I 6.5: 'Each Proposal shall be submitted as' one marked original, three hard copies and one encrypted USB copy); settled. Open: how the single USB copy relates to the two separately sealed envelopes and how its means of decryption is given (draft question CQ-USB-PACKAGING)</t>
+          <t>VOL-I 6.2 makes any price, rate or other commercial information in Envelope A non-responsive, but Form 4-B (Envelope A) asks for each reference's contract value in SAR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -34484,24 +34497,24 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.5-01</t>
+          <t>VOL-I-3.3-01; VOL-I-6.2-02; VOL-I-9.5-01; VOL-IV-F4B-01</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>CQ-USB-PACKAGING</t>
+          <t>CQ-F4B-CONTRACT-VALUE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-FILE-NAMES</t>
+          <t>I-VOL-I-COPIES</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>The Financial Model must be in Microsoft Excel (VOL-I 10.3); settled. Open: how the Appendix 2 naming convention, which ends in '.pdf' and does not define [BIDDER] or the date in [YYYYMMDD], applies to it (draft question CQ-FILENAMES)</t>
+          <t>Copy quantities are per Proposal (VOL-I 6.5: 'Each Proposal shall be submitted as' one marked original, three hard copies and one encrypted USB copy); settled. Open: how the single USB copy relates to the two separately sealed envelopes and how its means of decryption is given (draft question CQ-USB-PACKAGING)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -34516,29 +34529,29 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.5-02; VOL-I-10.3-01</t>
+          <t>VOL-I-6.5-01</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>CQ-FILENAMES</t>
+          <t>CQ-USB-PACKAGING</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-BOND-LONGSTOP</t>
+          <t>I-VOL-I-FILE-NAMES</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>The VOL-I 12.2 periods (Commercial Close 120 days, Financial Close 270 days from the Preferred Bidder Notification) are unchanged: settled by ADD-02 Q13. Open: the Bid Bond's 180-day validity from the PDD (VOL-I 6.3) may end before the Financial Close long-stop, on which 12.2 lets the Authority call it; whether it must be extended to cover that period, and 'long-stop date' is undefined (draft question CQ-BOND-FC-COVERAGE)</t>
+          <t>The Financial Model must be in Microsoft Excel (VOL-I 10.3); settled. Open: how the Appendix 2 naming convention, which ends in '.pdf' and does not define [BIDDER] or the date in [YYYYMMDD], applies to it (draft question CQ-FILENAMES)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Commercial lead</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -34548,29 +34561,29 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-12.2-02</t>
+          <t>VOL-I-6.5-02; VOL-I-10.3-01</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>CQ-BOND-FC-COVERAGE</t>
+          <t>CQ-FILENAMES</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-APPENDICES</t>
+          <t>I-VOL-I-BOND-LONGSTOP</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 9.2 excludes 'the appendices expressly permitted by Volume II' from the page limit; none was found in the Volume II extract</t>
+          <t>HUMAN DECISION PENDING: The VOL-I 12.2 periods (Commercial Close 120 days, Financial Close 270 days from the Preferred Bidder Notification) are unchanged: settled by ADD-02 Q13. Open: the Bid Bond's 180-day validity from the PDD (VOL-I 6.3) may end before the Financial Close long-stop, on which 12.2 lets the Authority call it; whether it must be extended to cover that period, and 'long-stop date' is undefined (draft question CQ-BOND-FC-COVERAGE)</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Technical lead</t>
+          <t>Commercial lead</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -34580,24 +34593,24 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-9.2-01</t>
+          <t>VOL-I-12.2-02</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>CQ-PAGE-LIMIT-APPENDICES</t>
+          <t>CQ-BOND-FC-COVERAGE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-MISSING</t>
+          <t>I-VOL-I-APPENDICES</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Not in the pack: ESIA (VOL-II 9.1) and geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
+          <t>VOL-I 9.2 excludes 'the appendices expressly permitted by Volume II' from the page limit; none was found in the Volume II extract</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -34612,29 +34625,29 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
+          <t>VOL-I-9.2-01</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>CQ-VOL-III-DRAWINGS</t>
+          <t>CQ-PAGE-LIMIT-APPENDICES</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-T24-TENSIONS</t>
+          <t>I-VOL-II-MISSING</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; 'at all times' (VOL-II 2.4) read with those bases means continuous compliance on each parameter's own basis, which is not treated as a conflict</t>
+          <t>Not in the pack: the Environmental and Social Impact Assessment (ESIA; VOL-II 9.1) and the geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Process engineer</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -34644,29 +34657,29 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01</t>
+          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>CQ-T24-RANGES</t>
+          <t>CQ-VOL-III-DRAWINGS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-MISSING</t>
+          <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
+          <t>HUMAN DECISION PENDING: The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; 'at all times' (VOL-II 2.4) read with those bases means continuous compliance on each parameter's own basis, which is not treated as a conflict</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -34676,24 +34689,24 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01</t>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>CQ-VOL-V-SCHEDULES</t>
+          <t>CQ-T24-RANGES</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-PERSISTENT-BREACH</t>
+          <t>I-VOL-V-MISSING</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
+          <t>HUMAN DECISION PENDING: VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -34708,29 +34721,29 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01</t>
+          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>CQ-PERSISTENT-BREACH</t>
+          <t>CQ-VOL-V-SCHEDULES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-IV-SCALE</t>
+          <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
+          <t>HUMAN DECISION PENDING: VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -34740,57 +34753,61 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>ADD-02-T1-1-N3-01</t>
+          <t>VOL-V-31.4-01</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>CQ-SCORING-METHOD</t>
+          <t>CQ-PERSISTENT-BREACH</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
+          <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr"/>
+          <t>ADD-02-T1-1-N3-01</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>CQ-SCORING-METHOD</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -34800,7 +34817,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -34808,12 +34825,12 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -34828,7 +34845,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -34836,46 +34853,50 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr"/>
@@ -34884,12 +34905,12 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -34908,12 +34929,12 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare. It prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time' (ADD-01 App A p3) while ADD-01 2.1 (p1) substitutes 'Thursday 26 November 2026' in VOL-I 6.1; not corrected (a person decides: I-F4A-FIELDS)</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -34932,12 +34953,12 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -34956,12 +34977,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: follow-up only (clarification CQ-CONCESSION-TERM): Volume V is left unamended, so whether VOL-V 3.1 not listed in Form 4-E would be taken as accepted under the Volume V note, and how 'the term' in VOL-V 3.2 and 42.2 reads, remain; a legal and commercial question for people</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -34980,12 +35001,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/Q7: which clause governs the concession term is not stated by the Authority and is a decision for a person (Legal, I-CONCESSION; draft question CQ-CONCESSION-TERM), with what to record in Form 4-E under the Volume V note and how 'the term' in VOL-V 3.2 and 42.2 reads; no decision recorded</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -35004,12 +35025,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -35028,12 +35049,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -35043,7 +35064,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr"/>
@@ -35052,12 +35073,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -35076,12 +35097,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE, BID-BOND-VALIDITY, PROPOSAL-VALIDITY, PROPOSAL-VALIDITY-F4A, REFERENCE-LOOKBACK: every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -35091,7 +35112,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -35100,45 +35121,41 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE (ADD-01 3.1), BID-BOND-VALIDITY (VOL-I 6.3), PROPOSAL-VALIDITY (VOL-I 7.1), PROPOSAL-VALIDITY-F4A (Form 4-A), REFERENCE-LOOKBACK (VOL-I 8.5): every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr"/>
       <c r="F40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -35148,7 +35165,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr"/>
@@ -35156,17 +35173,17 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid management</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -35176,7 +35193,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.6-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr"/>
@@ -35184,17 +35201,17 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -35204,7 +35221,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr"/>
@@ -35212,12 +35229,12 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -35232,7 +35249,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -35240,12 +35257,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-copies</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -35260,7 +35277,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -35268,12 +35285,12 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-seal-and-mark</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -35296,33 +35313,61 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
+          <t>I-A5-deliver</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; lcc-certificate INFEASIBLE by 12 WD; assemble-envelope-a INFEASIBLE by 12 WD; copies INFEASIBLE by 12 WD; seal-and-mark INFEASIBLE by 12 WD; deliver INFEASIBLE by 12 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F47"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -36912,7 +36957,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>PROVISIONAL ASSUMPTION: Working Days between delivery and the Proposal Due Date; 0 = delivered on the PDD itself, before the time VOL-I 6.1 (as amended) states; late Proposals are rejected unopened (VOL-I 6.6); not stated in the pack (session 11, audit A5-7); owner Bid manager</t>
+          <t>PROVISIONAL ASSUMPTION: Working Days between delivery and the Proposal Due Date; 0 = delivered on the PDD itself, before the time VOL-I 6.1 (as amended) states; late Proposals are rejected unopened (VOL-I 6.6); not stated in the pack; owner Bid manager</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -39177,7 +39222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -39197,148 +39242,94 @@
     <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="45" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Id</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Kind</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Blocks</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Issues</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Reached</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>REL-MEMBER-FIN-STANDING</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>member_scope</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>confirmed dependency</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr"/>
-      <c r="K2" s="4" t="inlineStr"/>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>I-BIDDER-FACTS</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="inlineStr">
-        <is>
-          <t>curator</t>
-        </is>
-      </c>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="O2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>REL-MEMBER-FORM-4C</t>
+          <t>REL-MEMBER-FIN-STANDING</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -39363,18 +39354,18 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
+          <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
+          <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
+          <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr"/>
@@ -39399,7 +39390,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>REL-MEMBER-MULTIPLE-PARTICIPATION</t>
+          <t>REL-MEMBER-FORM-4C</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -39424,18 +39415,18 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
+          <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
+          <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
+          <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr"/>
@@ -39460,7 +39451,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>REL-MEMBER-DEBARMENT</t>
+          <t>REL-MEMBER-MULTIPLE-PARTICIPATION</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -39485,16 +39476,20 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
+          <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
+          <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
+        </is>
+      </c>
       <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
       <c r="L5" s="4" t="inlineStr">
@@ -39517,7 +39512,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>REL-MEMBER-INVESTMENT-LICENCE</t>
+          <t>REL-MEMBER-DEBARMENT</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -39542,20 +39537,16 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-8.9-01</t>
+          <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
+          <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
-        </is>
-      </c>
+      <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
       <c r="L6" s="4" t="inlineStr">
@@ -39578,12 +39569,12 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>REL-T24-PROCESS-DESIGN</t>
+          <t>REL-MEMBER-INVESTMENT-LICENCE</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>limit_applies</t>
+          <t>member_scope</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -39598,30 +39589,30 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4</t>
+          <t>VOL-I:8.1; words:member of the Bidder; words:consortium member; words:member of the consortium</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-3.1-01</t>
+          <t>VOL-I-8.9-01</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
+          <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr"/>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
+          <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-T24-TENSIONS</t>
+          <t>I-BIDDER-FACTS</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -39634,16 +39625,12 @@
           <t>proposed</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>ADD-02</t>
-        </is>
-      </c>
+      <c r="O7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>REL-T24-RELIABILITY-RUN</t>
+          <t>REL-T24-PROCESS-DESIGN</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -39668,18 +39655,18 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-7.2-01</t>
+          <t>VOL-II-3.1-01</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
+          <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
+          <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr"/>
@@ -39708,7 +39695,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>REL-T24-UNAVAILABILITY</t>
+          <t>REL-T24-RELIABILITY-RUN</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -39733,18 +39720,18 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-02</t>
+          <t>VOL-II-7.2-01</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
+          <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr"/>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
+          <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr"/>
@@ -39773,7 +39760,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>REL-T24-RAMP-UP-DEDUCTIONS</t>
+          <t>REL-T24-UNAVAILABILITY</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -39798,18 +39785,18 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-29.3-01</t>
+          <t>VOL-V-31.1-02</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
+          <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr"/>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
+          <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr"/>
@@ -39838,7 +39825,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+          <t>REL-T24-RAMP-UP-DEDUCTIONS</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -39863,16 +39850,20 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
+          <t>VOL-V-29.3-01</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
+          <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
+        </is>
+      </c>
       <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
       <c r="L11" s="4" t="inlineStr">
@@ -39899,12 +39890,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-MECHANISM</t>
+          <t>REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>limit_applies</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -39919,28 +39910,28 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
+          <t>VOL-II:T2-4</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>calc:availability-payment</t>
+          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
+          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr"/>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
-        </is>
-      </c>
+      <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
           <t>curator</t>
@@ -39953,34 +39944,34 @@
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>ADD-01</t>
+          <t>ADD-02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-DEDUCTIONS</t>
+          <t>REL-PAY-MECHANISM</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>proposed relationship</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -39990,15 +39981,15 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr"/>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr"/>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
+        </is>
+      </c>
       <c r="J13" s="4" t="inlineStr"/>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
@@ -40012,45 +40003,53 @@
           <t>proposed</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-QUOTED-PRICE</t>
+          <t>REL-PAY-DEDUCTIONS</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>proposed relationship</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
+          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
           <t>calc:availability-payment</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-10.2-01</t>
-        </is>
-      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr"/>
       <c r="J14" s="4" t="inlineStr"/>
       <c r="K14" s="4" t="inlineStr"/>
@@ -40065,16 +40064,12 @@
           <t>proposed</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01</t>
-        </is>
-      </c>
+      <c r="O14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FORM-4F</t>
+          <t>REL-PAY-QUOTED-PRICE</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -40099,12 +40094,12 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV-F4F-01</t>
+          <t>VOL-I-10.2-01</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr"/>
@@ -40131,22 +40126,22 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FINANCIAL-MODEL</t>
+          <t>REL-PAY-FORM-4F</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>proposed relationship</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -40156,24 +40151,16 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.3-01</t>
+          <t>VOL-IV-F4F-01</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr">
-        <is>
-          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
-        </is>
-      </c>
-      <c r="I16" s="4" t="inlineStr">
-        <is>
-          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
-        </is>
-      </c>
+          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr"/>
+      <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
@@ -40196,41 +40183,49 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>REL-MODEL-FORM-4F</t>
+          <t>REL-PAY-FINANCIAL-MODEL</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>proposed relationship</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
           <t>VOL-I-10.3-01</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>VOL-IV-F4F-02</t>
-        </is>
-      </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr"/>
-      <c r="I17" s="4" t="inlineStr"/>
+          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
+        </is>
+      </c>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
@@ -40253,44 +40248,40 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
+          <t>REL-MODEL-FORM-4F</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>possible impact</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>calc:availability-payment</t>
+          <t>VOL-I-10.3-01</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.6-01</t>
+          <t>VOL-IV-F4F-02</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
-        </is>
-      </c>
+          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
       <c r="I18" s="4" t="inlineStr"/>
       <c r="J18" s="4" t="inlineStr"/>
       <c r="K18" s="4" t="inlineStr"/>
@@ -40307,63 +40298,55 @@
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>ADD-01</t>
+          <t>ADD-01; ADD-02</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
+          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>missing_document</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>possible impact</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:39.1</t>
+          <t>calc:availability-payment</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-39.1-01</t>
+          <t>VOL-I-10.6-01</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr"/>
+          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
+        </is>
+      </c>
       <c r="I19" s="4" t="inlineStr"/>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>I-VOL-V-MISSING</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr"/>
       <c r="M19" s="4" t="inlineStr">
         <is>
           <t>curator</t>
@@ -40374,17 +40357,21 @@
           <t>proposed</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+          <t>REL-LCC-ENVELOPE-A</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>missing_document</t>
+          <t>cites</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -40399,34 +40386,30 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:39.1</t>
+          <t>VOL-I:8.6</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:18.2</t>
+          <t>VOL-I:9.1(i)</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+          <t>VOL-I:9.1(i) p4: “(i) the certificates and evidence required under Section 8.”; VOL-I:8.6 p4: “The Bidder shall submit a Local Content Certificate issued by the competent authority”</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr"/>
-      <c r="I20" s="4" t="inlineStr"/>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
-        </is>
-      </c>
-      <c r="K20" s="4" t="inlineStr">
-        <is>
-          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
-        </is>
-      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Item (i) of the Envelope A list is whatever Section 8 requires: the Local Content Certificate leaves it when ADD-01 4.1 deletes VOL-I 8.6 and returns when ADD-02 9.1 reinstates 8.6 at 35%.</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-MISSING</t>
+          <t>I-LCC-ISSUER</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -40439,130 +40422,114 @@
           <t>proposed</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-02</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+          <t>REL-VOL-V-FORM-4E</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>missing_document</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1; VOL-V:1.2; VOL-V:1.3; VOL-V:1.4; VOL-V:1.5; VOL-V:1.6; VOL-V:3.1; VOL-V:3.2; VOL-V:3.3; VOL-V:12.1; VOL-V:12.2; VOL-V:12.3; VOL-V:12.4; VOL-V:18.1; VOL-V:18.2; VOL-V:18.3; VOL-V:18.4; VOL-V:24.1; VOL-V:24.2; VOL-V:24.3; VOL-V:24.4; VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5; VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5; VOL-V:34.1; VOL-V:34.2; VOL-V:34.3; VOL-V:36.1; VOL-V:36.2; VOL-V:36.3; VOL-V:39.1; VOL-V:39.2; VOL-V:39.3; VOL-V:39.4; VOL-V:39.5; VOL-V:40.1; VOL-V:40.2; VOL-V:40.3; VOL-V:42.1; VOL-V:42.2; VOL-V:44.1; VOL-V:44.2; VOL-V:44.3</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV-F4E-01</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:cover/note-to-bidders p2: “This extract contains the clauses of the draft Project Agreement on which the Authority invites comment through Form 4-E.”; VOL-V:cover/note-to-bidders p2: “A deviation not listed in Form 4-E will be taken as accepted.”</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>A changed Volume V clause (ADD-02 8.1: VOL-V 36.2, SAR 5,000,000 to SAR 2,500,000) is a clause on which Form 4-E invites comment: whether to list a deviation from it is re-read; what to list is for Legal.</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>proposed relationship</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:39.1</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V-31.4-01; VOL-V:39.3</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr"/>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>curator</t>
-        </is>
-      </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="O21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-02</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+          <t>REL-CHANGE-IN-LAW-FINANCIAL-MODEL</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>missing_document</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>possible impact</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:31.2</t>
+          <t>VOL-V:36.2</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V 36.2 sets the capital expenditure a General Change in Law must exceed before the Project Company is compensated (SAR 2,500,000 after ADD-02 8.1); no clause links it to the Financial Model, and whether the model prices the retained Change in Law risk is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 7 (deductions)</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>I-VOL-V-MISSING</t>
-        </is>
-      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
       <c r="M22" s="4" t="inlineStr">
         <is>
           <t>curator</t>
@@ -40582,7 +40549,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
+          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -40602,54 +40569,325 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
+          <t>VOL-V:39.1</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
+          <t>VOL-V-39.1-01</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
+          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr"/>
       <c r="I23" s="4" t="inlineStr"/>
       <c r="J23" s="4" t="inlineStr">
         <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>proposed relationship</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V:39.3</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 7 (deductions)</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>the Environmental Permit issued for the site</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="N27" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr">
+      <c r="O27" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A2:O27"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -31016,7 +31016,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-14 (event_day_counted, policy conservative)</t>
+          <t>2026-10-14 (event_day_counted, policy conservative) (calc deadline: ambiguous, the counting rules state nothing for Working Days counted after a date (VOL-I 2.4 covers Working Days counted backwards): not stated, so every reading is kept and a person decides)</t>
         </is>
       </c>
       <c r="H23" s="4" t="b">

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AF$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Evidence'!$A$1:$F$27</definedName>
@@ -539,7 +539,7 @@
     <row r="2" ht="210" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 37). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none; approved by the owner: VOL-II-p3-r1 (transcription), VOL-IV-p6-r1 (transcription and displayed translations); their interpretations stay proposed. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. In 'Text as issued', a segment marked '[&lt;document&gt; &lt;clause&gt; p&lt;n&gt;; issued by ADD-0x]' is that addendum's own text, not text of the volumes as issued. Evidence codes are defined in the Evidence sheet. Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
+          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 38). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none; approved by the owner: VOL-II-p3-r1 (transcription), VOL-IV-p6-r1 (transcription and displayed translations); their interpretations stay proposed. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. In 'Text as issued', a segment marked '[&lt;document&gt; &lt;clause&gt; p&lt;n&gt;; issued by ADD-0x]' is that addendum's own text, not text of the volumes as issued. Evidence codes are defined in the Evidence sheet. Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-01: ADD-01 §2.2 names this period as moving with the Proposal Due Date. dates moved: PROPOSAL-VALIDITY 2027-04-11 -&gt; 2027-04-25. by ADD-01/2.2 [ADD-01; proposed; annotates VOL-I:7.1 (interprets)] &lt;- ADD-01:2.2 (ADD-01 p1); ADD-01/2.1 [ADD-01; proposed; moves the date anchor PDD (VOL-I:6.1)] &lt;- ADD-01:2.1 (ADD-01 p1)</t>
+          <t>reading re-made at ADD-01: ADD-01 §2.2 names this period as moving with the Proposal Due Date. dates moved: PROPOSAL-VALIDITY 2027-04-11 -&gt; 2027-04-25. by ADD-01/2.2 [ADD-01; proposed; annotates VOL-I:7.1 (interprets)] &lt;- ADD-01:2.2 (ADD-01 p1); ADD-01/2.1 [ADD-01; proposed; moves the date anchor PDD (VOL-I:6.1)] &lt;- ADD-01:2.1 (ADD-01 p1); EV-FORM-4A: evidence field not on the reissued form (VOL-IV-F4A-04) (I-F4A-FIELDS)</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="AE10" s="4" t="inlineStr">
         <is>
-          <t>I-NO-CONSEQUENCE</t>
+          <t>I-NO-CONSEQUENCE; I-F4A-FIELDS (evidence field not on the reissued form (VOL-IV-F4A-04))</t>
         </is>
       </c>
       <c r="AF10" s="4" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AE20" s="4" t="inlineStr">
         <is>
-          <t>I-READING-F4C</t>
+          <t>I-READING-F4C; I-BIDDER-FACTS (via REL-MEMBER-FORM-4C (confirmed))</t>
         </is>
       </c>
       <c r="AF20" s="4" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="Z33" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 §5.1 amends 'from the value shown' (which exists only in the image) to 3 mg/l, same basis. The Environmental Permit, which prevails over the reproduction (VOL-II p3, reproduction preamble), is not in the pack; no Permit compliance is claimed, including for the amended TN limit.</t>
+          <t>ADD-02 §5.1 amends 'from the value shown' (which exists only in the image) to 3 mg/l, same basis. The Environmental Permit, which prevails over the reproduction (VOL-II p3, reproduction preamble), is not in the pack; no Permit compliance is claimed, including for the amended TN limit. Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA33" s="4" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="AE33" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF33" s="4" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="AE65" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-APPENDICES</t>
+          <t>I-VOL-I-APPENDICES; I-VOL-I-PAGE-LIMIT-Q2</t>
         </is>
       </c>
       <c r="AF65" s="4" t="inlineStr"/>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="AE95" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS; I-VOL-II-AT-ALL-TIMES</t>
         </is>
       </c>
       <c r="AF95" s="4" t="inlineStr">
@@ -13919,7 +13919,11 @@
         </is>
       </c>
       <c r="Q96" s="4" t="inlineStr"/>
-      <c r="R96" s="4" t="inlineStr"/>
+      <c r="R96" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED), so the parameters assessed 'Continuous at outlet' stay Residual Chlorine and pH. How the qualifier 'all values are maxima' applies to their ranges stays open (I-VOL-II-T24-TENSIONS; Process engineer); no decision recorded. by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/ResidualChlorine (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S96" s="4" t="inlineStr">
         <is>
           <t>VOL-II 2.5 p2</t>
@@ -13949,7 +13953,7 @@
       </c>
       <c r="Z96" s="4" t="inlineStr">
         <is>
-          <t>Which parameters are 'continuous' comes from the Table 2-4 basis column (image reading, transcription confirmed by the owner, 3 Oct 2026): Residual Chlorine and pH read 'Continuous at outlet'. Those two table rows are listed as units.</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED), so the parameters assessed 'Continuous at outlet' stay Residual Chlorine and pH. How the qualifier 'all values are maxima' applies to their ranges stays open (I-VOL-II-T24-TENSIONS; Process engineer); no decision recorded. Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA96" s="4" t="inlineStr">
@@ -13969,12 +13973,12 @@
       </c>
       <c r="AD96" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:2.5 (VOL-II p2; text layer); VOL-II:T2-4/ResidualChlorine (VOL-II p3; image reading); VOL-II:T2-4/pH (VOL-II p3; image reading)</t>
+          <t>VOL-II:2.5 (VOL-II p2; text layer); VOL-II:T2-4/ResidualChlorine (VOL-II p3; image reading); VOL-II:T2-4/pH (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/ResidualChlorine (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE96" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24</t>
+          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
         </is>
       </c>
       <c r="AF96" s="4" t="inlineStr">
@@ -14065,7 +14069,11 @@
         </is>
       </c>
       <c r="Q97" s="4" t="inlineStr"/>
-      <c r="R97" s="4" t="inlineStr"/>
+      <c r="R97" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/BOD5 (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S97" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/BOD5 p3</t>
@@ -14095,7 +14103,7 @@
       </c>
       <c r="Z97" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026). The table's qualifier 'all values are maxima' is recorded as context.</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA97" s="4" t="inlineStr">
@@ -14115,12 +14123,12 @@
       </c>
       <c r="AD97" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/BOD5 (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/BOD5 (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/BOD5 (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE97" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF97" s="4" t="inlineStr">
@@ -14211,7 +14219,11 @@
         </is>
       </c>
       <c r="Q98" s="4" t="inlineStr"/>
-      <c r="R98" s="4" t="inlineStr"/>
+      <c r="R98" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/COD (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S98" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/COD p3</t>
@@ -14241,7 +14253,7 @@
       </c>
       <c r="Z98" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA98" s="4" t="inlineStr">
@@ -14261,12 +14273,12 @@
       </c>
       <c r="AD98" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/COD (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/COD (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/COD (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE98" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF98" s="4" t="inlineStr">
@@ -14357,7 +14369,11 @@
         </is>
       </c>
       <c r="Q99" s="4" t="inlineStr"/>
-      <c r="R99" s="4" t="inlineStr"/>
+      <c r="R99" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/TSS (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S99" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/TSS p3</t>
@@ -14387,7 +14403,7 @@
       </c>
       <c r="Z99" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA99" s="4" t="inlineStr">
@@ -14407,12 +14423,12 @@
       </c>
       <c r="AD99" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/TSS (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/TSS (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/TSS (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE99" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF99" s="4" t="inlineStr">
@@ -14503,7 +14519,11 @@
         </is>
       </c>
       <c r="Q100" s="4" t="inlineStr"/>
-      <c r="R100" s="4" t="inlineStr"/>
+      <c r="R100" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/TP (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S100" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/TP p3</t>
@@ -14533,7 +14553,7 @@
       </c>
       <c r="Z100" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA100" s="4" t="inlineStr">
@@ -14553,12 +14573,12 @@
       </c>
       <c r="AD100" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/TP (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/TP (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/TP (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE100" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF100" s="4" t="inlineStr">
@@ -14649,7 +14669,11 @@
         </is>
       </c>
       <c r="Q101" s="4" t="inlineStr"/>
-      <c r="R101" s="4" t="inlineStr"/>
+      <c r="R101" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/Turbidity (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S101" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/Turbidity p3</t>
@@ -14679,7 +14703,7 @@
       </c>
       <c r="Z101" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA101" s="4" t="inlineStr">
@@ -14699,12 +14723,12 @@
       </c>
       <c r="AD101" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/Turbidity (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/Turbidity (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/Turbidity (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE101" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF101" s="4" t="inlineStr">
@@ -14795,7 +14819,11 @@
         </is>
       </c>
       <c r="Q102" s="4" t="inlineStr"/>
-      <c r="R102" s="4" t="inlineStr"/>
+      <c r="R102" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/FaecalColiforms (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S102" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/FaecalColiforms p3</t>
@@ -14825,7 +14853,7 @@
       </c>
       <c r="Z102" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026, including the limit 2.2).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA102" s="4" t="inlineStr">
@@ -14845,12 +14873,12 @@
       </c>
       <c r="AD102" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/FaecalColiforms (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/FaecalColiforms (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/FaecalColiforms (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE102" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF102" s="4" t="inlineStr">
@@ -14941,7 +14969,11 @@
         </is>
       </c>
       <c r="Q103" s="4" t="inlineStr"/>
-      <c r="R103" s="4" t="inlineStr"/>
+      <c r="R103" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. How the qualifier 'all values are maxima' applies to this range stays open (I-VOL-II-T24-TENSIONS, CQ-T24-RANGES; Process engineer); no decision recorded. by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/ResidualChlorine (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S103" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/ResidualChlorine p3</t>
@@ -14971,7 +15003,7 @@
       </c>
       <c r="Z103" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026). A range although the table says 'all values are maxima'; a continuous chlorine residual sits beside VOL-II 3.3, which permits UV-only disinfection or dechlorination. Not resolved here.</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. How the qualifier 'all values are maxima' applies to this range stays open (I-VOL-II-T24-TENSIONS, CQ-T24-RANGES; Process engineer); no decision recorded. Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA103" s="4" t="inlineStr">
@@ -14991,12 +15023,12 @@
       </c>
       <c r="AD103" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/ResidualChlorine (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/ResidualChlorine (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/ResidualChlorine (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE103" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF103" s="4" t="inlineStr">
@@ -15087,7 +15119,11 @@
         </is>
       </c>
       <c r="Q104" s="4" t="inlineStr"/>
-      <c r="R104" s="4" t="inlineStr"/>
+      <c r="R104" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. How the qualifier 'all values are maxima' applies to this range stays open (I-VOL-II-T24-TENSIONS, CQ-T24-RANGES; Process engineer); no decision recorded. by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/pH (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S104" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/pH p3</t>
@@ -15117,7 +15153,7 @@
       </c>
       <c r="Z104" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026), including the unit dash. A range although the table says 'all values are maxima'.</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. How the qualifier 'all values are maxima' applies to this range stays open (I-VOL-II-T24-TENSIONS, CQ-T24-RANGES; Process engineer); no decision recorded. Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA104" s="4" t="inlineStr">
@@ -15137,12 +15173,12 @@
       </c>
       <c r="AD104" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/pH (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/pH (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/pH (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE104" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF104" s="4" t="inlineStr">
@@ -15233,7 +15269,11 @@
         </is>
       </c>
       <c r="Q105" s="4" t="inlineStr"/>
-      <c r="R105" s="4" t="inlineStr"/>
+      <c r="R105" s="4" t="inlineStr">
+        <is>
+          <t>reading re-made at ADD-02: Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). by ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/OilGrease (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+        </is>
+      </c>
       <c r="S105" s="4" t="inlineStr">
         <is>
           <t>VOL-II T2-4/OilGrease p3</t>
@@ -15263,7 +15303,7 @@
       </c>
       <c r="Z105" s="4" t="inlineStr">
         <is>
-          <t>Read from the image (transcription confirmed by the owner, 3 Oct 2026).</t>
+          <t>Re-read at ADD-02: 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED): the value, unit and basis read at BASE are unchanged. The Environmental Permit, which prevails over the reproduction, is not supplied (I-PERMIT). Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA105" s="4" t="inlineStr">
@@ -15283,12 +15323,12 @@
       </c>
       <c r="AD105" s="4" t="inlineStr">
         <is>
-          <t>VOL-II:T2-4/OilGrease (VOL-II p3; image reading)</t>
+          <t>VOL-II:T2-4/OilGrease (VOL-II p3; image reading); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/OilGrease (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE105" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF105" s="4" t="inlineStr">
@@ -15602,7 +15642,7 @@
       </c>
       <c r="AE107" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-PROCESS-DESIGN (confirmed))</t>
         </is>
       </c>
       <c r="AF107" s="4" t="inlineStr">
@@ -17688,7 +17728,7 @@
       </c>
       <c r="AE122" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24</t>
+          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
         </is>
       </c>
       <c r="AF122" s="4" t="inlineStr">
@@ -18110,7 +18150,7 @@
       </c>
       <c r="AE125" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-III</t>
+          <t>I-VOL-III; I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="AF125" s="4" t="inlineStr"/>
@@ -20450,7 +20490,7 @@
       </c>
       <c r="AE142" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-RELIABILITY-RUN (confirmed))</t>
         </is>
       </c>
       <c r="AF142" s="4" t="inlineStr">
@@ -27853,7 +27893,7 @@
       </c>
       <c r="R194" s="4" t="inlineStr">
         <is>
-          <t>reading re-made at ADD-02: ADD-02 5.1 amends the TN limit to 3 mg/l 'assessed on the same basis' (30-day rolling average as read); the payment terms of this clause are unchanged. by ADD-02/5.1 [ADD-02; proposed] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+          <t>reading re-made at ADD-02: ADD-02 5.1 amends the TN limit to 3 mg/l 'assessed on the same basis' (30-day rolling average as read) and states 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED), so the rolling-average parameters as read stay BOD5, COD, TSS, TN and TP; the payment terms of this clause are unchanged. by ADD-02/5.1 [ADD-02; proposed] &lt;- ADD-02:5.1 (ADD-02 p1); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/BOD5 (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="S194" s="4" t="inlineStr">
@@ -27889,7 +27929,7 @@
       </c>
       <c r="Z194" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 5.1 amends the TN limit to 3 mg/l 'assessed on the same basis' (30-day rolling average as read); the payment terms of this clause are unchanged.</t>
+          <t>ADD-02 5.1 amends the TN limit to 3 mg/l 'assessed on the same basis' (30-day rolling average as read) and states 'All other parameters in Table 2-4 are unchanged.' (ADD-02 5.1, p1; op ADD-02/5.1/unchanged, confirms, PROPOSED), so the rolling-average parameters as read stay BOD5, COD, TSS, TN and TP; the payment terms of this clause are unchanged. Printed table title: 'Table 2-4 Minimum Effluent Quality Parameters at the Point of Discharge'.</t>
         </is>
       </c>
       <c r="AA194" s="4" t="inlineStr">
@@ -27909,12 +27949,12 @@
       </c>
       <c r="AD194" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:29.3 (VOL-V p3; text layer); VOL-II:T2-4/BOD5 (VOL-II p3; image reading); VOL-II:T2-4/COD (VOL-II p3; image reading); VOL-II:T2-4/TSS (VOL-II p3; image reading); VOL-II:T2-4/TN (VOL-II p3; image reading); VOL-II:T2-4/TP (VOL-II p3; image reading); ADD-01/Q6 [ADD-01; proposed; annotates VOL-V:29.3 (interprets)] &lt;- ADD-01:Q6 (ADD-01 p2); ADD-02/5.1 [ADD-02; proposed] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
+          <t>VOL-V:29.3 (VOL-V p3; text layer); VOL-II:T2-4/BOD5 (VOL-II p3; image reading); VOL-II:T2-4/COD (VOL-II p3; image reading); VOL-II:T2-4/TSS (VOL-II p3; image reading); VOL-II:T2-4/TN (VOL-II p3; image reading); VOL-II:T2-4/TP (VOL-II p3; image reading); ADD-01/Q6 [ADD-01; proposed; annotates VOL-V:29.3 (interprets)] &lt;- ADD-01:Q6 (ADD-01 p2); ADD-02/5.1 [ADD-02; proposed] &lt;- ADD-02:5.1 (ADD-02 p1); ADD-02/5.1/unchanged [ADD-02; proposed; annotates VOL-II:T2-4/BOD5 (confirms)] &lt;- ADD-02:5.1 (ADD-02 p1)</t>
         </is>
       </c>
       <c r="AE194" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24</t>
+          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed))</t>
         </is>
       </c>
       <c r="AF194" s="4" t="inlineStr">
@@ -28368,7 +28408,7 @@
       </c>
       <c r="AE197" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING; I-VOL-II-T24-TENSIONS (via REL-T24-UNAVAILABILITY (confirmed))</t>
         </is>
       </c>
       <c r="AF197" s="4" t="inlineStr">
@@ -28940,7 +28980,7 @@
       </c>
       <c r="AE201" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-PERSISTENT-BREACH</t>
+          <t>I-VOL-V-PERSISTENT-BREACH; I-VOL-V-MISSING (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH (proposed))</t>
         </is>
       </c>
       <c r="AF201" s="4" t="inlineStr">
@@ -33971,7 +34011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34097,7 +34137,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-5.4-01; VOL-I-9.4-01; VOL-I-1.4-01; VOL-I-8.1-01; VOL-I-8.2-01; VOL-I-8.4-01; VOL-I-8.4-02; VOL-I-8.8-01; VOL-I-8.9-01; VOL-I-8.10-01; VOL-I-9.1h-01; VOL-I-9.5-01; VOL-IV-F4A-06; VOL-IV-F4A-07; VOL-IV-F4B-01; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03</t>
+          <t>VOL-I-5.4-01; VOL-I-9.4-01; VOL-I-1.4-01; VOL-I-8.1-01; VOL-I-8.2-01; VOL-I-8.4-01; VOL-I-8.4-02; VOL-I-8.8-01; VOL-I-8.9-01; VOL-I-8.10-01; VOL-I-9.1h-01; VOL-I-9.5-01; VOL-IV-F4A-06; VOL-IV-F4A-07; VOL-IV-F4B-01; VOL-IV-F4C-01; VOL-IV-F4C-02; VOL-IV-F4C-03; VOL-IV-F4C-N1 (via REL-MEMBER-FORM-4C (confirmed))</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr"/>
@@ -34125,7 +34165,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-9.3-01; VOL-IV-F4A-01; ADD-01-AppA-01; VOL-IV-FORMS-01; VOL-IV-F4A-02; VOL-IV-F4A-03; VOL-IV-F4A-04; VOL-IV-F4A-05; VOL-IV-F4A-06; VOL-IV-F4A-07</t>
+          <t>VOL-I-9.3-01; VOL-IV-F4A-01; ADD-01-AppA-01; VOL-IV-FORMS-01; VOL-IV-F4A-02; VOL-IV-F4A-03; VOL-IV-F4A-04; VOL-IV-F4A-05; VOL-IV-F4A-06; VOL-IV-F4A-07; VOL-I-7.1-01 (evidence field not on the reissued form (VOL-IV-F4A-04))</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -34322,7 +34362,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: Table 2-4 is reproduced from an Environmental Permit that is not in the pack. The precedence language is in the VOL-II p3 reproduction preamble ('the Environmental Permit shall prevail'; VOL-II 2.4 incorporates the table by reference); the owner confirmed that location on 3 Oct 2026. Not confirmed, and not claimed: the Permit's contents and compliance with the Permit, including after the TN amendment (ADD-02 5.1, 3 mg/l)</t>
+          <t>HUMAN DECISION PENDING: Table 2-4 is reproduced from an Environmental Permit that is not in the pack. The precedence language is in the VOL-II p3 reproduction preamble ('the Environmental Permit shall prevail'; VOL-II 2.4 incorporates the table by reference); the owner confirmed that location on 3 Oct 2026. Not confirmed, and not claimed: the Permit's contents and compliance with the Permit, including after the TN amendment (ADD-02 5.1, 3 mg/l). Context, not binding: the pre-bid minutes record that 'the permit was under review by the regulator and that any change would be issued by Addendum.' (ADD-01 Appendix B item 5, p4); the minutes do not bind the Authority (ADD-01 3.2, p1)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -34391,7 +34431,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -34450,12 +34490,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 10.1: Envelope B holds 'only' Form 4-F and the Financial Model, yet 10.3 (model auditor's opinion) and 10.6 (financing assumptions schedule) need more documents; where they go is unstated</t>
+          <t>HUMAN DECISION PENDING: VOL-I 10.1: Envelope B holds 'only' Form 4-F and the Financial Model, yet 10.3 (model auditor's opinion) and 10.6 (financing assumptions schedule) need more documents; where they go is unstated</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -34482,12 +34522,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>VOL-I 6.2 makes any price, rate or other commercial information in Envelope A non-responsive, but Form 4-B (Envelope A) asks for each reference's contract value in SAR</t>
+          <t>HUMAN DECISION PENDING: VOL-I 6.2 makes any price, rate or other commercial information in Envelope A non-responsive, but Form 4-B (Envelope A) asks for each reference's contract value in SAR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -34615,7 +34655,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Technical lead</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -34637,17 +34677,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-MISSING</t>
+          <t>I-VOL-I-PAGE-LIMIT-Q2</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Not in the pack: the Environmental and Social Impact Assessment (ESIA; VOL-II 9.1) and the geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
+          <t>HUMAN DECISION PENDING: Page limit: ADD-02 2.1 sets 'one hundred and fifty (150) pages'; VOL-I 9.2 as amended still prints that the Form Sheets are excluded. ADD-01 Q2 answered about the '120-page limit' that 'The limit applies to the Technical Proposal narrative only.' Whether that answer still holds after ADD-02 2.1 is a decision for a person (Bid manager); no decision recorded (A2 lists it for review after ADD-02 2.1; the undefined permitted appendices are raised as CQ-PAGE-LIMIT-APPENDICES)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Technical lead</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -34657,29 +34697,25 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>CQ-VOL-III-DRAWINGS</t>
-        </is>
-      </c>
+          <t>VOL-I-9.2-01</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-T24-TENSIONS</t>
+          <t>I-VOL-II-MISSING</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; 'at all times' (VOL-II 2.4) read with those bases means continuous compliance on each parameter's own basis, which is not treated as a conflict</t>
+          <t>Not in the pack: the Environmental and Social Impact Assessment (ESIA; VOL-II 9.1) and the geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Process engineer</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -34689,29 +34725,29 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01</t>
+          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>CQ-T24-RANGES</t>
+          <t>CQ-VOL-III-DRAWINGS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-MISSING</t>
+          <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
+          <t>HUMAN DECISION PENDING: The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; the 'at all times' reading is I-VOL-II-AT-ALL-TIMES, and the point at which compliance is assessed is I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -34721,24 +34757,24 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01</t>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01; VOL-II-3.1-01 (via REL-T24-PROCESS-DESIGN (confirmed)); VOL-II-7.2-01 (via REL-T24-RELIABILITY-RUN (confirmed)); VOL-V-31.1-02 (via REL-T24-UNAVAILABILITY (confirmed)); VOL-V-29.3-01 (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); VOL-II-2.5-01 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-4.3-02 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>CQ-VOL-V-SCHEDULES</t>
+          <t>CQ-T24-RANGES</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-PERSISTENT-BREACH</t>
+          <t>I-VOL-V-MISSING</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
+          <t>HUMAN DECISION PENDING: VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -34753,29 +34789,29 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01</t>
+          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01; VOL-V-31.4-01 (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH (proposed))</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>CQ-PERSISTENT-BREACH</t>
+          <t>CQ-VOL-V-SCHEDULES</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-IV-SCALE</t>
+          <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
+          <t>HUMAN DECISION PENDING: VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -34785,39 +34821,39 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>ADD-02-T1-1-N3-01</t>
+          <t>VOL-V-31.4-01</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>CQ-SCORING-METHOD</t>
+          <t>CQ-PERSISTENT-BREACH</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
+          <t>I-VOL-II-AT-ALL-TIMES</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>HUMAN DECISION PENDING: 'at all times' (VOL-II 2.4) vs Table 2-4 assessment bases. Proposed reading (not decided): Table 2-4 gives a basis of assessment for each parameter and a general qualifier, and VOL-II 2.4 requires that the treated effluent 'shall at all times comply with the parameters set out in Table 2-4'; the assistant reads the two together as continuous compliance on each parameter's printed basis. Whether that reading holds is for the Process engineer; no decision recorded (the ranges and the reliability run are raised separately: CQ-T24-RANGES, CQ-PCOD-RELIABILITY-RUN)</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+          <t>VOL-II-2.4-01</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr"/>
@@ -34825,27 +34861,27 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
+          <t>I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>HUMAN DECISION PENDING: The point at which Table 2-4 compliance is assessed. The pack prints three candidates: the table title 'Minimum Effluent Quality Parameters at the Point of Discharge' (VOL-II p3, the Table 2-4 image); 'Continuous at outlet' (the basis of assessment of Residual Chlorine and pH, VOL-II p3); and 'the delivery point shown on Drawing 03-C-114' (VOL-II 5.1, p4; the end of the 18 km treated effluent main), on a drawing of Volume III, which is not supplied. Which point governs, and whether to raise it with the Authority before the clarification cut-off, is for the Process engineer; no decision recorded and no question drafted</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+          <t>VOL-II-T2-4-TN; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-5.1-01</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr"/>
@@ -34853,122 +34889,138 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
+          <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
+          <t>ADD-02-T1-1-N3-01</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>CQ-SCORING-METHOD</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed [context (not binding): ADD-01:AppB/item-5-effluent-standards p4 'the permit was under review by the regulator and that any change would be issued by Addendum.' (pre-bid minutes; they do not bind the Authority (ADD-01 3.2, p1))]. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare. It prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time' (ADD-01 App A p3) while ADD-01 2.1 (p1) substitutes 'Thursday 26 November 2026' in VOL-I 6.1; not corrected (a person decides: I-F4A-FIELDS)</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
@@ -34977,12 +35029,12 @@
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -35001,12 +35053,12 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: which clause governs the concession term is not stated by the Authority and is a decision for a person (Legal, I-CONCESSION; draft question CQ-CONCESSION-TERM), with what to record in Form 4-E under the Volume V note and how 'the term' in VOL-V 3.2 and 42.2 reads; no decision recorded</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare. It prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time' (ADD-01 App A p3) while ADD-01 2.1 (p1) substitutes 'Thursday 26 November 2026' in VOL-I 6.1; not corrected (a person decides: I-F4A-FIELDS)</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -35025,12 +35077,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -35049,12 +35101,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -35073,12 +35125,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/Q7: which clause governs the concession term is not stated by the Authority and is a decision for a person (Legal, I-CONCESSION; draft question CQ-CONCESSION-TERM), with what to record in Form 4-E under the Volume V note and how 'the term' in VOL-V 3.2 and 42.2 reads; no decision recorded</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -35088,7 +35140,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr"/>
@@ -35097,12 +35149,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -35112,7 +35164,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr"/>
@@ -35121,12 +35173,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE (ADD-01 3.1), BID-BOND-VALIDITY (VOL-I 6.3), PROPOSAL-VALIDITY (VOL-I 7.1), PROPOSAL-VALIDITY-F4A (Form 4-A), REFERENCE-LOOKBACK (VOL-I 8.5): every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -35136,7 +35188,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr"/>
@@ -35145,101 +35197,89 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr"/>
       <c r="F41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr"/>
       <c r="F42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE (ADD-01 3.1), BID-BOND-VALIDITY (VOL-I 6.3), PROPOSAL-VALIDITY (VOL-I 7.1), PROPOSAL-VALIDITY-F4A (Form 4-A), REFERENCE-LOOKBACK (VOL-I 8.5): every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
       <c r="F43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -35249,7 +35289,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr"/>
@@ -35257,12 +35297,12 @@
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -35277,7 +35317,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr"/>
@@ -35285,17 +35325,17 @@
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -35305,7 +35345,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr"/>
@@ -35313,12 +35353,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -35333,7 +35373,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
@@ -35341,33 +35381,117 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>I-A5-copies</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-seal-and-mark</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-deliver</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; lcc-certificate INFEASIBLE by 12 WD; assemble-envelope-a INFEASIBLE by 12 WD; copies INFEASIBLE by 12 WD; seal-and-mark INFEASIBLE by 12 WD; deliver INFEASIBLE by 12 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F48"/>
+  <autoFilter ref="A1:F51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -35539,14 +35663,14 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>proposed 22</t>
+          <t>proposed 23</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
@@ -40851,7 +40975,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr"/>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>context (not binding): ADD-01:AppB/item-5-effluent-standards p4 'the permit was under review by the regulator and that any change would be issued by Addendum.' (pre-bid minutes; they do not bind the Authority (ADD-01 3.2, p1))</t>
+        </is>
+      </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>the Environmental Permit issued for the site</t>

--- a/out/a1/a1.xlsx
+++ b/out/a1/a1.xlsx
@@ -19,12 +19,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'A1 register'!$A$4:$AI$209</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dates'!$A$1:$H$97</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Issues'!$A$1:$F$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Stages'!$A$1:$J$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Assumptions'!$A$1:$D$66</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Evidence'!$A$1:$F$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Date coverage'!$A$1:$E$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Relationships'!$A$2:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Relationships'!$A$2:$P$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -539,10 +539,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="210" customHeight="1">
+    <row r="2" ht="285" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 38). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none; approved by the owner: VOL-II-p3-r1 (transcription), VOL-IV-p6-r1 (transcription and displayed translations); their interpretations stay proposed. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. In 'Text as issued', a segment marked '[&lt;document&gt; &lt;clause&gt; p&lt;n&gt;; issued by ADD-0x]' is that addendum's own text, not text of the volumes as issued. Evidence codes are defined in the Evidence sheet. Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
+          <t>WORKING DRAFT, full register: 205 rows (review status: proposed 205; amendment ops: proposed 38). Rows and ops count as accepted only with a named person's decision bound to their current content. Image readings pending the owner's review: none; approved by the owner: VOL-II-p3-r1 (transcription), VOL-IV-p6-r1 (transcription and displayed translations); their interpretations stay proposed. Validated state: ADD-02. Pass/fail or scored: contractual_post_award = an obligation under the Project Agreement after award; not assessed at bid stage; pass_fail = a gate checked as met or not met at bid stage (a stated rejection, disqualification, non-responsiveness or exclusion, or a document the VOL-I 11.1 checks require); procedural = a step of the tender process with no stated effect on whether the Proposal stays in; scored = marked under the evaluation criteria (Table 1-1 or the financial evaluation); a shortfall loses marks. 'Change at &lt;stage&gt;' says what that addendum did to the row besides its status (the reading re-made, with its note; dates moved; the ops and annotations, with provision and page); a row whose unit an op reissued or amended elsewhere with the row's own words unchanged reads 'ACTIVE (reissued by &lt;op&gt;, unchanged)'. In 'Text as issued', a segment marked '[&lt;document&gt; &lt;clause&gt; p&lt;n&gt;; issued by ADD-0x]' is that addendum's own text, not text of the volumes as issued. The three state columns: 'Value at the validated stage' says what the row's own quoted words, cells and consequence did across the stages (unchanged, changed, amended with the quoted words unchanged, new, not in force; a deletion and a later reinstatement are both named), with each op that re-reads the row named with its kind and review ('proposed, not accepted'), never counted as a confirmation; 'Interpretation' lists the open issues on the reading (HUMAN DECISION PENDING where a person decides; an applied rule awaiting a person's confirmation; other open issues); 'Approval' says what a person has recorded for the row, its image transcription and every op on its units (an image transcription approval covers the transcription and its displayed translation only, never the interpretation). Evidence codes are defined in the Evidence sheet. Relationship status: confirmed = stated in the documents (the entry quotes the cross-reference), not confirmed by a person; proposed = inferred by a curator or a model, a person decides; possible = a weaker inference.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="AA5" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-01 by ADD-01/2.1; value as read: 'Thursday 26 November 2026'</t>
+          <t>changed at ADD-01 by ADD-01/2.1 (the quoted value); value as read: 'Thursday 26 November 2026'</t>
         </is>
       </c>
       <c r="AB5" s="4" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="AA6" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'no later than ten (10) Working Days before the Proposal Due Date'</t>
+          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'no later than ten (10) Working Days before the Proposal Due Date'</t>
         </is>
       </c>
       <c r="AB6" s="4" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="AA7" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'valid for one hundred and eighty (180) days from the Proposal Due Date'</t>
+          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'valid for one hundred and eighty (180) days from the Proposal Due Date'</t>
         </is>
       </c>
       <c r="AB7" s="4" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AA8" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/Q3 (interprets; ADD-01), ADD-02/Q8 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'in the amount of SAR 4,500,000'</t>
+          <t>unchanged since BASE; re-read by ADD-01/Q3 (interprets; proposed, not accepted; not counted as a confirmation), ADD-02/Q8 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'in the amount of SAR 4,500,000'</t>
         </is>
       </c>
       <c r="AB8" s="4" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="AA9" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/Q3 (interprets; ADD-01), ADD-02/Q8 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'issued by a bank licensed to operate in the Kingdom holding a long-term credit rating of not lower than A-'</t>
+          <t>unchanged since BASE; re-read by ADD-01/Q3 (interprets; proposed, not accepted; not counted as a confirmation), ADD-02/Q8 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'issued by a bank licensed to operate in the Kingdom holding a long-term credit rating of not lower than A-'</t>
         </is>
       </c>
       <c r="AB9" s="4" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="AA10" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'one hundred and fifty (150) days from the Proposal Due Date'</t>
+          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'one hundred and fifty (150) days from the Proposal Due Date'</t>
         </is>
       </c>
       <c r="AB10" s="4" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="AA12" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; ADD-01), ADD-01/Q5 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'at least two (2) reference sewage treatment plants, each of nominal capacity not less than 80,000 m³/day and each havin…'</t>
+          <t>unchanged since BASE; re-read by ADD-01/2.2 (interprets; proposed, not accepted; not counted as a confirmation), ADD-01/Q5 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'at least two (2) reference sewage treatment plants, each of nominal capacity not less than 80,000 m³/day and each havin…'</t>
         </is>
       </c>
       <c r="AB12" s="4" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AA13" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/4.2 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'not less than thirty-five per cent (35%) for the construction phase'</t>
+          <t>changed at ADD-02 by ADD-02/9.1 (reinstated in amended form; the quoted value, consequence differ from BASE; deleted at ADD-01 by ADD-01/4.1); re-read by ADD-01/4.2 (interprets; revoked by ADD-02/9.2; no longer in force); value as read: 'not less than thirty-five per cent (35%) for the construction phase'</t>
         </is>
       </c>
       <c r="AB13" s="4" t="inlineStr">
@@ -2502,7 +2502,7 @@
       <c r="Z15" s="4" t="inlineStr"/>
       <c r="AA15" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-01; re-read by ADD-01/3.1 (adds_obligation; ADD-01) (an annotation; not a confirmation); value as read: 'shall notify the Authority through the Portal within five (5) Working Days of this Addendum'</t>
+          <t>new at ADD-01; re-read by ADD-01/3.1 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'shall notify the Authority through the Portal within five (5) Working Days of this Addendum'</t>
         </is>
       </c>
       <c r="AB15" s="4" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AA17" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-01, but what it depends on changed (anchor date; see A2); value as read: 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time'</t>
+          <t>unchanged since BASE (unit reissued at ADD-01 by ADD-01/AppA/para1; the row's words unchanged); value as read: 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time'</t>
         </is>
       </c>
       <c r="AB17" s="4" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="AA18" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Form 4-C shall be completed in the Arabic language, signed and stamped by an authorised signatory of each member of the…'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Form 4-C shall be completed in the Arabic language, signed and stamped by an authorised signatory of each member of the…'</t>
         </is>
       </c>
       <c r="AB18" s="4" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="AA19" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'أن جميع المعلومات المقدمة في هذا العرض صحيحة وكاملة'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'أن جميع المعلومات المقدمة في هذا العرض صحيحة وكاملة'</t>
         </is>
       </c>
       <c r="AB19" s="4" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="AA20" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف'</t>
         </is>
       </c>
       <c r="AB20" s="4" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AA22" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'A named accountable security officer will be appointed for the concession period.'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'A named accountable security officer will be appointed for the concession period.'</t>
         </is>
       </c>
       <c r="AB22" s="4" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="AA23" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection.'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'Security incidents affecting the Facility will be notified to the Authority within twenty-four (24) hours of detection.'</t>
         </is>
       </c>
       <c r="AB23" s="4" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="AA24" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'An independent penetration test of the operational technology environment will be carried out annually and the report p…'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'An independent penetration test of the operational technology environment will be carried out annually and the report p…'</t>
         </is>
       </c>
       <c r="AB24" s="4" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="AA25" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'Remote access to the control system will require multi-factor authentication and will be logged.'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'Remote access to the control system will require multi-factor authentication and will be logged.'</t>
         </is>
       </c>
       <c r="AB25" s="4" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="AA26" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/4.1; value as read: 'ninety-six (96) hours'</t>
+          <t>changed at ADD-02 by ADD-02/4.1 (the quoted value); value as read: 'ninety-six (96) hours'</t>
         </is>
       </c>
       <c r="AB26" s="4" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="AA28" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/T1-1-rev/note(2); value as read: 'sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial'</t>
+          <t>changed at ADD-02 by ADD-02/T1-1-rev/note(2) (the quoted value); value as read: 'sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial'</t>
         </is>
       </c>
       <c r="AB28" s="4" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="AA29" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/Q6 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'sixty per cent (60%) of the payment indexed to the published consumer price index and forty per cent (40%) remaining fi…'</t>
+          <t>unchanged since BASE; re-read by ADD-01/Q6 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'sixty per cent (60%) of the payment indexed to the published consumer price index and forty per cent (40%) remaining fi…'</t>
         </is>
       </c>
       <c r="AB29" s="4" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="AA30" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/T1-1-rev/note(1) (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'scoring less than seventy (70) marks out of one hundred (100)'</t>
+          <t>unchanged since BASE; re-read by ADD-02/T1-1-rev/note(1) (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'scoring less than seventy (70) marks out of one hundred (100)'</t>
         </is>
       </c>
       <c r="AB30" s="4" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AA31" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/3.1; value as read: 'Marks: 15'</t>
+          <t>changed at ADD-02 by ADD-02/3.1 (the quoted value, cells); value as read: 'Marks: 15'</t>
         </is>
       </c>
       <c r="AB31" s="4" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AA32" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/3.1; value as read: 'Marks: 20'</t>
+          <t>changed at ADD-02 by ADD-02/3.1 (the quoted value, cells); value as read: 'Marks: 20'</t>
         </is>
       </c>
       <c r="AB32" s="4" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="AA33" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/5.1; value as read: 'Limit: 3'</t>
+          <t>changed at ADD-02 by ADD-02/5.1 (the quoted value, cells); value as read: 'Limit: 3'</t>
         </is>
       </c>
       <c r="AB33" s="4" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="AA34" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-01; re-read by ADD-01/cover/para3 (adds_obligation; ADD-01), ADD-02/cover/para3 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'Bidders shall acknowledge receipt in Form 4-A.'</t>
+          <t>new at ADD-01; re-read by ADD-01/cover/para3 (adds_obligation; proposed, not accepted; not counted as a confirmation), ADD-02/cover/para3 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'Bidders shall acknowledge receipt in Form 4-A.'</t>
         </is>
       </c>
       <c r="AB34" s="4" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="AA35" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-01; re-read by ADD-01/Q4 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'Bidders shall satisfy themselves as to ground conditions.'</t>
+          <t>new at ADD-01; re-read by ADD-01/Q4 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'Bidders shall satisfy themselves as to ground conditions.'</t>
         </is>
       </c>
       <c r="AB35" s="4" t="inlineStr">
@@ -5990,7 +5990,7 @@
       </c>
       <c r="AA37" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/T1-1-rev/note(3) (interprets; ADD-02) (an annotation; not a confirmation); value as read: 'Marks are awarded on the Authority's standard five-point scale and multiplied by the weight shown.'</t>
+          <t>new at ADD-02; re-read by ADD-02/T1-1-rev/note(3) (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'Marks are awarded on the Authority's standard five-point scale and multiplied by the weight shown.'</t>
         </is>
       </c>
       <c r="AB37" s="4" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AA38" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'The operational technology environment will be segregated from any business network in accordance with Volume II Clause…'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'The operational technology environment will be segregated from any business network in accordance with Volume II Clause…'</t>
         </is>
       </c>
       <c r="AB38" s="4" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="AA39" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'An information security management system covering the operational technology environment will be implemented before co…'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'An information security management system covering the operational technology environment will be implemented before co…'</t>
         </is>
       </c>
       <c r="AB39" s="4" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="AA40" s="4" t="inlineStr">
         <is>
-          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'Signed for and on behalf of the Bidder'</t>
+          <t>new at ADD-02; re-read by ADD-02/7.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'Signed for and on behalf of the Bidder'</t>
         </is>
       </c>
       <c r="AB40" s="4" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="AB50" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-VOL-I-ENV-A-PRICES (Legal)</t>
+          <t>HUMAN DECISION PENDING: I-VOL-I-ENV-A-PRICES (Legal), I-FORM-4E-COMMERCIAL-QUALIFICATION (Legal counsel)</t>
         </is>
       </c>
       <c r="AC50" s="4" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="AH50" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-I-ENV-A-PRICES</t>
+          <t>I-VOL-I-ENV-A-PRICES; I-FORM-4E-COMMERCIAL-QUALIFICATION (the issue names the row (curated, PROPOSED))</t>
         </is>
       </c>
       <c r="AI50" s="4" t="inlineStr"/>
@@ -9460,7 +9460,7 @@
       </c>
       <c r="AA59" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q10 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'The Bidder shall submit an executed Parent Company Guarantee from the ultimate parent company of the proposed EPC Contr…'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q10 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'The Bidder shall submit an executed Parent Company Guarantee from the ultimate parent company of the proposed EPC Contr…'</t>
         </is>
       </c>
       <c r="AB59" s="4" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AA63" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-02, but what it depends on changed (parameters; see A2); value as read: 'Envelope A shall contain, in the following order and separated by numbered dividers'</t>
+          <t>amended at ADD-02 by ADD-02/7.1 (an item inserted; the quoted words unchanged); value as read: 'Envelope A shall contain, in the following order and separated by numbered dividers'</t>
         </is>
       </c>
       <c r="AB63" s="4" t="inlineStr">
@@ -10446,12 +10446,12 @@
       </c>
       <c r="AA65" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/2.1; re-read by ADD-01/Q2 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'one hundred and fifty (150) pages'</t>
+          <t>changed at ADD-02 by ADD-02/2.1 (the quoted value); re-read by ADD-01/Q2 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'one hundred and fifty (150) pages'</t>
         </is>
       </c>
       <c r="AB65" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-VOL-I-PAGE-LIMIT-Q2 (Bid manager); open: I-VOL-I-APPENDICES</t>
+          <t>applied rule awaiting a person's confirmation: I-VOL-I-PAGE-LIMIT-Q2; open: I-VOL-I-APPENDICES</t>
         </is>
       </c>
       <c r="AC65" s="4" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AB67" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-CONCESSION (Legal)</t>
+          <t>HUMAN DECISION PENDING: I-CONCESSION (Legal), I-FORM-4E-COMMERCIAL-QUALIFICATION (Legal counsel), I-FORM-4E-CROSS-CHECK (Bid manager)</t>
         </is>
       </c>
       <c r="AC67" s="4" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="AH67" s="4" t="inlineStr">
         <is>
-          <t>I-CONCESSION</t>
+          <t>I-CONCESSION; I-FORM-4E-COMMERCIAL-QUALIFICATION (the issue names the row (curated, PROPOSED)); I-FORM-4E-CROSS-CHECK (the issue names the row (curated, PROPOSED))</t>
         </is>
       </c>
       <c r="AI67" s="4" t="inlineStr"/>
@@ -11877,12 +11877,12 @@
       </c>
       <c r="AA74" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q14 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Any conditional price, price subject to adjustment other than as provided in Volume V, or alternative price'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q14 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Any conditional price, price subject to adjustment other than as provided in Volume V, or alternative price'</t>
         </is>
       </c>
       <c r="AB74" s="4" t="inlineStr">
         <is>
-          <t>no open issue on the reading</t>
+          <t>HUMAN DECISION PENDING: I-FORM-4E-COMMERCIAL-QUALIFICATION (Legal counsel)</t>
         </is>
       </c>
       <c r="AC74" s="4" t="inlineStr">
@@ -11910,7 +11910,11 @@
           <t>VOL-I:10.5 (VOL-I p5; text layer); ADD-02/Q14 [ADD-02; proposed; annotates VOL-I:10.5 (confirms)] &lt;- ADD-02:Q14 (ADD-02 p2)</t>
         </is>
       </c>
-      <c r="AH74" s="4" t="inlineStr"/>
+      <c r="AH74" s="4" t="inlineStr">
+        <is>
+          <t>I-FORM-4E-COMMERCIAL-QUALIFICATION (the issue names the row (curated, PROPOSED))</t>
+        </is>
+      </c>
       <c r="AI74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
@@ -12034,7 +12038,7 @@
       </c>
       <c r="AA75" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q14 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'An alternative technical solution may be submitted only as a supplement to a fully compliant base Proposal and will be …'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q14 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'An alternative technical solution may be submitted only as a supplement to a fully compliant base Proposal and will be …'</t>
         </is>
       </c>
       <c r="AB75" s="4" t="inlineStr">
@@ -12509,7 +12513,7 @@
       </c>
       <c r="AA78" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; value as read: 'Marks: 25'</t>
+          <t>unchanged since BASE (unit reissued at ADD-02 by ADD-02/3.1; the row's words unchanged); value as read: 'Marks: 25'</t>
         </is>
       </c>
       <c r="AB78" s="4" t="inlineStr">
@@ -12666,7 +12670,7 @@
       </c>
       <c r="AA79" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; value as read: 'Marks: 20'</t>
+          <t>unchanged since BASE (unit reissued at ADD-02 by ADD-02/3.1; the row's words unchanged); value as read: 'Marks: 20'</t>
         </is>
       </c>
       <c r="AB79" s="4" t="inlineStr">
@@ -12823,7 +12827,7 @@
       </c>
       <c r="AA80" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; value as read: 'Marks: 10'</t>
+          <t>unchanged since BASE (unit reissued at ADD-02 by ADD-02/3.1; the row's words unchanged); value as read: 'Marks: 10'</t>
         </is>
       </c>
       <c r="AB80" s="4" t="inlineStr">
@@ -12980,7 +12984,7 @@
       </c>
       <c r="AA81" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; value as read: 'Marks: 10'</t>
+          <t>unchanged since BASE (unit reissued at ADD-02 by ADD-02/3.1; the row's words unchanged); value as read: 'Marks: 10'</t>
         </is>
       </c>
       <c r="AB81" s="4" t="inlineStr">
@@ -13141,7 +13145,7 @@
       </c>
       <c r="AA82" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q7 (interprets; ADD-02) (an annotation; not a confirmation); value as read: 'The concession period shall be twenty-five (25) years commencing on the Project Commercial Operation Date, following wh…'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q7 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'The concession period shall be twenty-five (25) years commencing on the Project Commercial Operation Date, following wh…'</t>
         </is>
       </c>
       <c r="AB82" s="4" t="inlineStr">
@@ -13306,7 +13310,7 @@
       </c>
       <c r="AA83" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q13 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q13 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'The Preferred Bidder shall achieve Commercial Close within one hundred and twenty (120) days'</t>
         </is>
       </c>
       <c r="AB83" s="4" t="inlineStr">
@@ -13471,7 +13475,7 @@
       </c>
       <c r="AA84" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q13 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q13 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Financial Close within two hundred and seventy (270) days, of the date of the Preferred Bidder Notification'</t>
         </is>
       </c>
       <c r="AB84" s="4" t="inlineStr">
@@ -15177,7 +15181,7 @@
       </c>
       <c r="AB95" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC95" s="4" t="inlineStr">
@@ -15207,7 +15211,7 @@
       </c>
       <c r="AH95" s="4" t="inlineStr">
         <is>
-          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS; I-VOL-II-AT-ALL-TIMES</t>
+          <t>I-PERMIT; I-READING-T24; I-VOL-II-T24-TENSIONS; I-VOL-II-AT-ALL-TIMES; I-VOL-II-COMPLIANCE-POINT (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
         </is>
       </c>
       <c r="AI95" s="4" t="inlineStr">
@@ -15341,12 +15345,12 @@
       </c>
       <c r="AA96" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-02, but what it depends on changed (dependency; see A2); re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'shall install continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous bas…'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'shall install continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous bas…'</t>
         </is>
       </c>
       <c r="AB96" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-VOL-II-T24-TENSIONS (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer), I-PERMIT (Technical); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC96" s="4" t="inlineStr">
@@ -15376,12 +15380,12 @@
       </c>
       <c r="AH96" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
+          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-CONTINUOUS-MONITORING (confirmed)); I-VOL-II-AT-ALL-TIMES (via REL-T24-CONTINUOUS-MONITORING (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-CONTINUOUS-MONITORING (confirmed)); I-PERMIT (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-CONTINUOUS-MONITORING (confirmed))</t>
         </is>
       </c>
       <c r="AI96" s="4" t="inlineStr">
         <is>
-          <t>&lt;- REL-T24-COMPLIANCE-MONITORING-STREAMS [confirmed limit_applies] from VOL-II:T2-4; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-COMPLIANCE-MONITORING-STREAMS</t>
+          <t>&lt;- REL-T24-CONTINUOUS-MONITORING [confirmed limit_applies] from VOL-II:T2-4</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15510,7 @@
       </c>
       <c r="AA97" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 10'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 10'</t>
         </is>
       </c>
       <c r="AB97" s="4" t="inlineStr">
@@ -15671,7 +15675,7 @@
       </c>
       <c r="AA98" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 50'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 50'</t>
         </is>
       </c>
       <c r="AB98" s="4" t="inlineStr">
@@ -15836,7 +15840,7 @@
       </c>
       <c r="AA99" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 10'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 10'</t>
         </is>
       </c>
       <c r="AB99" s="4" t="inlineStr">
@@ -16001,7 +16005,7 @@
       </c>
       <c r="AA100" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 1'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 1'</t>
         </is>
       </c>
       <c r="AB100" s="4" t="inlineStr">
@@ -16166,7 +16170,7 @@
       </c>
       <c r="AA101" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 2'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 2'</t>
         </is>
       </c>
       <c r="AB101" s="4" t="inlineStr">
@@ -16331,7 +16335,7 @@
       </c>
       <c r="AA102" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 2.2'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 2.2'</t>
         </is>
       </c>
       <c r="AB102" s="4" t="inlineStr">
@@ -16496,7 +16500,7 @@
       </c>
       <c r="AA103" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 0.5 - 1.0'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 0.5 - 1.0'</t>
         </is>
       </c>
       <c r="AB103" s="4" t="inlineStr">
@@ -16661,7 +16665,7 @@
       </c>
       <c r="AA104" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 6.0 - 9.0'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 6.0 - 9.0'</t>
         </is>
       </c>
       <c r="AB104" s="4" t="inlineStr">
@@ -16826,7 +16830,7 @@
       </c>
       <c r="AA105" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'Limit: 1'</t>
+          <t>unchanged since BASE; re-read by ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'Limit: 1'</t>
         </is>
       </c>
       <c r="AB105" s="4" t="inlineStr">
@@ -17170,12 +17174,12 @@
       </c>
       <c r="AA107" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-02, but what it depends on changed (dependency; see A2); re-read by ADD-01/Q1 (interprets; ADD-01), ADD-02/5.2 (adds_obligation; ADD-02) (an annotation; not a confirmation); value as read: 'The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditi…'</t>
+          <t>own words unchanged at ADD-02, but what it depends on changed (dependency; see A2); re-read by ADD-01/Q1 (interprets; proposed, not accepted; not counted as a confirmation), ADD-02/5.2 (adds_obligation; proposed, not accepted; not counted as a confirmation); value as read: 'The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditi…'</t>
         </is>
       </c>
       <c r="AB107" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC107" s="4" t="inlineStr">
@@ -17205,7 +17209,7 @@
       </c>
       <c r="AH107" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-PROCESS-DESIGN (confirmed))</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-PROCESS-DESIGN (confirmed)); I-VOL-II-AT-ALL-TIMES (via REL-T24-PROCESS-DESIGN (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-PROCESS-DESIGN (confirmed))</t>
         </is>
       </c>
       <c r="AI107" s="4" t="inlineStr">
@@ -19175,7 +19179,7 @@
       </c>
       <c r="AA120" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q11 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'shall satisfy itself as to the consistency of the flow figures stated in this Volume and shall raise any inconsistency …'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q11 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'shall satisfy itself as to the consistency of the flow figures stated in this Volume and shall raise any inconsistency …'</t>
         </is>
       </c>
       <c r="AB120" s="4" t="inlineStr">
@@ -19486,7 +19490,7 @@
       </c>
       <c r="AB122" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-VOL-II-T24-TENSIONS (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer), I-PERMIT (Technical); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC122" s="4" t="inlineStr">
@@ -19516,7 +19520,7 @@
       </c>
       <c r="AH122" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
+          <t>I-READING-T24; I-VOL-II-T24-TENSIONS (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); I-VOL-II-AT-ALL-TIMES (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); I-PERMIT (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
         </is>
       </c>
       <c r="AI122" s="4" t="inlineStr">
@@ -19646,7 +19650,7 @@
       </c>
       <c r="AA123" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/4.1; value as read: 'Standby provision for all rotating equipment shall be N+1.'</t>
+          <t>unchanged since BASE (unit amended elsewhere at ADD-02 by ADD-02/4.1; the row's words unchanged); value as read: 'Standby provision for all rotating equipment shall be N+1.'</t>
         </is>
       </c>
       <c r="AB123" s="4" t="inlineStr">
@@ -20429,7 +20433,7 @@
       </c>
       <c r="AA128" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-01 by ADD-01/5.1; value as read: 'Glass reinforced plastic pipe of an equivalent pressure class is acceptable for the buried sections of the transmission…'</t>
+          <t>changed at ADD-01 by ADD-01/5.1 (the quoted value); value as read: 'Glass reinforced plastic pipe of an equivalent pressure class is acceptable for the buried sections of the transmission…'</t>
         </is>
       </c>
       <c r="AB128" s="4" t="inlineStr">
@@ -20586,7 +20590,7 @@
       </c>
       <c r="AA129" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-01 by ADD-01/5.1; value as read: 'with a minimum nominal diameter of DN1200'</t>
+          <t>unchanged since BASE (unit amended elsewhere at ADD-01 by ADD-01/5.1; the row's words unchanged); value as read: 'with a minimum nominal diameter of DN1200'</t>
         </is>
       </c>
       <c r="AB129" s="4" t="inlineStr">
@@ -22548,7 +22552,7 @@
       </c>
       <c r="AB142" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC142" s="4" t="inlineStr">
@@ -22578,7 +22582,7 @@
       </c>
       <c r="AH142" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-RELIABILITY-RUN (confirmed))</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-II-T24-TENSIONS (via REL-T24-RELIABILITY-RUN (confirmed)); I-VOL-II-AT-ALL-TIMES (via REL-T24-RELIABILITY-RUN (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-RELIABILITY-RUN (confirmed))</t>
         </is>
       </c>
       <c r="AI142" s="4" t="inlineStr">
@@ -25202,7 +25206,7 @@
       </c>
       <c r="AA159" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-01, but what it depends on changed (cited units, anchor date; see A2); value as read: 'Name of Bidder / lead member:'</t>
+          <t>amended at ADD-01 by ADD-01/AppA/para1 (the unit reissued; the quoted words unchanged); value as read: 'Name of Bidder / lead member:'</t>
         </is>
       </c>
       <c r="AB159" s="4" t="inlineStr">
@@ -26355,7 +26359,7 @@
       </c>
       <c r="AA166" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'أنه لا يوجد أي تضارب في المصالح، فعلي أو محتمل، بيننا وبين الهيئة أو أي من مستشاريها فيما يتعلق بهذا المشروع'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'أنه لا يوجد أي تضارب في المصالح، فعلي أو محتمل، بيننا وبين الهيئة أو أي من مستشاريها فيما يتعلق بهذا المشروع'</t>
         </is>
       </c>
       <c r="AB166" s="4" t="inlineStr">
@@ -26516,7 +26520,7 @@
       </c>
       <c r="AA167" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة'</t>
         </is>
       </c>
       <c r="AB167" s="4" t="inlineStr">
@@ -26681,7 +26685,7 @@
       </c>
       <c r="AA168" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'أن الشركة غير مدرجة، ولم تكن مدرجة خلال الخمس سنوات السابقة، في أي قائمة حظر صادرة عن جهة حكومية في المملكة'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'أن الشركة غير مدرجة، ولم تكن مدرجة خلال الخمس سنوات السابقة، في أي قائمة حظر صادرة عن جهة حكومية في المملكة'</t>
         </is>
       </c>
       <c r="AB168" s="4" t="inlineStr">
@@ -26846,7 +26850,7 @@
       </c>
       <c r="AA169" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'نلتزم بقواعد الاتصال المنصوص عليها في البند ٤-٢ من المجلد الأول'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q9 (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'نلتزم بقواعد الاتصال المنصوص عليها في البند ٤-٢ من المجلد الأول'</t>
         </is>
       </c>
       <c r="AB169" s="4" t="inlineStr">
@@ -28256,7 +28260,7 @@
       </c>
       <c r="AB178" s="4" t="inlineStr">
         <is>
-          <t>open: I-NO-CONSEQUENCE</t>
+          <t>HUMAN DECISION PENDING: I-VOL-V-MISSING (Legal counsel), I-VOL-V-PERSISTENT-BREACH (Legal counsel), I-FORM-4E-COMMERCIAL-QUALIFICATION (Legal counsel), I-FORM-4E-CROSS-CHECK (Bid manager); open: I-NO-CONSEQUENCE</t>
         </is>
       </c>
       <c r="AC178" s="4" t="inlineStr">
@@ -28286,7 +28290,7 @@
       </c>
       <c r="AH178" s="4" t="inlineStr">
         <is>
-          <t>I-NO-CONSEQUENCE</t>
+          <t>I-NO-CONSEQUENCE; I-VOL-V-MISSING (via REL-MISSING-SCHEDULE-11-LATE-COMPLETION &gt; REL-VOL-V-FORM-4E (confirmed); via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH &gt; REL-VOL-V-FORM-4E (proposed)); I-VOL-V-PERSISTENT-BREACH (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH &gt; REL-VOL-V-FORM-4E (proposed)); I-FORM-4E-COMMERCIAL-QUALIFICATION (the issue names the row (curated, PROPOSED)); I-FORM-4E-CROSS-CHECK (the issue names the row (curated, PROPOSED))</t>
         </is>
       </c>
       <c r="AI178" s="4" t="inlineStr">
@@ -28608,7 +28612,7 @@
       </c>
       <c r="AB180" s="4" t="inlineStr">
         <is>
-          <t>open: I-NO-CONSEQUENCE</t>
+          <t>HUMAN DECISION PENDING: I-FORM-4E-COMMERCIAL-QUALIFICATION (Legal counsel); open: I-NO-CONSEQUENCE</t>
         </is>
       </c>
       <c r="AC180" s="4" t="inlineStr">
@@ -28638,7 +28642,7 @@
       </c>
       <c r="AH180" s="4" t="inlineStr">
         <is>
-          <t>I-NO-CONSEQUENCE</t>
+          <t>I-NO-CONSEQUENCE; I-FORM-4E-COMMERCIAL-QUALIFICATION (the issue names the row (curated, PROPOSED))</t>
         </is>
       </c>
       <c r="AI180" s="4" t="inlineStr">
@@ -28933,7 +28937,7 @@
       </c>
       <c r="AA182" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-02/Q7 (interprets; ADD-02) (an annotation; not a confirmation); value as read: 'shall continue for a period of twenty-five (25) years from the Effective Date'</t>
+          <t>unchanged since BASE; re-read by ADD-02/Q7 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'shall continue for a period of twenty-five (25) years from the Effective Date'</t>
         </is>
       </c>
       <c r="AB182" s="4" t="inlineStr">
@@ -30787,12 +30791,12 @@
       </c>
       <c r="AA194" s="4" t="inlineStr">
         <is>
-          <t>own words unchanged at ADD-02, but what it depends on changed (cited units; see A2); re-read by ADD-01/Q6 (interprets; ADD-01), ADD-02/5.1/unchanged (confirms; ADD-02) (an annotation; not a confirmation); value as read: 'During the first twelve (12) months after PCOD (the Ramp-Up Period) the Availability Payment shall be paid at ninety pe…'</t>
+          <t>own words unchanged at ADD-02, but what it depends on changed (cited units; see A2); re-read by ADD-01/Q6 (interprets; proposed, not accepted; not counted as a confirmation), ADD-02/5.1/unchanged (confirms; proposed, not accepted; not counted as a confirmation); value as read: 'During the first twelve (12) months after PCOD (the Ramp-Up Period) the Availability Payment shall be paid at ninety pe…'</t>
         </is>
       </c>
       <c r="AB194" s="4" t="inlineStr">
         <is>
-          <t>open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer), I-PERMIT (Technical); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC194" s="4" t="inlineStr">
@@ -30822,12 +30826,12 @@
       </c>
       <c r="AH194" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24</t>
+          <t>I-READING-T24; I-VOL-II-AT-ALL-TIMES (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); I-PERMIT (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-RAMP-UP-DEDUCTIONS (confirmed))</t>
         </is>
       </c>
       <c r="AI194" s="4" t="inlineStr">
         <is>
-          <t>&lt;- REL-T24-RAMP-UP-DEDUCTIONS [confirmed limit_applies] from VOL-II:T2-4; issue I-VOL-II-T24-TENSIONS not carried by REL-T24-RAMP-UP-DEDUCTIONS: the relationship's scope is the members of VOL-II:T2-4 whose words carry 'rolling average' (its evidence: 'no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis'): BOD5, COD, TN, TP, TSS; the issue's subject is ResidualChlorine, pH; REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RAMP-UP-DEDUCTIONS</t>
+          <t>&lt;- REL-T24-RAMP-UP-DEDUCTIONS [confirmed limit_applies] from VOL-II:T2-4; issue I-VOL-II-T24-TENSIONS not carried by REL-T24-RAMP-UP-DEDUCTIONS: the relationship's scope is the members of VOL-II:T2-4 whose words carry 'rolling average' (its evidence: 'no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis'): BOD5, COD, TN, TP, TSS; the issue's subject is ResidualChlorine, pH (scope PROPOSED, not reviewed; the owner may keep the issue on the row); REACHED at ADD-02 (confirmed dependency): from VOL-II:T2-4 via REL-T24-RAMP-UP-DEDUCTIONS</t>
         </is>
       </c>
     </row>
@@ -30956,7 +30960,7 @@
       </c>
       <c r="AA195" s="4" t="inlineStr">
         <is>
-          <t>unchanged since BASE; re-read by ADD-01/Q6 (interprets; ADD-01) (an annotation; not a confirmation); value as read: 'Invoices shall be submitted within ten (10) Working Days of each month end'</t>
+          <t>unchanged since BASE; re-read by ADD-01/Q6 (interprets; proposed, not accepted; not counted as a confirmation); value as read: 'Invoices shall be submitted within ten (10) Working Days of each month end'</t>
         </is>
       </c>
       <c r="AB195" s="4" t="inlineStr">
@@ -31291,7 +31295,7 @@
       </c>
       <c r="AB197" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-V-MISSING (Legal counsel), I-VOL-II-T24-TENSIONS (Process engineer); open: I-READING-T24</t>
+          <t>HUMAN DECISION PENDING: I-PERMIT (Technical), I-VOL-V-MISSING (Legal counsel), I-VOL-II-T24-TENSIONS (Process engineer), I-VOL-II-AT-ALL-TIMES (Process engineer), I-VOL-II-COMPLIANCE-POINT (Process engineer); open: I-READING-T24</t>
         </is>
       </c>
       <c r="AC197" s="4" t="inlineStr">
@@ -31321,7 +31325,7 @@
       </c>
       <c r="AH197" s="4" t="inlineStr">
         <is>
-          <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING; I-VOL-II-T24-TENSIONS (via REL-T24-UNAVAILABILITY (confirmed))</t>
+          <t>I-READING-T24; I-PERMIT; I-VOL-V-MISSING; I-VOL-II-T24-TENSIONS (via REL-T24-UNAVAILABILITY (confirmed)); I-VOL-II-AT-ALL-TIMES (via REL-T24-UNAVAILABILITY (confirmed)); I-VOL-II-COMPLIANCE-POINT (via REL-T24-UNAVAILABILITY (confirmed))</t>
         </is>
       </c>
       <c r="AI197" s="4" t="inlineStr">
@@ -32244,7 +32248,7 @@
       </c>
       <c r="AA203" s="4" t="inlineStr">
         <is>
-          <t>changed at ADD-02 by ADD-02/8.1; value as read: 'SAR 2,500,000'</t>
+          <t>changed at ADD-02 by ADD-02/8.1 (the quoted value); value as read: 'SAR 2,500,000'</t>
         </is>
       </c>
       <c r="AB203" s="4" t="inlineStr">
@@ -37104,7 +37108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -37470,7 +37474,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-T2-4-TN; ADD-02-5.2-01; VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1; VOL-II-3.1-01; VOL-II-7.2-01; VOL-V-31.1-02</t>
+          <t>VOL-II-T2-4-TN; ADD-02-5.2-01; VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1; VOL-II-3.1-01; VOL-II-7.2-01; VOL-V-31.1-02; VOL-V-29.3-01 (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); VOL-II-4.3-02 (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-2.5-01 (via REL-MISSING-ENVIRONMENTAL-PERMIT &gt; REL-T24-CONTINUOUS-MONITORING (confirmed))</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -37775,7 +37779,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: Page limit: ADD-02 2.1 sets 'one hundred and fifty (150) pages'; VOL-I 9.2 as amended still prints that the Form Sheets are excluded. ADD-01 Q2 answered about the '120-page limit' that 'The limit applies to the Technical Proposal narrative only.' Whether that answer still holds after ADD-02 2.1 is a decision for a person (Bid manager); no decision recorded (A2 lists it for review after ADD-02 2.1; the undefined permitted appendices are raised as CQ-PAGE-LIMIT-APPENDICES)</t>
+          <t>PROPOSED BASIS (applied rule; a person confirms the application): applied rule: VOL-I 9.2 as amended by ADD-02 2.1 'The Technical Proposal narrative shall not exceed one hundred and fifty (150) pages of A4, excluding the Form Sheets and the appendices expressly permitted by Volume II.'; a person confirms the application VOL-I 9.2 as amended by ADD-02 2.1 provides: 'The Technical Proposal narrative shall not exceed one hundred and fifty (150) pages of A4, excluding the Form Sheets and the appendices expressly permitted by Volume II.' (applied, not decided) Page limit: ADD-02 2.1 (p1) substitutes 'one hundred and fifty (150) pages' and leaves the other words of VOL-I 9.2 (p5) as printed (ADD-02 p1: 'All other terms of the RFP Documents remain unchanged.'). ADD-01 Q2 (p1), asked about the '120-page limit', answered 'The limit applies to the Technical Proposal narrative only. Form Sheets and the appendices permitted by Volume II are excluded.', words VOL-I 9.2 as amended still prints. Proposed basis: Q2's answer restates the clause's unchanged words, so it still holds at 150 pages; the Bid manager confirms the application (no decision recorded; A2 lists 9.2 for review after ADD-02 2.1; the undefined permitted appendices stay raised as CQ-PAGE-LIMIT-APPENDICES)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -37798,17 +37802,17 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-MISSING</t>
+          <t>I-FORM-4E-COMMERCIAL-QUALIFICATION</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Not in the pack: the Environmental and Social Impact Assessment (ESIA; VOL-II 9.1) and the geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
+          <t>HUMAN DECISION PENDING: Form 4-E and a qualification of a commercial term of Volume V. VOL-I 9.6 (p5): 'Form 4-E shall list every deviation, qualification or reservation to Volume V. A Proposal that states ‘no deviations’ in Form 4-E while containing a qualification elsewhere in the Proposal shall be treated as non-responsive.' Form 4-E is in Envelope A (VOL-I 9.1, p4: '(e) Form 4-E — Schedule of Deviations;'), and VOL-I 6.2 (p3): 'The appearance of any price, rate, or other commercial information within Envelope A shall render the Proposal non-responsive.' Stated in Envelope B instead, a qualification of a price meets VOL-I 10.5 (p5): 'Any conditional price, price subject to adjustment other than as provided in Volume V, or alternative price shall render the Proposal non-responsive.' and Form 4-F (VOL-IV p9): 'is not subject to any qualification'. Whether a qualification of a commercial term of Volume V can be made at all, and how Form 4-E words it without commercial information, is a decision for Legal counsel, with Commercial; no decision recorded and no question drafted. Raised by the Form 4-E check (A5 form_4e_checks, its commercial-qualification finding)</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Technical lead</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -37818,29 +37822,25 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>CQ-VOL-III-DRAWINGS</t>
-        </is>
-      </c>
+          <t>VOL-IV-F4E-01 (the issue names the row (curated, PROPOSED)); VOL-I-9.6-01 (the issue names the row (curated, PROPOSED)); VOL-I-10.5-01 (the issue names the row (curated, PROPOSED)); VOL-I-6.2-02 (the issue names the row (curated, PROPOSED)); VOL-IV-F4F-02 (the issue names the row (curated, PROPOSED))</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-T24-TENSIONS</t>
+          <t>I-FORM-4E-CROSS-CHECK</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; the 'at all times' reading is I-VOL-II-AT-ALL-TIMES, and the point at which compliance is assessed is I-VOL-II-COMPLIANCE-POINT</t>
+          <t>HUMAN DECISION PENDING: How Form 4-E is cross-checked against the rest of the Proposal. VOL-I 9.6 (p5): 'A Proposal that states ‘no deviations’ in Form 4-E while containing a qualification elsewhere in the Proposal shall be treated as non-responsive.' The Form 4-E check (A5 form_4e_checks, its cross-check finding) lists the Proposal documents that are final only after Form 4-E starts, so a qualification in them cannot be checked against its declaration, and computes whether making Form 4-E wait for all of them is feasible on the assumed durations (INFEASIBLE on the programme of 7 Oct 2026). How the cross-check is done (a later final read of every document, a different order, or a change of a lead time) is a decision for the Bid manager, with Legal; no decision recorded; no duration, setting or dependency is changed</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Process engineer</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -37850,29 +37850,25 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01; VOL-II-3.1-01 (via REL-T24-PROCESS-DESIGN (confirmed)); VOL-II-7.2-01 (via REL-T24-RELIABILITY-RUN (confirmed)); VOL-V-31.1-02 (via REL-T24-UNAVAILABILITY (confirmed)); VOL-II-2.5-01 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-4.3-02 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed))</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>CQ-T24-RANGES</t>
-        </is>
-      </c>
+          <t>VOL-IV-F4E-01 (the issue names the row (curated, PROPOSED)); VOL-I-9.6-01 (the issue names the row (curated, PROPOSED))</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-MISSING</t>
+          <t>I-VOL-II-MISSING</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
+          <t>Not in the pack: the Environmental and Social Impact Assessment (ESIA; VOL-II 9.1) and the geotechnical report (ADD-01 Q4), both 'in the data room'; tie-in points (1.3); asset register format (7.4). ESIA compliance and ground risk unverifiable</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Technical lead</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -37882,29 +37878,29 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01; VOL-V-31.4-01 (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH (proposed))</t>
+          <t>VOL-II-1.3-01; VOL-II-5.4-01; VOL-II-7.4-01; VOL-II-9.1-01</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>CQ-VOL-V-SCHEDULES</t>
+          <t>CQ-VOL-III-DRAWINGS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-PERSISTENT-BREACH</t>
+          <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
+          <t>HUMAN DECISION PENDING: The printed qualifier is confirmed (owner, 3 Oct 2026): 'all values are maxima; compliance assessed as a 30-day rolling average unless stated'. Unresolved: how it interacts with the chlorine (0.5-1.0 mg/l) and pH (6.0-9.0) ranges, and a chlorine residual 'continuous at outlet' vs UV-only disinfection or dechlorination allowed by VOL-II 3.3 (draft question CQ-T24-RANGES). Each parameter keeps its own printed basis of assessment; the 'at all times' reading is I-VOL-II-AT-ALL-TIMES, and the point at which compliance is assessed is I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -37914,29 +37910,29 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01</t>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-3.3-01; VOL-II-3.1-01 (via REL-T24-PROCESS-DESIGN (confirmed)); VOL-II-7.2-01 (via REL-T24-RELIABILITY-RUN (confirmed)); VOL-V-31.1-02 (via REL-T24-UNAVAILABILITY (confirmed)); VOL-II-4.3-02 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-2.5-01 (via REL-T24-CONTINUOUS-MONITORING (confirmed))</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>CQ-PERSISTENT-BREACH</t>
+          <t>CQ-T24-RANGES</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-AT-ALL-TIMES</t>
+          <t>I-VOL-V-MISSING</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: 'at all times' (VOL-II 2.4) vs Table 2-4 assessment bases. Proposed reading (not decided): Table 2-4 gives a basis of assessment for each parameter and a general qualifier, and VOL-II 2.4 requires that the treated effluent 'shall at all times comply with the parameters set out in Table 2-4'; the assistant reads the two together as continuous compliance on each parameter's printed basis. Whether that reading holds is for the Process engineer; no decision recorded (the ranges and the reliability run are raised separately: CQ-T24-RANGES, CQ-PCOD-RELIABILITY-RUN)</t>
+          <t>HUMAN DECISION PENDING: VOL-V is an extract: omitted clauses, Schedules 7 (deductions), 9 (indexation), 11 (defaults), 12 (termination sums) and the Direct Agreement are not supplied, yet unlisted deviations are accepted</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Process engineer</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -37946,25 +37942,29 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr"/>
+          <t>VOL-V-NOTE-01; VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03; VOL-V-39.1-01; VOL-V-31.4-01 (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH (proposed)); VOL-IV-F4E-01 (via REL-MISSING-SCHEDULE-11-LATE-COMPLETION &gt; REL-VOL-V-FORM-4E (confirmed); via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH &gt; REL-VOL-V-FORM-4E (proposed))</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>CQ-VOL-V-SCHEDULES</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-II-COMPLIANCE-POINT</t>
+          <t>I-VOL-V-PERSISTENT-BREACH</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>HUMAN DECISION PENDING: The point at which Table 2-4 compliance is assessed. The pack prints three candidates: the table title 'Minimum Effluent Quality Parameters at the Point of Discharge' (VOL-II p3, the Table 2-4 image); 'Continuous at outlet' (the basis of assessment of Residual Chlorine and pH, VOL-II p3); and 'the delivery point shown on Drawing 03-C-114' (VOL-II 5.1, p4; the end of the 18 km treated effluent main), on a drawing of Volume III, which is not supplied. Which point governs, and whether to raise it with the Authority before the clarification cut-off, is for the Process engineer; no decision recorded and no question drafted</t>
+          <t>HUMAN DECISION PENDING: VOL-V 31.4: 'on a second occurrence' is not defined (a second persistent breach, or a further event after the remediation plan); the termination right in 39.3 turns on it</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Process engineer</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -37974,25 +37974,29 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-T2-4-TN; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-5.1-01</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr"/>
+          <t>VOL-V-31.4-01; VOL-IV-F4E-01 (via REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH &gt; REL-VOL-V-FORM-4E (proposed))</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>CQ-PERSISTENT-BREACH</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-IV-SCALE</t>
+          <t>I-VOL-II-AT-ALL-TIMES</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
+          <t>HUMAN DECISION PENDING: 'at all times' (VOL-II 2.4) vs Table 2-4 assessment bases. Proposed reading (not decided): Table 2-4 gives a basis of assessment for each parameter and a general qualifier, and VOL-II 2.4 requires that the treated effluent 'shall at all times comply with the parameters set out in Table 2-4'; the assistant reads the two together as continuous compliance on each parameter's printed basis. Whether that reading holds is for the Process engineer; no decision recorded (the ranges and the reliability run are raised separately: CQ-T24-RANGES, CQ-PCOD-RELIABILITY-RUN)</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -38002,39 +38006,35 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>ADD-02-T1-1-N3-01</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>CQ-SCORING-METHOD</t>
-        </is>
-      </c>
+          <t>VOL-II-2.4-01; VOL-II-3.1-01 (via REL-T24-PROCESS-DESIGN (confirmed)); VOL-II-7.2-01 (via REL-T24-RELIABILITY-RUN (confirmed)); VOL-V-31.1-02 (via REL-T24-UNAVAILABILITY (confirmed)); VOL-V-29.3-01 (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); VOL-II-4.3-02 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-2.5-01 (via REL-T24-CONTINUOUS-MONITORING (confirmed))</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
+          <t>I-VOL-II-COMPLIANCE-POINT</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed [context (not binding): ADD-01:AppB/item-5-effluent-standards p4 'the permit was under review by the regulator and that any change would be issued by Addendum.' (pre-bid minutes; they do not bind the Authority (ADD-01 3.2, p1))]. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>HUMAN DECISION PENDING: The point at which Table 2-4 compliance is assessed. The pack prints three candidates: the table title 'Minimum Effluent Quality Parameters at the Point of Discharge' (VOL-II p3, the Table 2-4 image); 'Continuous at outlet' (the basis of assessment of Residual Chlorine and pH, VOL-II p3); and 'the delivery point shown on Drawing 03-C-114' (VOL-II 5.1, p4; the end of the 18 km treated effluent main), on a drawing of Volume III, which is not supplied. Which point governs, and whether to raise it with the Authority before the clarification cut-off, is for the Process engineer; no decision recorded and no question drafted</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Technical</t>
+          <t>Process engineer</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
+          <t>VOL-II-T2-4-TN; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-5.1-01; VOL-II-3.1-01 (via REL-T24-PROCESS-DESIGN (confirmed)); VOL-II-7.2-01 (via REL-T24-RELIABILITY-RUN (confirmed)); VOL-V-31.1-02 (via REL-T24-UNAVAILABILITY (confirmed)); VOL-V-29.3-01 (via REL-T24-RAMP-UP-DEDUCTIONS (confirmed)); VOL-II-2.4-01 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-4.3-02 (via REL-T24-COMPLIANCE-MONITORING-STREAMS (confirmed)); VOL-II-2.5-01 (via REL-T24-CONTINUOUS-MONITORING (confirmed))</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr"/>
@@ -38042,45 +38042,49 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
+          <t>I-VOL-IV-SCALE</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>ADD-02 note (3) to Table 1-1: marks on the Authority's 'standard five-point scale' multiplied by 'the weight shown'; the scale is not in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>relationships (automatic)</t>
+          <t>curated (proposed wording)</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr"/>
+          <t>ADD-02-T1-1-N3-01</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>CQ-SCORING-METHOD</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
+          <t>I-AUTO-NOT-SUPPLIED-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
+          <t>the Environmental Permit issued for the site is referenced but not supplied (referenced in VOL-II 2.4, VOL-II T2-4-heading/para1). Without it these conclusions cannot be established: VOL-II-2.4-01, VOL-II-T2-4-BOD5, VOL-II-T2-4-COD, VOL-II-T2-4-TSS, VOL-II-T2-4-TN, VOL-II-T2-4-TP, VOL-II-T2-4-Turbidity, VOL-II-T2-4-FaecalColiforms, VOL-II-T2-4-ResidualChlorine, VOL-II-T2-4-pH, VOL-II-T2-4-OilGrease, VOL-II-T2-4-NOTE1 (REL-MISSING-ENVIRONMENTAL-PERMIT, link confirmed): that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed [context (not binding): ADD-01:AppB/item-5-effluent-standards p4 'the permit was under review by the regulator and that any change would be issued by Addendum.' (pre-bid minutes; they do not bind the Authority (ADD-01 3.2, p1))]. Linked open issues: I-PERMIT. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Legal counsel</t>
+          <t>Technical</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -38090,7 +38094,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+          <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-NOTE1; VOL-II-T2-4-OilGrease; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-TSS; VOL-II-T2-4-Turbidity; VOL-II-T2-4-pH</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr"/>
@@ -38098,70 +38102,78 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-11</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default) is referenced but not supplied (referenced in VOL-V 39.1). Without it these conclusions cannot be established: VOL-V-39.1-01 (REL-MISSING-SCHEDULE-11-DEFAULTS, link confirmed): which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E; VOL-V:18.2 (REL-MISSING-SCHEDULE-11-LATE-COMPLETION, link confirmed): whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion; VOL-V-31.4-01, VOL-V:39.3 (REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH, link proposed): whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure. Linked open issues: I-VOL-V-MISSING, I-VOL-V-PERSISTENT-BREACH. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>C31 (automatic)</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.4-01; VOL-V-39.1-01</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/Q4</t>
+          <t>I-AUTO-NOT-SUPPLIED-VOL-V-SCHEDULE-7</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
+          <t>Volume V Schedule 7 (deductions) is referenced but not supplied (referenced in VOL-V 31.2). Without it these conclusions cannot be established: VOL-V-31.1-01, VOL-V-31.1-02, VOL-V-31.1-03 (REL-MISSING-SCHEDULE-7-DEDUCTIONS, link confirmed): the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each. Linked open issues: I-VOL-V-MISSING. Not a prerequisite for completing the bid; a person decides whether to raise a clarification or reserve the position</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal counsel</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr"/>
+          <t>relationships (automatic)</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
       <c r="F34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-01/AppA/para1</t>
+          <t>I-AUTO-PRINTED-AppA-proposal-due-date</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare. It prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time' (ADD-01 App A p3) while ADD-01 2.1 (p1) substitutes 'Thursday 26 November 2026' in VOL-I 6.1; not corrected (a person decides: I-F4A-FIELDS)</t>
+          <t>ADD-01:AppA/proposal-due-date prints the Proposal Due Date as 2026-11-12; the effective date (VOL-I:6.1) is 2026-11-26. Not corrected: a person decides what to print and sign, and whether to seek clarification</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Bid manager</t>
+          <t>Legal</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>amendment op</t>
+          <t>C31 (automatic)</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
@@ -38170,12 +38182,12 @@
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
+          <t>I-OP-ADD-01/Q4</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
+          <t>ADD-01/Q4: the geotechnical report and the wadi-crossing drawing (Volume III) are referenced but not supplied</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -38194,12 +38206,12 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
+          <t>I-OP-ADD-01/AppA/para1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
+          <t>ADD-01/AppA/para1: the reissued form may differ from the original in more than its stated purpose; compare. It prints 'Proposal Due Date: 12 November 2026, 14:00 Riyadh time' (ADD-01 App A p3) while ADD-01 2.1 (p1) substitutes 'Thursday 26 November 2026' in VOL-I 6.1; not corrected (a person decides: I-F4A-FIELDS)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -38218,12 +38230,12 @@
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q7</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(2)</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q7: which clause governs the concession term is not stated by the Authority and is a decision for a person (Legal, I-CONCESSION; draft question CQ-CONCESSION-TERM), with what to record in Form 4-E under the Volume V note and how 'the term' in VOL-V 3.2 and 42.2 reads; no decision recorded</t>
+          <t>ADD-02/T1-1-rev/note(2): the addendum restates the value without quoting the old words; the old words were located in the target by shape and need a person's check</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -38242,12 +38254,12 @@
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/Q11</t>
+          <t>I-OP-ADD-02/T1-1-rev/note(3)</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
+          <t>ADD-02/T1-1-rev/note(3): the 'standard five-point scale' is not defined in the pack and the table shows Marks, not weights</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -38266,12 +38278,12 @@
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>I-OP-ADD-02/7.1</t>
+          <t>I-OP-ADD-02/Q7</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
+          <t>ADD-02/Q7: which clause governs the concession term is not stated by the Authority and is a decision for a person (Legal, I-CONCESSION; draft question CQ-CONCESSION-TERM), with what to record in Form 4-E under the Volume V note and how 'the term' in VOL-V 3.2 and 42.2 reads; no decision recorded</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -38290,12 +38302,12 @@
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-01</t>
+          <t>I-OP-ADD-02/Q11</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/Q11: follow-up only (clarification CQ-DWF-STORM-FLOW): 'dry weather flow' in Table 2-6 row 2-6.4 is not defined, so the storm flow to be passed to full treatment is unclear</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -38305,7 +38317,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr"/>
@@ -38314,12 +38326,12 @@
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-SUMMARY-ADD-02</t>
+          <t>I-OP-ADD-02/7.1</t>
         </is>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
+          <t>ADD-02/7.1: re-lettering of the items after (e) is not stated</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -38329,7 +38341,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>C28 (automatic)</t>
+          <t>amendment op</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr"/>
@@ -38338,12 +38350,12 @@
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>I-AUTO-COUNTING</t>
+          <t>I-AUTO-SUMMARY-ADD-01</t>
         </is>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE (ADD-01 3.1), BID-BOND-VALIDITY (VOL-I 6.3), PROPOSAL-VALIDITY (VOL-I 7.1), PROPOSAL-VALIDITY-F4A (Form 4-A), REFERENCE-LOOKBACK (VOL-I 8.5): every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
+          <t>ADD-01's cover summary does not match its provisions (C28): [omitted] ADD-01/3.1 adds an obligation (ADD-01:3.1); the summary does not mention it: 'The attendance record is held by the Authority. A Bidder that considers its attendance to have been incorrectly recorded shall notify the Authority through the Portal within five (5) Working Days of this Addendum.'; [omitted] ADD-01/AppA/para1 replaces VOL-IV:F4-A; the summary does not mention it: 'Form 4-A is reissued below to add the acknowledgement of Addenda at paragraph 1. Bidders shall use this version.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -38353,7 +38365,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>D4 (automatic)</t>
+          <t>C28 (automatic)</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr"/>
@@ -38362,68 +38374,60 @@
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-ratio</t>
+          <t>I-AUTO-SUMMARY-ADD-02</t>
         </is>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
+          <t>ADD-02's cover summary does not match its provisions (C28): [consequence not mentioned] ADD-02:7.2 states 'Failure to submit Form 4-G shall render the Proposal non-responsive.'; the summary says only 'adds Form 4-G'; [understated] 'reinstates Volume I Clause 8.6', but ADD-02/9.1 reinstates it in an amended form: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty-five per cent (35%) for the construction phase. Failure …' (as issued: 'The Bidder shall submit a Local Content Certificate issued by the competent authority evidencing a local content ratio of not less than thirty per cent (30%) f…'); [consequence not mentioned] ADD-02:9.1 states 'Failure to submit the certificate shall render the Proposal non-responsive.'; the summary says only 'reinstates Volume I Clause 8.6'; [omitted] ADD-02/T1-1-rev/note(2) amends VOL-I:11.2; the summary does not mention it: '(2) The combined score weighting stated in Volume I Clause 11.2 is amended to sixty-five per cent (65%) technical and thirty-five per cent (35%) commercial.'; [omitted] ADD-02/5.2 adds an obligation (VOL-II:S3); the summary does not mention it: 'Bidders shall reflect the amended limit in the process design submitted under Volume II Section 3.'; [omitted] ADD-02/9.2 ends the effect of ADD-01:4.2; the summary does not mention it: 'Section 4.2 of Addendum No. 1 ceases to have effect.'. The summary is never applied; a person decides whether to raise a clarification</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-8.6-01</t>
-        </is>
-      </c>
+          <t>C28 (automatic)</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
       <c r="F44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>I-A5-attendance-notice</t>
+          <t>I-AUTO-COUNTING</t>
         </is>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
+          <t>Counting conventions not stated in the pack for ATTENDANCE-NOTICE (ADD-01 3.1), BID-BOND-VALIDITY (VOL-I 6.3), PROPOSAL-VALIDITY (VOL-I 7.1), PROPOSAL-VALIDITY-F4A (Form 4-A), REFERENCE-LOOKBACK (VOL-I 8.5): every reading is shown (A1 Dates); planning uses the conservative reading (config/assumptions.yaml)</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Bid manager</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>A5 (automatic)</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
-        </is>
-      </c>
+          <t>D4 (automatic)</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
       <c r="F45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>I-A5-lcc-certificate</t>
+          <t>I-A5-lcc-ratio</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
+          <t>A5 lcc-ratio: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-06 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 5 WD is an ASSUMPTION: lcc_ratio_calc)</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -38446,12 +38450,12 @@
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>I-A5-assemble-envelope-a</t>
+          <t>I-A5-attendance-notice</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
+          <t>A5 attendance-notice: CONDITIONAL — window elapsed 2026-10-14; whether the condition arose is not known (ATTENDANCE-NOTICE = 2026-10-14 is before the planning date 2026-10-22; needed only if the Bidder considers its attendance at the Pre-Bid Conference to have been incorrectly recorded (ADD-01 3.1); an elapsed window alone does not establish a missed duty: a person records whether the condition arose and, if it did, what was done) (ADD-01-3.1-01, VOL-I-5.4-01; duration 2 WD is an ASSUMPTION: clarification_drafting)</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -38466,7 +38470,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>ADD-01-3.1-01; VOL-I-5.4-01</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr"/>
@@ -38474,17 +38478,17 @@
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>I-A5-copies</t>
+          <t>I-A5-lcc-certificate</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
+          <t>A5 lcc-certificate: INFEASIBLE by 12 WD (total float -12 WD: latest start 2026-10-13 is before the planning date 2026-10-22; not compressed) (VOL-I-8.6-01; duration 30 WD is an ASSUMPTION: lcc_certificate)</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Bid management</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -38494,7 +38498,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-8.6-01</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
@@ -38502,12 +38506,12 @@
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>I-A5-seal-and-mark</t>
+          <t>I-A5-assemble-envelope-a</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+          <t>A5 assemble-envelope-a: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-10 (after lcc-certificate) is after the latest start 2026-11-24; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.2-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: envelope_assembly)</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -38522,7 +38526,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr"/>
@@ -38530,12 +38534,12 @@
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>I-A5-deliver</t>
+          <t>I-A5-copies</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+          <t>A5 copies: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after assemble-envelope-a) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-6.5-01, VOL-I-6.5-02, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: copies_and_usb)</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -38550,7 +38554,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr"/>
@@ -38558,33 +38562,89 @@
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>I-A5-seal-and-mark</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>A5 seal-and-mark: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-13 (after copies) is after the latest start 2026-11-25; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 0 WD is an ASSUMPTION: seal_and_mark)</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>I-A5-deliver</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>A5 deliver: INFEASIBLE by 12 WD (total float -12 WD: earliest start 2026-12-14 (after seal-and-mark) is after the latest start 2026-11-26; not compressed) (VOL-I-6.1-01, VOL-I-6.2-01, VOL-I-9.1-01, VOL-I-App3-01; duration 1 WD is an ASSUMPTION: delivery)</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Bid management</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>A5 (automatic)</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-9.1-01; VOL-I-App3-01</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>I-A5-FEASIBILITY</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>A5 at the status date: lcc-ratio INFEASIBLE by 12 WD; lcc-certificate INFEASIBLE by 12 WD; assemble-envelope-a INFEASIBLE by 12 WD; copies INFEASIBLE by 12 WD; seal-and-mark INFEASIBLE by 12 WD; deliver INFEASIBLE by 12 WD. Lead times are PROVISIONAL assumptions (A5 drivers)</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Bid manager</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>A5 (automatic)</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>VOL-I-6.1-01; VOL-I-6.2-01; VOL-I-6.2-02; VOL-I-6.5-01; VOL-I-6.5-02; VOL-I-8.6-01; VOL-I-9.1-01; VOL-I-App3-01</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F51"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -42439,7 +42499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O27"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -42448,15 +42508,16 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="70" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="30" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="45" customHeight="1">
@@ -42499,45 +42560,50 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>Scope</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Document</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Blocks</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>Issues</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Origin</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>Reached</t>
         </is>
@@ -42574,35 +42640,36 @@
           <t>VOL-I-8.4-01; VOL-I-8.4-02; calc:financial-standing</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>VOL-I:8.4 p4: “on a combined basis across consortium members weighted by shareholding”; VOL-I:8.1 p4: “No change to the composition, shareholding or lead member of a prequalified consortium shall be effective without the prior written consent of the Authority.”</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr"/>
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>The financial standing is combined across the members and weighted by shareholding: a member added, removed or re-weighted changes the calculation (the members and their shares are bidder facts, I-BIDDER-FACTS).</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr"/>
       <c r="K3" s="4" t="inlineStr"/>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr"/>
+      <c r="P3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -42635,35 +42702,36 @@
           <t>VOL-I-9.4-01; VOL-IV-F4C-N1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>VOL-I:9.4 p5: “signed and stamped by an authorised signatory of each member of the Bidder”; VOL-I:9.4 p5: “Failure to submit a complete and properly executed Form 4-C for each member shall render the Proposal non-responsive.”; VOL-IV:F4-C/image/note p6: “يجب تقديم هذا النموذج باللغة العربية عن كل عضو من أعضاء الائتلاف”</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr"/>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>One Form 4-C per member: a new member gives its own (in Arabic, signed and stamped by its authorised signatory).</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
       <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O4" s="4" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -42696,35 +42764,36 @@
           <t>VOL-I-8.2-01; VOL-IV-F4C-02</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>VOL-I:8.2 p4: “No firm, and no affiliate of a firm, shall participate in more than one Proposal.”; VOL-IV:F4-C/image/intro p6: “بصفتنا ممثلين مفوضين عن العضو المذكور أدناه في ائتلاف مقدم العرض”; VOL-IV:F4-C/image/decl2 p6: “أن الشركة لم تشارك، بصورة مباشرة أو غير مباشرة، في أكثر من عرض واحد لهذه المناقصة”</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Each member declares in its Form 4-C (declaration 2, given for 'the member named below') that it has not taken part in more than one proposal: a new member, and its affiliates, must be checked against VOL-I 8.2.</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
       <c r="K5" s="4" t="inlineStr"/>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N5" s="4" t="inlineStr">
+      <c r="O5" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -42757,31 +42826,32 @@
           <t>VOL-I-8.10-01; VOL-IV-F4C-03</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>VOL-I:8.10 p4: “No member of the Bidder shall be the subject of, or have been the subject of within the preceding five (5) years, any debarment by a public authority in the Kingdom.”; VOL-I:8.10 p4: “A declaration to this effect shall be given in Form 4-C.”</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
       <c r="I6" s="4" t="inlineStr"/>
       <c r="J6" s="4" t="inlineStr"/>
       <c r="K6" s="4" t="inlineStr"/>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr"/>
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N6" s="4" t="inlineStr">
+      <c r="O6" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -42814,35 +42884,36 @@
           <t>VOL-I-8.9-01</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>VOL-I:8.9 p4: “evidence of a current investment licence for each foreign consortium member”</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Whether a new member is foreign is a bidder fact (bidder.foreign_members is a labelled assumption).</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
       <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>I-BIDDER-FACTS</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N7" s="4" t="inlineStr">
+      <c r="O7" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -42875,35 +42946,36 @@
           <t>VOL-II-3.1-01</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr"/>
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>VOL-II:3.1 p3: “The treatment process shall be capable of achieving the effluent quality in Table 2-4 under all design influent conditions in Table 2-2.”</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr"/>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>A changed limit, unit or basis of assessment changes what the process design must achieve. The qualifier 'all values are maxima' and the chlorine and pH ranges stay an open question (I-VOL-II-T24-TENSIONS).</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr"/>
       <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
         <is>
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O8" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
+      <c r="P8" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
@@ -42940,35 +43012,36 @@
           <t>VOL-II-7.2-01</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>VOL-II:7.2 p4: “during which every parameter in Table 2-4 has been met”; VOL-II:7.3 p4: “A failure of any Table 2-4 parameter during the reliability run shall restart the run in full.”</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>The 30-day reliability run before PCOD must meet every Table 2-4 parameter as amended; a failure restarts it in full.</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr"/>
       <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O9" s="4" t="inlineStr">
+      <c r="P9" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
@@ -43005,35 +43078,36 @@
           <t>VOL-V-31.1-02</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>VOL-V:31.1 p3: “(b) the treated effluent fails any parameter in Volume II Table 2-4”</t>
         </is>
       </c>
-      <c r="H10" s="4" t="inlineStr"/>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>After PCOD a failure of any Table 2-4 parameter is an Unavailability Event (VOL-V 31.1(b)), with deductions and no cure period.</t>
         </is>
       </c>
-      <c r="J10" s="4" t="inlineStr"/>
       <c r="K10" s="4" t="inlineStr"/>
-      <c r="L10" s="4" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
         <is>
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
-      <c r="M10" s="4" t="inlineStr">
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
+      <c r="O10" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O10" s="4" t="inlineStr">
+      <c r="P10" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
@@ -43072,33 +43146,38 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>rolling average (verbatim in its evidence; members in scope: BOD5, COD, TN, TP, TSS) (scope PROPOSED, not reviewed; the owner may keep the issue on the row)</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>VOL-V:29.3 p3: “no availability deduction shall apply to a parameter listed in Table 2-4 as assessed on a rolling average basis”</t>
         </is>
       </c>
-      <c r="H11" s="4" t="inlineStr"/>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>The second limb of 29.3 turns on which parameters Table 2-4 assesses on a rolling average: a changed basis of assessment changes the Ramp-Up relief.</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
       <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
         <is>
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
+      <c r="O11" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O11" s="4" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
@@ -43132,34 +43211,35 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>VOL-II-2.4-01; VOL-II-2.5-01; VOL-II-4.3-02</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>VOL-II-2.4-01; VOL-II-4.3-02</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.4 p2: “The treated effluent shall at all times comply with the parameters set out in Table 2-4.”; VOL-II:4.3 p4: “such that the Facility can meet Table 2-4 with any one stream out of service”</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr"/>
       <c r="J12" s="4" t="inlineStr"/>
       <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>I-VOL-II-T24-TENSIONS</t>
         </is>
       </c>
-      <c r="M12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O12" s="4" t="inlineStr">
+      <c r="P12" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
@@ -43168,12 +43248,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-MECHANISM</t>
+          <t>REL-T24-CONTINUOUS-MONITORING</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>limit_applies</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -43188,68 +43268,73 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
+          <t>VOL-II:T2-4</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>calc:availability-payment</t>
+          <t>VOL-II-2.5-01</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr"/>
+          <t>continuous (verbatim in its evidence; members in scope: ResidualChlorine, pH) (scope PROPOSED, not reviewed; the owner may keep the issue on the row)</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II:2.5 p2: “continuous online monitoring for those parameters identified in Table 2-4 as assessed on a continuous basis”</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>VOL-II 2.5 monitors the parameters Table 2-4 assesses on a continuous basis: a changed basis of assessment, or a changed limit of a continuously assessed parameter, changes what is monitored online.</t>
+        </is>
+      </c>
       <c r="K13" s="4" t="inlineStr"/>
       <c r="L13" s="4" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr">
         <is>
+          <t>I-VOL-II-T24-TENSIONS</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01</t>
-        </is>
-      </c>
+      <c r="P13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-DEDUCTIONS</t>
+          <t>REL-PAY-MECHANISM</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>proposed relationship</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+          <t>VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -43257,93 +43342,99 @@
           <t>calc:availability-payment</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-V:H:C29 p3: “CLAUSE 29 — PAYMENT MECHANISM”</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr"/>
-      <c r="J14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>Every sub-clause of Clause 29 is part of the payment mechanism the Availability Payment is calculated under (the Ramp-Up payment of 29.3 included).</t>
+        </is>
+      </c>
       <c r="K14" s="4" t="inlineStr"/>
       <c r="L14" s="4" t="inlineStr"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
+      <c r="O14" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-QUOTED-PRICE</t>
+          <t>REL-PAY-DEDUCTIONS</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>proposed relationship</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
+          <t>VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
           <t>calc:availability-payment</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I-10.2-01</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr"/>
-      <c r="I15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:1.1 p2: “Availability Payment means the annual payment calculated under Clause 29 and adjusted under Clause 31.”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>The definition says the Availability Payment is adjusted under Clause 31, but the price quoted under VOL-I 10.2 is calculated under Clause 29 only: whether a change to the deductions changes the quoted price, or only the risk priced into it, is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
       <c r="J15" s="4" t="inlineStr"/>
       <c r="K15" s="4" t="inlineStr"/>
       <c r="L15" s="4" t="inlineStr"/>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
+      <c r="O15" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01</t>
-        </is>
-      </c>
+      <c r="P15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FORM-4F</t>
+          <t>REL-PAY-QUOTED-PRICE</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -43368,30 +43459,31 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV-F4F-01</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>VOL-I-10.2-01</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.2 p5: “The Bidder shall quote a single Availability Payment expressed in Saudi Riyals per annum, calculated in accordance with the payment mechanism at Volume V Clause 29.”</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr"/>
       <c r="J16" s="4" t="inlineStr"/>
       <c r="K16" s="4" t="inlineStr"/>
       <c r="L16" s="4" t="inlineStr"/>
-      <c r="M16" s="4" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
+      <c r="O16" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O16" s="4" t="inlineStr">
+      <c r="P16" s="4" t="inlineStr">
         <is>
           <t>ADD-01</t>
         </is>
@@ -43400,22 +43492,22 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FINANCIAL-MODEL</t>
+          <t>REL-PAY-FORM-4F</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>proposed</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>proposed relationship</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -43425,38 +43517,31 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.3-01</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
-        </is>
-      </c>
+          <t>VOL-IV-F4F-01</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
-        </is>
-      </c>
+          <t>VOL-IV:F4-F/availability-payment-sar-per-annum-year-1-of-operations p9: “Availability Payment (SAR per annum, year 1 of operations):”; VOL-IV:F4-F/indexation-basis-assumed p9: “Indexation basis assumed: Per Volume V Clause 29.2”</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
       <c r="J17" s="4" t="inlineStr"/>
       <c r="K17" s="4" t="inlineStr"/>
       <c r="L17" s="4" t="inlineStr"/>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
+      <c r="P17" s="4" t="inlineStr">
         <is>
           <t>ADD-01</t>
         </is>
@@ -43465,195 +43550,198 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>REL-MODEL-FORM-4F</t>
+          <t>REL-PAY-FINANCIAL-MODEL</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>feeds_calculation</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>proposed relationship</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
+          <t>calc:availability-payment</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
           <t>VOL-I-10.3-01</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>VOL-IV-F4F-02</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
-      <c r="I18" s="4" t="inlineStr"/>
-      <c r="J18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>VOL-IV:F4-F/para1 p9: “has been derived from the Financial Model submitted with this Form”; VOL-I:10.2 p5: “calculated in accordance with the payment mechanism at Volume V Clause 29”</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>Form 4-F states that the Availability Payment is derived from the Financial Model, and VOL-I 10.2 that it is calculated under the payment mechanism of Volume V Clause 29; so the model must reproduce Clause 29 (the Ramp-Up payment of 29.3 included). That a change to Clause 29 requires the model to be re-run is the curator's inference, not a stated link.</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>Reaches the Envelope B modelling activities (fin-model-build, fin-model-freeze) through the row's evidence item (EV-FIN-MODEL).</t>
+        </is>
+      </c>
       <c r="K18" s="4" t="inlineStr"/>
       <c r="L18" s="4" t="inlineStr"/>
-      <c r="M18" s="4" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr"/>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
+      <c r="O18" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01; ADD-02</t>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
+          <t>REL-MODEL-FORM-4F</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>feeds_calculation</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>possible impact</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>calc:availability-payment</t>
+          <t>VOL-I-10.3-01</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.6-01</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
-        </is>
-      </c>
+          <t>VOL-IV-F4F-02</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
+          <t>VOL-IV:F4-F/para1 p9: “We confirm that the Availability Payment stated above is unconditional, is not subject to any qualification, and has been derived from the Financial Model submitted with this Form.”</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr"/>
       <c r="J19" s="4" t="inlineStr"/>
       <c r="K19" s="4" t="inlineStr"/>
       <c r="L19" s="4" t="inlineStr"/>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
+      <c r="O19" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01</t>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-02</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>REL-LCC-ENVELOPE-A</t>
+          <t>REL-PAY-FINANCING-ASSUMPTIONS</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>cites</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>possible impact</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:8.6</t>
+          <t>calc:availability-payment</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>VOL-I:9.1(i)</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>VOL-I:9.1(i) p4: “(i) the certificates and evidence required under Section 8.”; VOL-I:8.6 p4: “The Bidder shall submit a Local Content Certificate issued by the competent authority”</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>VOL-I-10.6-01</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:10.6 p5: “a schedule of the principal financing assumptions underlying the Availability Payment”</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Item (i) of the Envelope A list is whatever Section 8 requires: the Local Content Certificate leaves it when ADD-01 4.1 deletes VOL-I 8.6 and returns when ADD-02 9.1 reinstates 8.6 at 35%.</t>
+          <t>The schedule states the financing assumptions underlying the Availability Payment; whether a change to the payment mechanism changes them (for example debt sized on the Ramp-Up revenue) is a commercial judgement.</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr"/>
       <c r="K20" s="4" t="inlineStr"/>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>I-LCC-ISSUER</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O20" s="4" t="inlineStr">
-        <is>
-          <t>ADD-01; ADD-02</t>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>REL-VOL-V-FORM-4E</t>
+          <t>REL-LCC-ENVELOPE-A</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>cites</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -43668,39 +43756,44 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:1.1; VOL-V:1.2; VOL-V:1.3; VOL-V:1.4; VOL-V:1.5; VOL-V:1.6; VOL-V:3.1; VOL-V:3.2; VOL-V:3.3; VOL-V:12.1; VOL-V:12.2; VOL-V:12.3; VOL-V:12.4; VOL-V:18.1; VOL-V:18.2; VOL-V:18.3; VOL-V:18.4; VOL-V:24.1; VOL-V:24.2; VOL-V:24.3; VOL-V:24.4; VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5; VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5; VOL-V:34.1; VOL-V:34.2; VOL-V:34.3; VOL-V:36.1; VOL-V:36.2; VOL-V:36.3; VOL-V:39.1; VOL-V:39.2; VOL-V:39.3; VOL-V:39.4; VOL-V:39.5; VOL-V:40.1; VOL-V:40.2; VOL-V:40.3; VOL-V:42.1; VOL-V:42.2; VOL-V:44.1; VOL-V:44.2; VOL-V:44.3</t>
+          <t>VOL-I:8.6</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>VOL-IV-F4E-01</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:cover/note-to-bidders p2: “This extract contains the clauses of the draft Project Agreement on which the Authority invites comment through Form 4-E.”; VOL-V:cover/note-to-bidders p2: “A deviation not listed in Form 4-E will be taken as accepted.”</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr"/>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>A changed Volume V clause (ADD-02 8.1: VOL-V 36.2, SAR 5,000,000 to SAR 2,500,000) is a clause on which Form 4-E invites comment: whether to list a deviation from it is re-read; what to list is for Legal.</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr"/>
+          <t>VOL-I:9.1(i)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>VOL-I:9.1(i) p4: “(i) the certificates and evidence required under Section 8.”; VOL-I:8.6 p4: “The Bidder shall submit a Local Content Certificate issued by the competent authority”</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>Item (i) of the Envelope A list is whatever Section 8 requires: the Local Content Certificate leaves it when ADD-01 4.1 deletes VOL-I 8.6 and returns when ADD-02 9.1 reinstates 8.6 at 35%.</t>
+        </is>
+      </c>
       <c r="K21" s="4" t="inlineStr"/>
       <c r="L21" s="4" t="inlineStr"/>
       <c r="M21" s="4" t="inlineStr">
         <is>
+          <t>I-LCC-ISSUER</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O21" s="4" t="inlineStr">
+      <c r="P21" s="4" t="inlineStr">
         <is>
           <t>ADD-01; ADD-02</t>
         </is>
@@ -43709,7 +43802,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>REL-CHANGE-IN-LAW-FINANCIAL-MODEL</t>
+          <t>REL-VOL-V-FORM-4E</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -43719,119 +43812,117 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>possible</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>possible impact</t>
+          <t>confirmed dependency</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:36.2</t>
+          <t>VOL-V:1.1; VOL-V:1.2; VOL-V:1.3; VOL-V:1.4; VOL-V:1.5; VOL-V:1.6; VOL-V:3.1; VOL-V:3.2; VOL-V:3.3; VOL-V:12.1; VOL-V:12.2; VOL-V:12.3; VOL-V:12.4; VOL-V:18.1; VOL-V:18.2; VOL-V:18.3; VOL-V:18.4; VOL-V:24.1; VOL-V:24.2; VOL-V:24.3; VOL-V:24.4; VOL-V:29.1; VOL-V:29.2; VOL-V:29.3; VOL-V:29.4; VOL-V:29.5; VOL-V:31.1; VOL-V:31.2; VOL-V:31.3; VOL-V:31.4; VOL-V:31.5; VOL-V:34.1; VOL-V:34.2; VOL-V:34.3; VOL-V:36.1; VOL-V:36.2; VOL-V:36.3; VOL-V:39.1; VOL-V:39.2; VOL-V:39.3; VOL-V:39.4; VOL-V:39.5; VOL-V:40.1; VOL-V:40.2; VOL-V:40.3; VOL-V:42.1; VOL-V:42.2; VOL-V:44.1; VOL-V:44.2; VOL-V:44.3</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>VOL-I-10.3-01</t>
+          <t>VOL-IV-F4E-01</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>VOL-V 36.2 sets the capital expenditure a General Change in Law must exceed before the Project Company is compensated (SAR 2,500,000 after ADD-02 8.1); no clause links it to the Financial Model, and whether the model prices the retained Change in Law risk is a commercial judgement (inferred, not stated).</t>
+          <t>VOL-V:cover/note-to-bidders p2: “This extract contains the clauses of the draft Project Agreement on which the Authority invites comment through Form 4-E.”; VOL-V:cover/note-to-bidders p2: “A deviation not listed in Form 4-E will be taken as accepted.”</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr"/>
-      <c r="J22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>A changed Volume V clause (ADD-02 8.1: VOL-V 36.2, SAR 5,000,000 to SAR 2,500,000) is a clause on which Form 4-E invites comment: whether to list a deviation from it is re-read; what to list is for Legal.</t>
+        </is>
+      </c>
       <c r="K22" s="4" t="inlineStr"/>
       <c r="L22" s="4" t="inlineStr"/>
-      <c r="M22" s="4" t="inlineStr">
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
+      <c r="O22" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O22" s="4" t="inlineStr">
-        <is>
-          <t>ADD-02</t>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>ADD-01; ADD-02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
+          <t>REL-CHANGE-IN-LAW-FINANCIAL-MODEL</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>missing_document</t>
+          <t>depends_on</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>possible</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>possible impact</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:39.1</t>
+          <t>VOL-V:36.2</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-39.1-01</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
-        </is>
-      </c>
+          <t>VOL-I-10.3-01</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr"/>
       <c r="H23" s="4" t="inlineStr"/>
-      <c r="I23" s="4" t="inlineStr"/>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>I-VOL-V-MISSING</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V 36.2 sets the capital expenditure a General Change in Law must exceed before the Project Company is compensated (SAR 2,500,000 after ADD-02 8.1); no clause links it to the Financial Model, and whether the model prices the retained Change in Law risk is a commercial judgement (inferred, not stated).</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N23" s="4" t="inlineStr">
+      <c r="O23" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
+          <t>REL-MISSING-SCHEDULE-11-DEFAULTS</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -43856,47 +43947,48 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:18.2</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>VOL-V-39.1-01</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “The Authority may terminate for a Project Company Event of Default, being the events listed in Schedule 11.”</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr"/>
-      <c r="J24" s="4" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr">
         <is>
           <t>Volume V Schedule 11 (Project Company Events of Default)</t>
         </is>
       </c>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
-        </is>
-      </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
+          <t>which events are Project Company Events of Default, so how to avoid them and whether to reserve the position in Form 4-E</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
           <t>I-VOL-V-MISSING</t>
         </is>
       </c>
-      <c r="M24" s="4" t="inlineStr">
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
+      <c r="O24" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
+          <t>REL-MISSING-SCHEDULE-11-LATE-COMPLETION</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -43906,66 +43998,63 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:18.2 p2: “without prejudice to its termination rights under Clause 39”; VOL-V:39.1 p4: “being the events listed in Schedule 11”</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>whether late completion short of the VOL-V 18.3 long-stop is itself an Event of Default giving a termination right under 39.1, so whether delay liquidated damages are in practice the only remedy for late completion</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>proposed relationship</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:39.1</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V-31.4-01; VOL-V:39.3</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="inlineStr"/>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
-        </is>
-      </c>
-      <c r="K25" s="4" t="inlineStr">
-        <is>
-          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
-        </is>
-      </c>
-      <c r="M25" s="4" t="inlineStr">
-        <is>
-          <t>curator</t>
-        </is>
-      </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>proposed</t>
-        </is>
-      </c>
-      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+          <t>REL-MISSING-SCHEDULE-11-PERSISTENT-BREACH</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -43975,137 +44064,209 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>proposed</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>confirmed dependency</t>
+          <t>proposed relationship</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>VOL-V:31.2</t>
+          <t>VOL-V:39.1</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
-      <c r="I26" s="4" t="inlineStr"/>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>Volume V Schedule 7 (deductions)</t>
-        </is>
-      </c>
+          <t>VOL-V-31.4-01; VOL-V:39.3</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:39.1 p4: “being the events listed in Schedule 11”; VOL-V:31.4 p3: “on a second occurrence, to terminate under Clause 39.3”; VOL-V:39.3 p4: “The Authority may terminate for persistent breach in the circumstances described in Clause 31.4.”</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>31.4 and 39.3 give a termination right for persistent breach; 39.1 gives one for the Events of Default in Schedule 11, which is not supplied. The documents do not say whether persistent breach is also listed there: that it may be is the curator's inference.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+          <t>Volume V Schedule 11 (Project Company Events of Default)</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>I-VOL-V-MISSING</t>
+          <t>whether persistent breach (three or more Unavailability Events in a rolling 90 days) is also an Event of Default listed in Schedule 11, giving a termination right under 39.1 independent of 31.4 and 39.3; so an amendment or deletion of 31.4 or 39.3 cannot be concluded to remove that exposure</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
+          <t>I-VOL-V-MISSING; I-VOL-V-PERSISTENT-BREACH</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O26" s="4" t="inlineStr">
-        <is>
-          <t>ADD-02</t>
-        </is>
-      </c>
+      <c r="P26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>REL-MISSING-SCHEDULE-7-DEDUCTIONS</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>missing_document</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>confirmed dependency</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V-31.1-01; VOL-V-31.1-02; VOL-V-31.1-03</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>VOL-V:31.2 p3: “the Authority shall deduct from the Availability Payment the amounts calculated under Schedule 7”</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr"/>
+      <c r="J27" s="4" t="inlineStr"/>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Volume V Schedule 7 (deductions)</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>the amount of the deduction for each Unavailability Event under 31.1(a), (b) and (c), so the price risk of each</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>I-VOL-V-MISSING</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>curator</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>proposed</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>ADD-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>REL-MISSING-ENVIRONMENTAL-PERMIT</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>missing_document</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>confirmed dependency</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>VOL-II:2.4; VOL-II:T2-4-heading/para1</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>VOL-II-2.4-01; VOL-II-T2-4-BOD5; VOL-II-T2-4-COD; VOL-II-T2-4-TSS; VOL-II-T2-4-TN; VOL-II-T2-4-TP; VOL-II-T2-4-Turbidity; VOL-II-T2-4-FaecalColiforms; VOL-II-T2-4-ResidualChlorine; VOL-II-T2-4-pH; VOL-II-T2-4-OilGrease; VOL-II-T2-4-NOTE1</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>VOL-II:2.4 p2: “Table 2-4 is reproduced overleaf from the Environmental Permit issued for the site”; VOL-II:T2-4-heading/para1 p3: “In the event of any discrepancy between this reproduction and the Environmental Permit, the Environmental Permit shall prevail.”; VOL-II:T2-4/note1 p3: “Where a parameter is not listed above, the limit stated in the Environmental Permit shall apply.”</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr"/>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>context (not binding): ADD-01:AppB/item-5-effluent-standards p4 'the permit was under review by the regulator and that any change would be issued by Addendum.' (pre-bid minutes; they do not bind the Authority (ADD-01 3.2, p1))</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>the Environmental Permit issued for the site</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>that the reproduced Table 2-4 limits, as amended by the addenda, are the limits that govern (the Permit prevails over the reproduction), and the limit of any parameter not listed (Note 1); Permit compliance is not claimed</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>I-PERMIT</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="N28" s="4" t="inlineStr">
         <is>
           <t>curator</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
+      <c r="O28" s="4" t="inlineStr">
         <is>
           <t>proposed</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="P28" s="4" t="inlineStr">
         <is>
           <t>ADD-02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:O27"/>
+  <autoFilter ref="A2:P28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
